--- a/hidden-housing-costs/outputs/cbsa_affordability_2026_06.xlsx
+++ b/hidden-housing-costs/outputs/cbsa_affordability_2026_06.xlsx
@@ -2894,7 +2894,7 @@
         <v>0.0553926142966436</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0531237859388389</v>
+        <v>0.053123785938839</v>
       </c>
       <c r="N2" t="n">
         <v>0.00730452056659036</v>
@@ -2992,7 +2992,7 @@
         <v>0.0276907886264308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0777862795899633</v>
+        <v>0.077786279589963</v>
       </c>
       <c r="M3" t="n">
         <v>0.0330527929011777</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00851494440778551</v>
+        <v>0.00851494440778548</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0570040921049297</v>
@@ -3013,13 +3013,13 @@
         <v>0.0272570774792698</v>
       </c>
       <c r="S3" t="n">
-        <v>21501.9347146756</v>
+        <v>21501.9347146755</v>
       </c>
       <c r="T3" t="n">
         <v>1160.68709606547</v>
       </c>
       <c r="U3" t="n">
-        <v>3260.4896952929</v>
+        <v>3260.48969529289</v>
       </c>
       <c r="V3" t="n">
         <v>1385.44086724577</v>
@@ -3028,7 +3028,7 @@
         <v>1003.94265742447</v>
       </c>
       <c r="X3" t="n">
-        <v>356.912409796737</v>
+        <v>356.912409796736</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>0.381057513460698</v>
       </c>
       <c r="J4" t="n">
-        <v>0.25684234697908</v>
+        <v>0.256842346979081</v>
       </c>
       <c r="K4" t="n">
         <v>0.028729122507985</v>
@@ -3289,7 +3289,7 @@
         <v>0.601428251274032</v>
       </c>
       <c r="J6" t="n">
-        <v>0.413716463991846</v>
+        <v>0.413716463991847</v>
       </c>
       <c r="K6" t="n">
         <v>0.0231396057229075</v>
@@ -3316,7 +3316,7 @@
         <v>0.0249907741807401</v>
       </c>
       <c r="S6" t="n">
-        <v>31856.4516134829</v>
+        <v>31856.451613483</v>
       </c>
       <c r="T6" t="n">
         <v>1225.65863593096</v>
@@ -3408,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00898864559888065</v>
+        <v>0.00898864559888068</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0374320161104587</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0109046463712736</v>
+        <v>0.0109046463712737</v>
       </c>
       <c r="S7" t="n">
         <v>27252.5313781543</v>
@@ -3432,13 +3432,13 @@
         <v>675.758667461384</v>
       </c>
       <c r="X7" t="n">
-        <v>458.079357010156</v>
+        <v>458.079357010157</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>555.722588372847</v>
+        <v>555.722588372848</v>
       </c>
       <c r="AA7" t="n">
         <v>0.00388888888888889</v>
@@ -3494,7 +3494,7 @@
         <v>0.312069282550604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0448800879346147</v>
+        <v>0.0448800879346148</v>
       </c>
       <c r="L8" t="n">
         <v>0.0151621918698023</v>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00826738461953428</v>
+        <v>0.0082673846195343</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0667591308027394</v>
@@ -3524,7 +3524,7 @@
         <v>1474.31088865209</v>
       </c>
       <c r="U8" t="n">
-        <v>498.078002923006</v>
+        <v>498.078002923005</v>
       </c>
       <c r="V8" t="n">
         <v>2193.03744686999</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>271.583584751701</v>
+        <v>271.583584751702</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0.023467787872917</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0948934225543143</v>
+        <v>0.0948934225543141</v>
       </c>
       <c r="M9" t="n">
         <v>0.0423387925542318</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0093871151491668</v>
+        <v>0.00938711514916681</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0423387925542318</v>
@@ -3625,7 +3625,7 @@
         <v>1252.26462868673</v>
       </c>
       <c r="U9" t="n">
-        <v>5063.60792092077</v>
+        <v>5063.60792092076</v>
       </c>
       <c r="V9" t="n">
         <v>2259.24030948636</v>
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2254.0763316361</v>
+        <v>2254.07633163611</v>
       </c>
       <c r="AA9" t="n">
         <v>0.00342857142857143</v>
@@ -3699,13 +3699,13 @@
         <v>0.0200893938569507</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0484732722987785</v>
+        <v>0.0484732722987787</v>
       </c>
       <c r="M10" t="n">
         <v>0.0402701031405238</v>
       </c>
       <c r="N10" t="n">
-        <v>0.00488122462309379</v>
+        <v>0.0048812246230938</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -3717,16 +3717,16 @@
         <v>0.0451513277636176</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0690344625266121</v>
+        <v>0.0690344625266123</v>
       </c>
       <c r="S10" t="n">
-        <v>15046.0812515799</v>
+        <v>15046.08125158</v>
       </c>
       <c r="T10" t="n">
-        <v>783.647075571932</v>
+        <v>783.647075571931</v>
       </c>
       <c r="U10" t="n">
-        <v>1890.84540583075</v>
+        <v>1890.84540583076</v>
       </c>
       <c r="V10" t="n">
         <v>1570.85618330555</v>
@@ -3812,13 +3812,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00604160804742369</v>
+        <v>0.0060416080474237</v>
       </c>
       <c r="Q11" t="n">
         <v>0.0497645731771824</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00801437802209264</v>
+        <v>0.00801437802209266</v>
       </c>
       <c r="S11" t="n">
         <v>20733.1589280537</v>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>374.864517605361</v>
+        <v>374.864517605362</v>
       </c>
       <c r="AA11" t="n">
         <v>0.01</v>
@@ -3892,7 +3892,7 @@
         <v>16674.1259089892</v>
       </c>
       <c r="I12" t="n">
-        <v>0.560694643490189</v>
+        <v>0.56069464349019</v>
       </c>
       <c r="J12" t="n">
         <v>0.375416546414256</v>
@@ -3916,7 +3916,7 @@
         <v>0.0122713970137817</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0526197503950959</v>
+        <v>0.052619750395096</v>
       </c>
       <c r="R12" t="n">
         <v>0.0239374051082168</v>
@@ -3928,7 +3928,7 @@
         <v>1678.70502297071</v>
       </c>
       <c r="U12" t="n">
-        <v>3668.28134649155</v>
+        <v>3668.28134649156</v>
       </c>
       <c r="V12" t="n">
         <v>1726.66802362702</v>
@@ -3937,7 +3937,7 @@
         <v>610.438190171168</v>
       </c>
       <c r="X12" t="n">
-        <v>545.034098367115</v>
+        <v>545.034098367114</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>1426.86632073588</v>
       </c>
       <c r="U13" t="n">
-        <v>4094.56934781061</v>
+        <v>4094.56934781062</v>
       </c>
       <c r="V13" t="n">
         <v>1843.95032218175</v>
@@ -4130,7 +4130,7 @@
         <v>1296.74187663028</v>
       </c>
       <c r="U14" t="n">
-        <v>5724.85871524386</v>
+        <v>5724.85871524384</v>
       </c>
       <c r="V14" t="n">
         <v>2587.23439481897</v>
@@ -4139,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>328.018425200188</v>
+        <v>328.018425200187</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
         <v>0.040568924510891</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0166122751229942</v>
+        <v>0.0166122751229941</v>
       </c>
       <c r="M15" t="n">
         <v>0.0760667334579206</v>
@@ -4222,7 +4222,7 @@
         <v>0.0787713284253133</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00869334096661947</v>
+        <v>0.00869334096661949</v>
       </c>
       <c r="S15" t="n">
         <v>14941.3246636107</v>
@@ -4231,7 +4231,7 @@
         <v>1363.39984603751</v>
       </c>
       <c r="U15" t="n">
-        <v>558.288730058465</v>
+        <v>558.288730058464</v>
       </c>
       <c r="V15" t="n">
         <v>2556.37471132034</v>
@@ -4302,7 +4302,7 @@
         <v>0.393878233062227</v>
       </c>
       <c r="K16" t="n">
-        <v>0.022661938411039</v>
+        <v>0.0226619384110389</v>
       </c>
       <c r="L16" t="n">
         <v>0.0842740834660511</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0119752792191666</v>
+        <v>0.0119752792191667</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0504743173700413</v>
@@ -4341,7 +4341,7 @@
         <v>150.863408248993</v>
       </c>
       <c r="X16" t="n">
-        <v>626.37895483773</v>
+        <v>626.378954837731</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.00199431381380105</v>
+        <v>0.00199431381380104</v>
       </c>
       <c r="Q17" t="n">
         <v>0.0345681061058848</v>
@@ -4507,7 +4507,7 @@
         <v>0.0359964394624403</v>
       </c>
       <c r="L18" t="n">
-        <v>0.068816722501724</v>
+        <v>0.0688167225017241</v>
       </c>
       <c r="M18" t="n">
         <v>0.0610374408276161</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>749.274297793748</v>
+        <v>749.274297793746</v>
       </c>
       <c r="AA18" t="n">
         <v>0.004</v>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>976.379899578327</v>
+        <v>976.379899578329</v>
       </c>
       <c r="AA19" t="n">
         <v>0.00416666666666667</v>
@@ -4700,7 +4700,7 @@
         <v>22692.7604987565</v>
       </c>
       <c r="I20" t="n">
-        <v>0.659911053058613</v>
+        <v>0.659911053058612</v>
       </c>
       <c r="J20" t="n">
         <v>0.437703934781686</v>
@@ -4736,13 +4736,13 @@
         <v>1523.06944434235</v>
       </c>
       <c r="U20" t="n">
-        <v>6874.96624182312</v>
+        <v>6874.9662418231</v>
       </c>
       <c r="V20" t="n">
         <v>1827.68333321082</v>
       </c>
       <c r="W20" t="n">
-        <v>913.841666605409</v>
+        <v>913.84166660541</v>
       </c>
       <c r="X20" t="n">
         <v>380.767361085587</v>
@@ -4902,7 +4902,7 @@
         <v>14955.8852422036</v>
       </c>
       <c r="I22" t="n">
-        <v>0.44227402943254</v>
+        <v>0.442274029432541</v>
       </c>
       <c r="J22" t="n">
         <v>0.322345954311778</v>
@@ -4929,7 +4929,7 @@
         <v>0.050440543272723</v>
       </c>
       <c r="R22" t="n">
-        <v>0.00901459872623217</v>
+        <v>0.00901459872623215</v>
       </c>
       <c r="S22" t="n">
         <v>20520.1881435816</v>
@@ -4953,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>418.250337100994</v>
+        <v>418.250337100993</v>
       </c>
       <c r="AA22" t="n">
         <v>0.00488888888888889</v>
@@ -5119,7 +5119,7 @@
         <v>0.042066744743447</v>
       </c>
       <c r="N24" t="n">
-        <v>0.00858504994764222</v>
+        <v>0.00858504994764224</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>2052.18407556432</v>
       </c>
       <c r="W24" t="n">
-        <v>418.813076645778</v>
+        <v>418.813076645779</v>
       </c>
       <c r="X24" t="n">
         <v>439.753730478068</v>
@@ -5232,7 +5232,7 @@
         <v>0.0407080097768207</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0170802838224423</v>
+        <v>0.0170802838224422</v>
       </c>
       <c r="S25" t="n">
         <v>32107.006769328</v>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>623.464537168054</v>
+        <v>623.464537168055</v>
       </c>
       <c r="Z26" t="n">
         <v>1457.34835563033</v>
@@ -5413,7 +5413,7 @@
         <v>0.877511035764174</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0535410338166088</v>
+        <v>0.0535410338166087</v>
       </c>
       <c r="L27" t="n">
         <v>0.112268855284201</v>
@@ -5440,7 +5440,7 @@
         <v>58192.3668105718</v>
       </c>
       <c r="T27" t="n">
-        <v>2788.41704116899</v>
+        <v>2788.41704116898</v>
       </c>
       <c r="U27" t="n">
         <v>5846.96198320121</v>
@@ -5449,7 +5449,7 @@
         <v>2668.51510839872</v>
       </c>
       <c r="W27" t="n">
-        <v>968.608024827119</v>
+        <v>968.60802482712</v>
       </c>
       <c r="X27" t="n">
         <v>219.089910377563</v>
@@ -5719,7 +5719,7 @@
         <v>0.019730928027163</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0487400900670992</v>
+        <v>0.048740090067099</v>
       </c>
       <c r="M30" t="n">
         <v>0.0369954900509306</v>
@@ -5746,7 +5746,7 @@
         <v>882.130330238403</v>
       </c>
       <c r="U30" t="n">
-        <v>2179.07194671987</v>
+        <v>2179.07194671986</v>
       </c>
       <c r="V30" t="n">
         <v>1653.994369197</v>
@@ -5820,7 +5820,7 @@
         <v>0.0433410895687032</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0473695882786146</v>
+        <v>0.0473695882786147</v>
       </c>
       <c r="M31" t="n">
         <v>0.0476751985255735</v>
@@ -5832,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00764025617397011</v>
+        <v>0.00764025617397012</v>
       </c>
       <c r="Q31" t="n">
         <v>0.0531237926427819</v>
@@ -5847,16 +5847,16 @@
         <v>2020.30154915553</v>
       </c>
       <c r="U31" t="n">
-        <v>2208.08598801934</v>
+        <v>2208.08598801935</v>
       </c>
       <c r="V31" t="n">
         <v>2222.33170407108</v>
       </c>
       <c r="W31" t="n">
-        <v>253.980766179552</v>
+        <v>253.980766179553</v>
       </c>
       <c r="X31" t="n">
-        <v>356.142901293442</v>
+        <v>356.142901293443</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
         <v>0.0162069760475615</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.0725292642369069</v>
+        <v>0.072529264236907</v>
       </c>
       <c r="R32" t="n">
         <v>0.0243104640713423</v>
@@ -5948,7 +5948,7 @@
         <v>951.830638593275</v>
       </c>
       <c r="U32" t="n">
-        <v>717.321640678989</v>
+        <v>717.32164067899</v>
       </c>
       <c r="V32" t="n">
         <v>2308.43978033569</v>
@@ -6126,10 +6126,10 @@
         <v>0.0651698559002442</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0238972733629619</v>
+        <v>0.023897273362962</v>
       </c>
       <c r="N34" t="n">
-        <v>0.00442329338689441</v>
+        <v>0.0044232933868944</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -6138,7 +6138,7 @@
         <v>0.00634513809982093</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.0283205667498563</v>
+        <v>0.0283205667498564</v>
       </c>
       <c r="R34" t="n">
         <v>0.0143757035074068</v>
@@ -6236,10 +6236,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.00472885090166909</v>
+        <v>0.0047288509016691</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0472885090166909</v>
+        <v>0.047288509016691</v>
       </c>
       <c r="R35" t="n">
         <v>0.0496529344675255</v>
@@ -6325,10 +6325,10 @@
         <v>0.0237970250064996</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0999035474664131</v>
+        <v>0.0999035474664132</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0535873748294508</v>
+        <v>0.053587374829451</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00751485000205253</v>
+        <v>0.00751485000205251</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0535873748294508</v>
+        <v>0.053587374829451</v>
       </c>
       <c r="R36" t="n">
         <v>0.0888422266909319</v>
@@ -6352,16 +6352,16 @@
         <v>894.220808669236</v>
       </c>
       <c r="U36" t="n">
-        <v>3754.0756031454</v>
+        <v>3754.07560314541</v>
       </c>
       <c r="V36" t="n">
-        <v>2013.65278396627</v>
+        <v>2013.65278396628</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>282.385518527128</v>
+        <v>282.385518527127</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -6423,13 +6423,13 @@
         <v>0.340754863979278</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0322872635908059</v>
+        <v>0.032287263590806</v>
       </c>
       <c r="L37" t="n">
         <v>0.023227491059792</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0588089443975395</v>
+        <v>0.0588089443975394</v>
       </c>
       <c r="N37" t="n">
         <v>0.00731844641391602</v>
@@ -6441,7 +6441,7 @@
         <v>0.0103955204743125</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0661273908114555</v>
+        <v>0.0661273908114554</v>
       </c>
       <c r="R37" t="n">
         <v>0.0102915652695694</v>
@@ -6456,7 +6456,7 @@
         <v>1060.05623698679</v>
       </c>
       <c r="V37" t="n">
-        <v>2683.92260441491</v>
+        <v>2683.9226044149</v>
       </c>
       <c r="W37" t="n">
         <v>333.999257438299</v>
@@ -6646,7 +6646,7 @@
         <v>0.0696824337684967</v>
       </c>
       <c r="R39" t="n">
-        <v>0.0163958667690581</v>
+        <v>0.016395866769058</v>
       </c>
       <c r="S39" t="n">
         <v>22874.4495655112</v>
@@ -6741,13 +6741,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0096287970497336</v>
+        <v>0.00962879704973359</v>
       </c>
       <c r="Q40" t="n">
         <v>0.0556419420162267</v>
       </c>
       <c r="R40" t="n">
-        <v>0.00756298240997257</v>
+        <v>0.00756298240997256</v>
       </c>
       <c r="S40" t="n">
         <v>25562.8652371981</v>
@@ -6762,10 +6762,10 @@
         <v>1707.22983431516</v>
       </c>
       <c r="W40" t="n">
-        <v>804.836921891432</v>
+        <v>804.836921891431</v>
       </c>
       <c r="X40" t="n">
-        <v>434.711300404323</v>
+        <v>434.711300404322</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -6830,10 +6830,10 @@
         <v>0.0389165913983441</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0626543974016247</v>
+        <v>0.0626543974016246</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0526119195202294</v>
+        <v>0.0526119195202295</v>
       </c>
       <c r="N41" t="n">
         <v>0.0104777975315711</v>
@@ -6863,7 +6863,7 @@
         <v>1862.56717485516</v>
       </c>
       <c r="W41" t="n">
-        <v>370.934988212682</v>
+        <v>370.934988212681</v>
       </c>
       <c r="X41" t="n">
         <v>364.752738409136</v>
@@ -6955,7 +6955,7 @@
         <v>21654.6407392462</v>
       </c>
       <c r="T42" t="n">
-        <v>1154.2047935274</v>
+        <v>1154.20479352741</v>
       </c>
       <c r="U42" t="n">
         <v>3080.28404272626</v>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>559.345399940205</v>
+        <v>559.345399940204</v>
       </c>
       <c r="AA42" t="n">
         <v>0.00457142857142857</v>
@@ -7038,7 +7038,7 @@
         <v>0.0202451616966562</v>
       </c>
       <c r="N43" t="n">
-        <v>0.00819447021055133</v>
+        <v>0.00819447021055132</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
         <v>0.0083651883399378</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0284396319072076</v>
+        <v>0.0284396319072075</v>
       </c>
       <c r="R43" t="n">
         <v>0.00956021524564321</v>
@@ -7056,7 +7056,7 @@
         <v>35230.0886853985</v>
       </c>
       <c r="T43" t="n">
-        <v>1113.87005102994</v>
+        <v>1113.87005102993</v>
       </c>
       <c r="U43" t="n">
         <v>2117.81871544507</v>
@@ -7065,7 +7065,7 @@
         <v>1266.29437380245</v>
       </c>
       <c r="W43" t="n">
-        <v>512.547722729565</v>
+        <v>512.547722729564</v>
       </c>
       <c r="X43" t="n">
         <v>523.22580028643</v>
@@ -7139,16 +7139,16 @@
         <v>0.0337456724862801</v>
       </c>
       <c r="N44" t="n">
-        <v>0.00957149983247217</v>
+        <v>0.00957149983247218</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.00759277630941302</v>
+        <v>0.00759277630941303</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.0433171723187522</v>
+        <v>0.0433171723187523</v>
       </c>
       <c r="R44" t="n">
         <v>0.0867745863932917</v>
@@ -7166,7 +7166,7 @@
         <v>2474.367689384</v>
       </c>
       <c r="W44" t="n">
-        <v>701.820653716189</v>
+        <v>701.82065371619</v>
       </c>
       <c r="X44" t="n">
         <v>556.732730111401</v>
@@ -7225,7 +7225,7 @@
         <v>43839.1237380792</v>
       </c>
       <c r="I45" t="n">
-        <v>0.792774000647535</v>
+        <v>0.792774000647534</v>
       </c>
       <c r="J45" t="n">
         <v>0.661862487742001</v>
@@ -7246,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.00725250320515061</v>
+        <v>0.0072525032051506</v>
       </c>
       <c r="Q45" t="n">
         <v>0.0275413809215594</v>
@@ -7270,7 +7270,7 @@
         <v>353.076949687821</v>
       </c>
       <c r="X45" t="n">
-        <v>480.376802296356</v>
+        <v>480.376802296355</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -7341,13 +7341,13 @@
         <v>0.0458526855871269</v>
       </c>
       <c r="N46" t="n">
-        <v>0.00764211426452112</v>
+        <v>0.00764211426452114</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.00636842855376761</v>
+        <v>0.00636842855376762</v>
       </c>
       <c r="Q46" t="n">
         <v>0.053494799851648</v>
@@ -7368,7 +7368,7 @@
         <v>2125.86806187596</v>
       </c>
       <c r="W46" t="n">
-        <v>354.311343645993</v>
+        <v>354.311343645994</v>
       </c>
       <c r="X46" t="n">
         <v>295.259453038328</v>
@@ -7472,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>153.04792479571</v>
+        <v>153.047924795711</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -7549,13 +7549,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.00558360707055045</v>
+        <v>0.00558360707055046</v>
       </c>
       <c r="Q48" t="n">
         <v>0.0291743469436261</v>
       </c>
       <c r="R48" t="n">
-        <v>0.00736725932919851</v>
+        <v>0.00736725932919852</v>
       </c>
       <c r="S48" t="n">
         <v>42896.4157523606</v>
@@ -7573,7 +7573,7 @@
         <v>88.1118321964679</v>
       </c>
       <c r="X48" t="n">
-        <v>370.997188195654</v>
+        <v>370.997188195655</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
@@ -7650,19 +7650,19 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.00303405221121696</v>
+        <v>0.00303405221121697</v>
       </c>
       <c r="Q49" t="n">
         <v>0.059732902908334</v>
       </c>
       <c r="R49" t="n">
-        <v>0.138866235821085</v>
+        <v>0.138866235821084</v>
       </c>
       <c r="S49" t="n">
         <v>57084.3120352503</v>
       </c>
       <c r="T49" t="n">
-        <v>2308.13174853798</v>
+        <v>2308.13174853799</v>
       </c>
       <c r="U49" t="n">
         <v>10236.0625369945</v>
@@ -7680,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>8566.79695403854</v>
+        <v>8566.79695403851</v>
       </c>
       <c r="AA49" t="n">
         <v>0.00338235294117647</v>
@@ -7730,19 +7730,19 @@
         <v>12196.4769791729</v>
       </c>
       <c r="I50" t="n">
-        <v>0.592475672513803</v>
+        <v>0.592475672513802</v>
       </c>
       <c r="J50" t="n">
         <v>0.366337577844379</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0491728861059248</v>
+        <v>0.0491728861059249</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0760238699663971</v>
+        <v>0.076023869966397</v>
       </c>
       <c r="M50" t="n">
-        <v>0.082188966777046</v>
+        <v>0.0821889667770458</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0.0187523718200561</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.082188966777046</v>
+        <v>0.0821889667770458</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0491728861059248</v>
+        <v>0.0491728861059249</v>
       </c>
       <c r="S50" t="n">
         <v>19725.292565002</v>
@@ -7766,7 +7766,7 @@
         <v>1637.11289712456</v>
       </c>
       <c r="U50" t="n">
-        <v>2531.06270279126</v>
+        <v>2531.06270279125</v>
       </c>
       <c r="V50" t="n">
         <v>2736.31727090819</v>
@@ -7870,13 +7870,13 @@
         <v>2151.56391970284</v>
       </c>
       <c r="V51" t="n">
-        <v>2445.41387575529</v>
+        <v>2445.41387575528</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>256.186215555315</v>
+        <v>256.186215555316</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -7941,13 +7941,13 @@
         <v>0.0229585818040506</v>
       </c>
       <c r="L52" t="n">
-        <v>0.114665361343563</v>
+        <v>0.114665361343564</v>
       </c>
       <c r="M52" t="n">
         <v>0.0340889022626543</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0223172806363396</v>
+        <v>0.0223172806363397</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7959,22 +7959,22 @@
         <v>0.0564061828989939</v>
       </c>
       <c r="R52" t="n">
-        <v>0.0798958646780959</v>
+        <v>0.079895864678096</v>
       </c>
       <c r="S52" t="n">
         <v>26029.2974128834</v>
       </c>
       <c r="T52" t="n">
-        <v>998.813101385221</v>
+        <v>998.81310138522</v>
       </c>
       <c r="U52" t="n">
-        <v>4988.51654525173</v>
+        <v>4988.51654525174</v>
       </c>
       <c r="V52" t="n">
         <v>1483.03769293677</v>
       </c>
       <c r="W52" t="n">
-        <v>970.913294083956</v>
+        <v>970.913294083957</v>
       </c>
       <c r="X52" t="n">
         <v>325.862774326928</v>
@@ -8048,7 +8048,7 @@
         <v>0.0364217677149153</v>
       </c>
       <c r="N53" t="n">
-        <v>0.00849841246681356</v>
+        <v>0.00849841246681358</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -8075,7 +8075,7 @@
         <v>1694.63200823958</v>
       </c>
       <c r="W53" t="n">
-        <v>395.414135255901</v>
+        <v>395.414135255902</v>
       </c>
       <c r="X53" t="n">
         <v>153.51372309935</v>
@@ -8149,7 +8149,7 @@
         <v>0.0270556606809704</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0161599421261905</v>
+        <v>0.0161599421261904</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
         <v>0.00320954406117394</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.0432156028071609</v>
+        <v>0.0432156028071608</v>
       </c>
       <c r="R54" t="n">
         <v>0.0477452835546536</v>
@@ -8277,7 +8277,7 @@
         <v>1613.32483839633</v>
       </c>
       <c r="W55" t="n">
-        <v>921.899907655045</v>
+        <v>921.899907655044</v>
       </c>
       <c r="X55" t="n">
         <v>259.284349027981</v>
@@ -8286,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>436.689429941864</v>
+        <v>436.689429941863</v>
       </c>
       <c r="AA55" t="n">
         <v>0.005</v>
@@ -8369,7 +8369,7 @@
         <v>27043.007006791</v>
       </c>
       <c r="T56" t="n">
-        <v>2197.79012952046</v>
+        <v>2197.79012952045</v>
       </c>
       <c r="U56" t="n">
         <v>2447.46931051365</v>
@@ -8458,19 +8458,19 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.00878738582867637</v>
+        <v>0.00878738582867634</v>
       </c>
       <c r="Q57" t="n">
         <v>0.064707113829344</v>
       </c>
       <c r="R57" t="n">
-        <v>0.00602563599680665</v>
+        <v>0.00602563599680664</v>
       </c>
       <c r="S57" t="n">
         <v>20332.3362092889</v>
       </c>
       <c r="T57" t="n">
-        <v>1930.74558416427</v>
+        <v>1930.74558416428</v>
       </c>
       <c r="U57" t="n">
         <v>1579.70093249804</v>
@@ -8482,13 +8482,13 @@
         <v>151.651289519812</v>
       </c>
       <c r="X57" t="n">
-        <v>360.405842377333</v>
+        <v>360.405842377331</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>247.135434773028</v>
+        <v>247.135434773027</v>
       </c>
       <c r="AA57" t="n">
         <v>0.00833333333333333</v>
@@ -8562,7 +8562,7 @@
         <v>0.00975706973751196</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.0514878464206116</v>
+        <v>0.0514878464206117</v>
       </c>
       <c r="R58" t="n">
         <v>0.0146356046062679</v>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>721.535307089007</v>
+        <v>721.535307089009</v>
       </c>
       <c r="AA58" t="n">
         <v>0.0024</v>
@@ -8633,7 +8633,7 @@
         <v>43042</v>
       </c>
       <c r="G59" t="n">
-        <v>313297.728316803</v>
+        <v>313297.728316804</v>
       </c>
       <c r="H59" t="n">
         <v>18672.8558970101</v>
@@ -8648,7 +8648,7 @@
         <v>0.0377423618656304</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0463201713805463</v>
+        <v>0.0463201713805464</v>
       </c>
       <c r="M59" t="n">
         <v>0.0344789245614593</v>
@@ -8684,7 +8684,7 @@
         <v>864.701730154378</v>
       </c>
       <c r="X59" t="n">
-        <v>615.602553885648</v>
+        <v>615.602553885649</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -8740,7 +8740,7 @@
         <v>14530.8075636579</v>
       </c>
       <c r="I60" t="n">
-        <v>0.561443024817728</v>
+        <v>0.561443024817727</v>
       </c>
       <c r="J60" t="n">
         <v>0.360440729365924</v>
@@ -8749,7 +8749,7 @@
         <v>0.0362890963396221</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0893481538664939</v>
+        <v>0.0893481538664937</v>
       </c>
       <c r="M60" t="n">
         <v>0.0420953517539616</v>
@@ -8850,7 +8850,7 @@
         <v>0.0208351583547888</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0662811585228399</v>
+        <v>0.0662811585228401</v>
       </c>
       <c r="M61" t="n">
         <v>0.0502341411962577</v>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.00941270890265186</v>
+        <v>0.00941270890265185</v>
       </c>
       <c r="Q61" t="n">
         <v>0.0502341411962577</v>
@@ -8874,10 +8874,10 @@
         <v>24405.9429714436</v>
       </c>
       <c r="T61" t="n">
-        <v>994.337097323943</v>
+        <v>994.337097323942</v>
       </c>
       <c r="U61" t="n">
-        <v>3163.20200934401</v>
+        <v>3163.20200934402</v>
       </c>
       <c r="V61" t="n">
         <v>2397.3741544502</v>
@@ -8969,7 +8969,7 @@
         <v>0.0689394838041205</v>
       </c>
       <c r="R62" t="n">
-        <v>0.00675325555632201</v>
+        <v>0.006753255556322</v>
       </c>
       <c r="S62" t="n">
         <v>23254.1631573265</v>
@@ -9055,10 +9055,10 @@
         <v>0.0208179498149751</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0512441841599385</v>
+        <v>0.0512441841599387</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0097665386281295</v>
+        <v>0.00976653862812949</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9067,7 +9067,7 @@
         <v>0.0138359297231834</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.061010722788068</v>
+        <v>0.0610107227880681</v>
       </c>
       <c r="R63" t="n">
         <v>0.0291282731014388</v>
@@ -9079,13 +9079,13 @@
         <v>879.058638447086</v>
       </c>
       <c r="U63" t="n">
-        <v>828.512766736379</v>
+        <v>828.512766736378</v>
       </c>
       <c r="V63" t="n">
-        <v>2039.41604119723</v>
+        <v>2039.41604119724</v>
       </c>
       <c r="W63" t="n">
-        <v>388.688704322298</v>
+        <v>388.688704322297</v>
       </c>
       <c r="X63" t="n">
         <v>550.642331123254</v>
@@ -9165,13 +9165,13 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0078164650650394</v>
+        <v>0.00781646506503937</v>
       </c>
       <c r="Q64" t="n">
         <v>0.0381052671920669</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0150746111968617</v>
+        <v>0.0150746111968616</v>
       </c>
       <c r="S64" t="n">
         <v>32630.314892487</v>
@@ -9189,13 +9189,13 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>466.525717406876</v>
+        <v>466.525717406875</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>899.728169284688</v>
+        <v>899.728169284687</v>
       </c>
       <c r="AA64" t="n">
         <v>0.00483870967741936</v>
@@ -9254,13 +9254,13 @@
         <v>0.0220797520445127</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0408475412823485</v>
+        <v>0.0408475412823484</v>
       </c>
       <c r="M65" t="n">
         <v>0.0317948429440982</v>
       </c>
       <c r="N65" t="n">
-        <v>0.00585694475286021</v>
+        <v>0.0058569447528602</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9358,7 +9358,7 @@
         <v>0.059635907744563</v>
       </c>
       <c r="M66" t="n">
-        <v>0.0395427674793716</v>
+        <v>0.0395427674793717</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>0.000686506379850202</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.0395427674793716</v>
+        <v>0.0395427674793717</v>
       </c>
       <c r="R66" t="n">
         <v>0.0211836254353777</v>
@@ -9563,7 +9563,7 @@
         <v>0.043329253096049</v>
       </c>
       <c r="N68" t="n">
-        <v>0.00984755752182933</v>
+        <v>0.00984755752182932</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9572,7 +9572,7 @@
         <v>0.0100299196981595</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.0531768106178784</v>
+        <v>0.0531768106178783</v>
       </c>
       <c r="R68" t="n">
         <v>0.00722154218267484</v>
@@ -9593,7 +9593,7 @@
         <v>507.868084073304</v>
       </c>
       <c r="X68" t="n">
-        <v>517.273048593178</v>
+        <v>517.27304859318</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.007620225497953</v>
+        <v>0.00762022549795301</v>
       </c>
       <c r="Q69" t="n">
         <v>0.0440449033781684</v>
@@ -9694,7 +9694,7 @@
         <v>917.720865213327</v>
       </c>
       <c r="X69" t="n">
-        <v>427.471789758669</v>
+        <v>427.47178975867</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.00497137395203725</v>
+        <v>0.00497137395203726</v>
       </c>
       <c r="Q70" t="n">
         <v>0.0402036852750865</v>
@@ -9979,7 +9979,7 @@
         <v>0.0423276360923981</v>
       </c>
       <c r="R72" t="n">
-        <v>0.00678327501480739</v>
+        <v>0.0067832750148074</v>
       </c>
       <c r="S72" t="n">
         <v>23004.4288227398</v>
@@ -10080,7 +10080,7 @@
         <v>0.0594881563304004</v>
       </c>
       <c r="R73" t="n">
-        <v>0.0343843246432459</v>
+        <v>0.0343843246432458</v>
       </c>
       <c r="S73" t="n">
         <v>22790.1615752995</v>
@@ -10181,7 +10181,7 @@
         <v>0.0478345648393837</v>
       </c>
       <c r="R74" t="n">
-        <v>0.00542910529014483</v>
+        <v>0.00542910529014482</v>
       </c>
       <c r="S74" t="n">
         <v>24071.9739960859</v>
@@ -10368,7 +10368,7 @@
         <v>0.104808005346473</v>
       </c>
       <c r="M76" t="n">
-        <v>0.0631263581497835</v>
+        <v>0.0631263581497834</v>
       </c>
       <c r="N76" t="n">
         <v>0.0103640289499644</v>
@@ -10392,7 +10392,7 @@
         <v>1901.55233326601</v>
       </c>
       <c r="U76" t="n">
-        <v>3926.31749628956</v>
+        <v>3926.31749628957</v>
       </c>
       <c r="V76" t="n">
         <v>2364.83962900719</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>445.941187184213</v>
+        <v>445.941187184212</v>
       </c>
       <c r="AA76" t="n">
         <v>0.00614035087719298</v>
@@ -10463,7 +10463,7 @@
         <v>0.422528694882118</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0316501297248133</v>
+        <v>0.0316501297248134</v>
       </c>
       <c r="L77" t="n">
         <v>0.0310171271303171</v>
@@ -10481,7 +10481,7 @@
         <v>0.00395700226513016</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.0285825332377903</v>
+        <v>0.0285825332377902</v>
       </c>
       <c r="R77" t="n">
         <v>0.00935831035703282</v>
@@ -10561,7 +10561,7 @@
         <v>0.573539918013263</v>
       </c>
       <c r="J78" t="n">
-        <v>0.409614507756028</v>
+        <v>0.409614507756029</v>
       </c>
       <c r="K78" t="n">
         <v>0.0419258005533881</v>
@@ -10600,7 +10600,7 @@
         <v>2423.48309903728</v>
       </c>
       <c r="W78" t="n">
-        <v>517.009727794619</v>
+        <v>517.00972779462</v>
       </c>
       <c r="X78" t="n">
         <v>298.274842958434</v>
@@ -10686,7 +10686,7 @@
         <v>0.0503283903987278</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0119960820950393</v>
+        <v>0.0119960820950392</v>
       </c>
       <c r="S79" t="n">
         <v>20089.4706555962</v>
@@ -10704,13 +10704,13 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>438.221877299322</v>
+        <v>438.221877299323</v>
       </c>
       <c r="Y79" t="n">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>504.255310864975</v>
+        <v>504.255310864974</v>
       </c>
       <c r="AA79" t="n">
         <v>0.0045</v>
@@ -10781,7 +10781,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0064247182135352</v>
+        <v>0.00642471821353519</v>
       </c>
       <c r="Q80" t="n">
         <v>0.053374582081677</v>
@@ -10805,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>290.03105431362</v>
+        <v>290.031054313619</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.00699205530056003</v>
+        <v>0.00699205530056004</v>
       </c>
       <c r="Q81" t="n">
         <v>0.0595768711968371</v>
@@ -10903,7 +10903,7 @@
         <v>2318.0367634836</v>
       </c>
       <c r="W81" t="n">
-        <v>575.909754902758</v>
+        <v>575.909754902759</v>
       </c>
       <c r="X81" t="n">
         <v>339.639086224704</v>
@@ -10912,7 +10912,7 @@
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>681.775518671649</v>
+        <v>681.775518671648</v>
       </c>
       <c r="AA81" t="n">
         <v>0.00556521739130435</v>
@@ -10962,7 +10962,7 @@
         <v>19920.4891669277</v>
       </c>
       <c r="I82" t="n">
-        <v>0.557089770658451</v>
+        <v>0.55708977065845</v>
       </c>
       <c r="J82" t="n">
         <v>0.382534597540619</v>
@@ -10971,7 +10971,7 @@
         <v>0.0240700967715567</v>
       </c>
       <c r="L82" t="n">
-        <v>0.0849532827231414</v>
+        <v>0.0849532827231411</v>
       </c>
       <c r="M82" t="n">
         <v>0.0385121548344907</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.00990312552886901</v>
+        <v>0.00990312552886903</v>
       </c>
       <c r="Q82" t="n">
         <v>0.0556286680942643</v>
@@ -10998,16 +10998,16 @@
         <v>1253.45028937881</v>
       </c>
       <c r="U82" t="n">
-        <v>4423.94219780759</v>
+        <v>4423.94219780758</v>
       </c>
       <c r="V82" t="n">
         <v>2005.5204630061</v>
       </c>
       <c r="W82" t="n">
-        <v>891.342428002713</v>
+        <v>891.342428002711</v>
       </c>
       <c r="X82" t="n">
-        <v>515.705261915854</v>
+        <v>515.705261915855</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
@@ -11072,10 +11072,10 @@
         <v>0.036951089985753</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0502567779070441</v>
+        <v>0.0502567779070442</v>
       </c>
       <c r="M83" t="n">
-        <v>0.0483860820273798</v>
+        <v>0.0483860820273799</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -11087,10 +11087,10 @@
         <v>0.0128525530385228</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.0483860820273798</v>
+        <v>0.0483860820273799</v>
       </c>
       <c r="R83" t="n">
-        <v>0.00725791230410696</v>
+        <v>0.00725791230410698</v>
       </c>
       <c r="S83" t="n">
         <v>21249.6852934968</v>
@@ -11099,7 +11099,7 @@
         <v>1944.58806159024</v>
       </c>
       <c r="U83" t="n">
-        <v>2644.8131941361</v>
+        <v>2644.81319413611</v>
       </c>
       <c r="V83" t="n">
         <v>2546.36595277289</v>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>381.954892915933</v>
+        <v>381.954892915934</v>
       </c>
       <c r="AA83" t="n">
         <v>0.008625</v>
@@ -11158,7 +11158,7 @@
         <v>37368</v>
       </c>
       <c r="G84" t="n">
-        <v>565555.229852956</v>
+        <v>565555.229852957</v>
       </c>
       <c r="H84" t="n">
         <v>33705.8603959869</v>
@@ -11200,7 +11200,7 @@
         <v>1170.11426866129</v>
       </c>
       <c r="U84" t="n">
-        <v>5002.98857177616</v>
+        <v>5002.98857177615</v>
       </c>
       <c r="V84" t="n">
         <v>1566.15294420819</v>
@@ -11209,7 +11209,7 @@
         <v>462.727006243328</v>
       </c>
       <c r="X84" t="n">
-        <v>565.555229852956</v>
+        <v>565.555229852957</v>
       </c>
       <c r="Y84" t="n">
         <v>0</v>
@@ -11372,7 +11372,7 @@
         <v>0.22345776579208</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0173038392018886</v>
+        <v>0.0173038392018885</v>
       </c>
       <c r="L86" t="n">
         <v>0.0303682377993144</v>
@@ -11399,7 +11399,7 @@
         <v>13777.8794102393</v>
       </c>
       <c r="T86" t="n">
-        <v>784.988665393675</v>
+        <v>784.988665393674</v>
       </c>
       <c r="U86" t="n">
         <v>1377.6551077659</v>
@@ -11476,7 +11476,7 @@
         <v>0.0404860460049322</v>
       </c>
       <c r="L87" t="n">
-        <v>0.078840188941547</v>
+        <v>0.0788401889415471</v>
       </c>
       <c r="M87" t="n">
         <v>0.0392591961259949</v>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>676.385983001277</v>
+        <v>676.385983001276</v>
       </c>
       <c r="AA87" t="n">
         <v>0.006875</v>
@@ -11595,7 +11595,7 @@
         <v>0.0437699375851426</v>
       </c>
       <c r="R88" t="n">
-        <v>0.00954980456403114</v>
+        <v>0.00954980456403112</v>
       </c>
       <c r="S88" t="n">
         <v>19991.7139145996</v>
@@ -11619,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>437.552945514779</v>
+        <v>437.552945514778</v>
       </c>
       <c r="AA88" t="n">
         <v>0.005</v>
@@ -11678,10 +11678,10 @@
         <v>0.0254049332913834</v>
       </c>
       <c r="L89" t="n">
-        <v>0.0502357437965208</v>
+        <v>0.0502357437965209</v>
       </c>
       <c r="M89" t="n">
-        <v>0.0376369382094568</v>
+        <v>0.0376369382094569</v>
       </c>
       <c r="N89" t="n">
         <v>0.00423415554856391</v>
@@ -11693,13 +11693,13 @@
         <v>0.00589099902408891</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.0418710937580207</v>
+        <v>0.0418710937580208</v>
       </c>
       <c r="R89" t="n">
         <v>0.0120438202270262</v>
       </c>
       <c r="S89" t="n">
-        <v>10147.5971381844</v>
+        <v>10147.5971381845</v>
       </c>
       <c r="T89" t="n">
         <v>884.015463740269</v>
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>419.088812439832</v>
+        <v>419.088812439831</v>
       </c>
       <c r="AA89" t="n">
         <v>0.009</v>
@@ -11791,7 +11791,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.00607265248864337</v>
+        <v>0.00607265248864338</v>
       </c>
       <c r="Q90" t="n">
         <v>0.0510102809046044</v>
@@ -11800,7 +11800,7 @@
         <v>0.0130795592063088</v>
       </c>
       <c r="S90" t="n">
-        <v>29132.6054185406</v>
+        <v>29132.6054185405</v>
       </c>
       <c r="T90" t="n">
         <v>2509.75305224811</v>
@@ -11821,7 +11821,7 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>695.008537545633</v>
+        <v>695.008537545631</v>
       </c>
       <c r="AA90" t="n">
         <v>0.00666666666666667</v>
@@ -11877,7 +11877,7 @@
         <v>0.273146490759587</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0339534106396953</v>
+        <v>0.0339534106396952</v>
       </c>
       <c r="L91" t="n">
         <v>0.0789958607117165</v>
@@ -11907,7 +11907,7 @@
         <v>1435.34648138248</v>
       </c>
       <c r="U91" t="n">
-        <v>3339.47101572711</v>
+        <v>3339.4710157271</v>
       </c>
       <c r="V91" t="n">
         <v>1660.90092845687</v>
@@ -11922,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>664.360371382747</v>
+        <v>664.360371382746</v>
       </c>
       <c r="AA91" t="n">
         <v>0.00740740740740741</v>
@@ -11993,7 +11993,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.00723836324337973</v>
+        <v>0.00723836324337975</v>
       </c>
       <c r="Q92" t="n">
         <v>0.0738313050824735</v>
@@ -12008,7 +12008,7 @@
         <v>1537.69743117965</v>
       </c>
       <c r="U92" t="n">
-        <v>638.57157211488</v>
+        <v>638.571572114881</v>
       </c>
       <c r="V92" t="n">
         <v>2829.36327337055</v>
@@ -12017,7 +12017,7 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>277.388556212798</v>
+        <v>277.388556212799</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -12073,7 +12073,7 @@
         <v>7402.5787305848</v>
       </c>
       <c r="I93" t="n">
-        <v>0.359575590900045</v>
+        <v>0.359575590900044</v>
       </c>
       <c r="J93" t="n">
         <v>0.205770082851558</v>
@@ -12085,7 +12085,7 @@
         <v>0.0664725643795244</v>
       </c>
       <c r="M93" t="n">
-        <v>0.0503168947436846</v>
+        <v>0.0503168947436845</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
@@ -12094,13 +12094,13 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.00895944707677688</v>
+        <v>0.0089594470767769</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.0503168947436846</v>
+        <v>0.0503168947436845</v>
       </c>
       <c r="R93" t="n">
-        <v>0.0392565246916673</v>
+        <v>0.0392565246916672</v>
       </c>
       <c r="S93" t="n">
         <v>12935.7318826291</v>
@@ -12118,7 +12118,7 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>322.316108587048</v>
+        <v>322.316108587049</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12287,19 +12287,19 @@
         <v>0.040640580735938</v>
       </c>
       <c r="M95" t="n">
-        <v>0.0227696721698993</v>
+        <v>0.0227696721698992</v>
       </c>
       <c r="N95" t="n">
-        <v>0.00240833071027781</v>
+        <v>0.0024083307102778</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.00695739982969144</v>
+        <v>0.00695739982969143</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0251780028801771</v>
+        <v>0.025178002880177</v>
       </c>
       <c r="R95" t="n">
         <v>0.0157636191945456</v>
@@ -12314,7 +12314,7 @@
         <v>2947.25491497022</v>
       </c>
       <c r="V95" t="n">
-        <v>1651.2566257611</v>
+        <v>1651.25662576109</v>
       </c>
       <c r="W95" t="n">
         <v>174.652143109346</v>
@@ -12382,7 +12382,7 @@
         <v>0.340417586884334</v>
       </c>
       <c r="K96" t="n">
-        <v>0.0311565522816338</v>
+        <v>0.0311565522816339</v>
       </c>
       <c r="L96" t="n">
         <v>0.0856805187744931</v>
@@ -12409,7 +12409,7 @@
         <v>26171.2696319131</v>
       </c>
       <c r="T96" t="n">
-        <v>1619.08139586738</v>
+        <v>1619.08139586739</v>
       </c>
       <c r="U96" t="n">
         <v>4452.47383863531</v>
@@ -12483,7 +12483,7 @@
         <v>0.35448800576654</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0254923870550919</v>
+        <v>0.0254923870550918</v>
       </c>
       <c r="L97" t="n">
         <v>0.0743527955773512</v>
@@ -12519,7 +12519,7 @@
         <v>1725.49878391758</v>
       </c>
       <c r="W97" t="n">
-        <v>739.499478821819</v>
+        <v>739.49947882182</v>
       </c>
       <c r="X97" t="n">
         <v>505.517221850853</v>
@@ -12599,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.00592957637536369</v>
+        <v>0.00592957637536372</v>
       </c>
       <c r="Q98" t="n">
         <v>0.0690677056202366</v>
@@ -12614,7 +12614,7 @@
         <v>1431.73276138392</v>
       </c>
       <c r="U98" t="n">
-        <v>574.184492846677</v>
+        <v>574.184492846678</v>
       </c>
       <c r="V98" t="n">
         <v>2619.11646482499</v>
@@ -12700,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.00331693412648053</v>
+        <v>0.00331693412648054</v>
       </c>
       <c r="Q99" t="n">
         <v>0.0576091581881426</v>
@@ -12721,7 +12721,7 @@
         <v>2229.70614156862</v>
       </c>
       <c r="W99" t="n">
-        <v>638.884281251754</v>
+        <v>638.884281251753</v>
       </c>
       <c r="X99" t="n">
         <v>165.163417893972</v>
@@ -12789,7 +12789,7 @@
         <v>0.0476411933761424</v>
       </c>
       <c r="L100" t="n">
-        <v>0.0852403705014315</v>
+        <v>0.0852403705014313</v>
       </c>
       <c r="M100" t="n">
         <v>0.0509531479958742</v>
@@ -12807,19 +12807,19 @@
         <v>0.0719713215441724</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0312270007003287</v>
+        <v>0.0312270007003286</v>
       </c>
       <c r="S100" t="n">
-        <v>24880.2731025902</v>
+        <v>24880.2731025901</v>
       </c>
       <c r="T100" t="n">
         <v>1888.2586994634</v>
       </c>
       <c r="U100" t="n">
-        <v>3378.50208482424</v>
+        <v>3378.50208482423</v>
       </c>
       <c r="V100" t="n">
-        <v>2019.52802081647</v>
+        <v>2019.52802081648</v>
       </c>
       <c r="W100" t="n">
         <v>833.055308586796</v>
@@ -12893,7 +12893,7 @@
         <v>0.0663183374266767</v>
       </c>
       <c r="M101" t="n">
-        <v>0.0425430029599798</v>
+        <v>0.0425430029599797</v>
       </c>
       <c r="N101" t="n">
         <v>0.0194102451004908</v>
@@ -12926,7 +12926,7 @@
         <v>786.037285589474</v>
       </c>
       <c r="X101" t="n">
-        <v>74.8606938656642</v>
+        <v>74.8606938656641</v>
       </c>
       <c r="Y101" t="n">
         <v>0</v>
@@ -12988,10 +12988,10 @@
         <v>0.465472569673073</v>
       </c>
       <c r="K102" t="n">
-        <v>0.0260330477156286</v>
+        <v>0.0260330477156287</v>
       </c>
       <c r="L102" t="n">
-        <v>0.0542355160742263</v>
+        <v>0.0542355160742264</v>
       </c>
       <c r="M102" t="n">
         <v>0.0327272599853617</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0.00446280817982205</v>
+        <v>0.00446280817982206</v>
       </c>
       <c r="Q102" t="n">
         <v>0.0389751914371126</v>
@@ -13092,10 +13092,10 @@
         <v>0.0238819932461986</v>
       </c>
       <c r="L103" t="n">
-        <v>0.0384765446744312</v>
+        <v>0.0384765446744311</v>
       </c>
       <c r="M103" t="n">
-        <v>0.0592932246112517</v>
+        <v>0.0592932246112518</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
@@ -13107,7 +13107,7 @@
         <v>0.0111449301815594</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.0592932246112517</v>
+        <v>0.0592932246112518</v>
       </c>
       <c r="R103" t="n">
         <v>0.0119409966230993</v>
@@ -13119,10 +13119,10 @@
         <v>1347.42205895053</v>
       </c>
       <c r="U103" t="n">
-        <v>2170.84665053141</v>
+        <v>2170.8466505314</v>
       </c>
       <c r="V103" t="n">
-        <v>3345.32373256682</v>
+        <v>3345.32373256683</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
@@ -13217,7 +13217,7 @@
         <v>27447.5325467703</v>
       </c>
       <c r="T104" t="n">
-        <v>1409.56023450611</v>
+        <v>1409.56023450612</v>
       </c>
       <c r="U104" t="n">
         <v>4162.60756752587</v>
@@ -13294,7 +13294,7 @@
         <v>0.0288962827460898</v>
       </c>
       <c r="L105" t="n">
-        <v>0.0900230347089722</v>
+        <v>0.0900230347089719</v>
       </c>
       <c r="M105" t="n">
         <v>0.0491236806683526</v>
@@ -13321,7 +13321,7 @@
         <v>1289.95895806819</v>
       </c>
       <c r="U105" t="n">
-        <v>4018.71829244323</v>
+        <v>4018.71829244322</v>
       </c>
       <c r="V105" t="n">
         <v>2192.93022871593</v>
@@ -13597,7 +13597,7 @@
         <v>0.0267094552475684</v>
       </c>
       <c r="L108" t="n">
-        <v>0.0429028689363115</v>
+        <v>0.0429028689363116</v>
       </c>
       <c r="M108" t="n">
         <v>0.040598371976304</v>
@@ -13615,7 +13615,7 @@
         <v>0.0544073420362713</v>
       </c>
       <c r="R108" t="n">
-        <v>0.00497529068337059</v>
+        <v>0.00497529068337058</v>
       </c>
       <c r="S108" t="n">
         <v>21462.0763577821</v>
@@ -13630,7 +13630,7 @@
         <v>1894.03584781051</v>
       </c>
       <c r="W108" t="n">
-        <v>644.229880207655</v>
+        <v>644.229880207656</v>
       </c>
       <c r="X108" t="n">
         <v>0</v>
@@ -13701,7 +13701,7 @@
         <v>0.0761771827085379</v>
       </c>
       <c r="M109" t="n">
-        <v>0.0426345495450539</v>
+        <v>0.0426345495450538</v>
       </c>
       <c r="N109" t="n">
         <v>0.00675047034463351</v>
@@ -13713,7 +13713,7 @@
         <v>0.00300020904205934</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.0493850198896874</v>
+        <v>0.0493850198896873</v>
       </c>
       <c r="R109" t="n">
         <v>0.300020904205934</v>
@@ -13799,7 +13799,7 @@
         <v>0.038083317195058</v>
       </c>
       <c r="L110" t="n">
-        <v>0.095208292987645</v>
+        <v>0.0952082929876449</v>
       </c>
       <c r="M110" t="n">
         <v>0.0408035541375621</v>
@@ -13841,7 +13841,7 @@
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>500.431286131017</v>
+        <v>500.431286131016</v>
       </c>
       <c r="AA110" t="n">
         <v>0.006</v>
@@ -13903,7 +13903,7 @@
         <v>0.0161755322054065</v>
       </c>
       <c r="M111" t="n">
-        <v>0.0313180052111401</v>
+        <v>0.03131800521114</v>
       </c>
       <c r="N111" t="n">
         <v>0.010961301823899</v>
@@ -13915,10 +13915,10 @@
         <v>0.00608961212438834</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.0422793070350391</v>
+        <v>0.042279307035039</v>
       </c>
       <c r="R111" t="n">
-        <v>0.00794297233615869</v>
+        <v>0.0079429723361587</v>
       </c>
       <c r="S111" t="n">
         <v>13181.5987619719</v>
@@ -13992,7 +13992,7 @@
         <v>13281.8612475543</v>
       </c>
       <c r="I112" t="n">
-        <v>0.600818090776625</v>
+        <v>0.600818090776624</v>
       </c>
       <c r="J112" t="n">
         <v>0.386482606283953</v>
@@ -14001,7 +14001,7 @@
         <v>0.0281961014118964</v>
       </c>
       <c r="L112" t="n">
-        <v>0.0958667448004478</v>
+        <v>0.0958667448004476</v>
       </c>
       <c r="M112" t="n">
         <v>0.0498055935339737</v>
@@ -14028,7 +14028,7 @@
         <v>968.98722112123</v>
       </c>
       <c r="U112" t="n">
-        <v>3294.55655181219</v>
+        <v>3294.55655181218</v>
       </c>
       <c r="V112" t="n">
         <v>1711.61902738854</v>
@@ -14144,7 +14144,7 @@
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>494.154578589219</v>
+        <v>494.154578589218</v>
       </c>
       <c r="AA113" t="n">
         <v>0.00226086956521739</v>
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>538.892727776395</v>
+        <v>538.892727776396</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
@@ -14313,7 +14313,7 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>0.00884570819198086</v>
+        <v>0.00884570819198084</v>
       </c>
       <c r="P115" t="n">
         <v>0.00132095909000247</v>
@@ -14340,13 +14340,13 @@
         <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>81.8307737074732</v>
+        <v>81.8307737074731</v>
       </c>
       <c r="Y115" t="n">
-        <v>547.97393107683</v>
+        <v>547.973931076829</v>
       </c>
       <c r="Z115" t="n">
-        <v>6137.30802806048</v>
+        <v>6137.30802806049</v>
       </c>
       <c r="AA115" t="n">
         <v>0.00375</v>
@@ -14405,13 +14405,13 @@
         <v>0.0343676767991116</v>
       </c>
       <c r="L116" t="n">
-        <v>0.0750662414296382</v>
+        <v>0.0750662414296386</v>
       </c>
       <c r="M116" t="n">
         <v>0.041241212158934</v>
       </c>
       <c r="N116" t="n">
-        <v>0.00589160173699056</v>
+        <v>0.00589160173699057</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14432,7 +14432,7 @@
         <v>1627.92811462032</v>
       </c>
       <c r="U116" t="n">
-        <v>3555.7377240391</v>
+        <v>3555.73772403912</v>
       </c>
       <c r="V116" t="n">
         <v>1953.51373754438</v>
@@ -14542,7 +14542,7 @@
         <v>694.095756379373</v>
       </c>
       <c r="X117" t="n">
-        <v>443.45006657571</v>
+        <v>443.450066575711</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
@@ -14619,13 +14619,13 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>0.00761769097792632</v>
+        <v>0.00761769097792634</v>
       </c>
       <c r="Q118" t="n">
         <v>0.0579345445426504</v>
       </c>
       <c r="R118" t="n">
-        <v>0.00641736493395513</v>
+        <v>0.00641736493395512</v>
       </c>
       <c r="S118" t="n">
         <v>21712.5707187549</v>
@@ -14634,7 +14634,7 @@
         <v>1444.96380915487</v>
       </c>
       <c r="U118" t="n">
-        <v>1870.35748869994</v>
+        <v>1870.35748869993</v>
       </c>
       <c r="V118" t="n">
         <v>2594.36683916443</v>
@@ -14643,13 +14643,13 @@
         <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>341.127819682519</v>
+        <v>341.12781968252</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>287.376019107445</v>
+        <v>287.376019107444</v>
       </c>
       <c r="AA118" t="n">
         <v>0.00556962025316456</v>
@@ -14720,13 +14720,13 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>0.00955346131813525</v>
+        <v>0.00955346131813526</v>
       </c>
       <c r="Q119" t="n">
         <v>0.0532517010510873</v>
       </c>
       <c r="R119" t="n">
-        <v>0.00896288370937782</v>
+        <v>0.00896288370937781</v>
       </c>
       <c r="S119" t="n">
         <v>29049.6051095062</v>
@@ -14741,16 +14741,16 @@
         <v>2196.62353949431</v>
       </c>
       <c r="W119" t="n">
-        <v>650.851419109427</v>
+        <v>650.851419109426</v>
       </c>
       <c r="X119" t="n">
-        <v>510.842683603328</v>
+        <v>510.842683603329</v>
       </c>
       <c r="Y119" t="n">
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>479.263317707851</v>
+        <v>479.26331770785</v>
       </c>
       <c r="AA119" t="n">
         <v>0.00542857142857143</v>
@@ -14806,7 +14806,7 @@
         <v>0.638049712338857</v>
       </c>
       <c r="K120" t="n">
-        <v>0.0261701406516686</v>
+        <v>0.0261701406516687</v>
       </c>
       <c r="L120" t="n">
         <v>0.0374708832057983</v>
@@ -14824,7 +14824,7 @@
         <v>0.00988243073559516</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.0431807320752532</v>
+        <v>0.0431807320752533</v>
       </c>
       <c r="R120" t="n">
         <v>0.010277727965019</v>
@@ -14842,7 +14842,7 @@
         <v>1722.97758679571</v>
       </c>
       <c r="W120" t="n">
-        <v>850.853129281832</v>
+        <v>850.853129281834</v>
       </c>
       <c r="X120" t="n">
         <v>589.052166425885</v>
@@ -14913,7 +14913,7 @@
         <v>0.0660716150729122</v>
       </c>
       <c r="M121" t="n">
-        <v>0.0577432602317886</v>
+        <v>0.0577432602317889</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
         <v>0.0124370098960776</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.0577432602317886</v>
+        <v>0.0577432602317889</v>
       </c>
       <c r="R121" t="n">
         <v>0.015546262370097</v>
@@ -15023,7 +15023,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0.00791744498443605</v>
+        <v>0.00791744498443604</v>
       </c>
       <c r="Q122" t="n">
         <v>0.0665065378692627</v>
@@ -15038,7 +15038,7 @@
         <v>1199.7779431615</v>
       </c>
       <c r="U122" t="n">
-        <v>736.227374212739</v>
+        <v>736.227374212738</v>
       </c>
       <c r="V122" t="n">
         <v>2290.48516421741</v>
@@ -15115,7 +15115,7 @@
         <v>0.0192436304617503</v>
       </c>
       <c r="M123" t="n">
-        <v>0.0704132840180468</v>
+        <v>0.0704132840180467</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
@@ -15124,13 +15124,13 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0.0076755221214958</v>
+        <v>0.00767552212149583</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.0704132840180468</v>
+        <v>0.0704132840180467</v>
       </c>
       <c r="R123" t="n">
-        <v>0.00906188350840946</v>
+        <v>0.00906188350840948</v>
       </c>
       <c r="S123" t="n">
         <v>18359.0119112505</v>
@@ -15139,22 +15139,22 @@
         <v>1638.92158473889</v>
       </c>
       <c r="U123" t="n">
-        <v>764.5686818758</v>
+        <v>764.568681875799</v>
       </c>
       <c r="V123" t="n">
-        <v>2797.59018732102</v>
+        <v>2797.59018732101</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>304.95616940915</v>
+        <v>304.956169409151</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>360.037693672616</v>
+        <v>360.037693672617</v>
       </c>
       <c r="AA123" t="n">
         <v>0.0076</v>
@@ -15219,13 +15219,13 @@
         <v>0.0382609144638563</v>
       </c>
       <c r="N124" t="n">
-        <v>0.00289855412604971</v>
+        <v>0.00289855412604972</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>0.00910974153901337</v>
+        <v>0.0091097415390134</v>
       </c>
       <c r="Q124" t="n">
         <v>0.041159468589906</v>
@@ -15249,7 +15249,7 @@
         <v>158.391490217987</v>
       </c>
       <c r="X124" t="n">
-        <v>497.801826399386</v>
+        <v>497.801826399387</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>0.54355069589118</v>
       </c>
       <c r="K125" t="n">
-        <v>0.0324273506009541</v>
+        <v>0.032427350600954</v>
       </c>
       <c r="L125" t="n">
         <v>0.0473109978494388</v>
@@ -15320,7 +15320,7 @@
         <v>0.021888461655644</v>
       </c>
       <c r="N125" t="n">
-        <v>0.00972820518028624</v>
+        <v>0.00972820518028621</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15347,7 +15347,7 @@
         <v>1349.22666491555</v>
       </c>
       <c r="W125" t="n">
-        <v>599.656295518024</v>
+        <v>599.656295518022</v>
       </c>
       <c r="X125" t="n">
         <v>502.653071243048</v>
@@ -15418,7 +15418,7 @@
         <v>0.0259203805786059</v>
       </c>
       <c r="M126" t="n">
-        <v>0.0508231971451077</v>
+        <v>0.0508231971451074</v>
       </c>
       <c r="N126" t="n">
         <v>0.00800850379256238</v>
@@ -15430,7 +15430,7 @@
         <v>0.0120127556888436</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.05883170093767</v>
+        <v>0.0588317009376698</v>
       </c>
       <c r="R126" t="n">
         <v>0.0115507266238881</v>
@@ -15442,10 +15442,10 @@
         <v>1622.44278333521</v>
       </c>
       <c r="U126" t="n">
-        <v>1050.24198028396</v>
+        <v>1050.24198028395</v>
       </c>
       <c r="V126" t="n">
-        <v>2059.25430192547</v>
+        <v>2059.25430192546</v>
       </c>
       <c r="W126" t="n">
         <v>324.488556667043</v>
@@ -15457,7 +15457,7 @@
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>468.012341346697</v>
+        <v>468.012341346696</v>
       </c>
       <c r="AA126" t="n">
         <v>0.008</v>
@@ -15516,7 +15516,7 @@
         <v>0.03108708583076</v>
       </c>
       <c r="L127" t="n">
-        <v>0.0470144199292358</v>
+        <v>0.0470144199292357</v>
       </c>
       <c r="M127" t="n">
         <v>0.0435219201630639</v>
@@ -15653,7 +15653,7 @@
         <v>188.436580451641</v>
       </c>
       <c r="X128" t="n">
-        <v>591.404512912563</v>
+        <v>591.404512912565</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
@@ -15721,7 +15721,7 @@
         <v>0.0126116627855781</v>
       </c>
       <c r="M129" t="n">
-        <v>0.0592659957476115</v>
+        <v>0.0592659957476116</v>
       </c>
       <c r="N129" t="n">
         <v>0.00550327103370679</v>
@@ -15730,10 +15730,10 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>0.00821874407662303</v>
+        <v>0.00821874407662304</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.0647692667813183</v>
+        <v>0.0647692667813184</v>
       </c>
       <c r="R129" t="n">
         <v>0.00305737279650377</v>
@@ -15748,7 +15748,7 @@
         <v>507.758155410158</v>
       </c>
       <c r="V129" t="n">
-        <v>2386.10825479458</v>
+        <v>2386.10825479459</v>
       </c>
       <c r="W129" t="n">
         <v>221.567195088069</v>
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0.00253289691094378</v>
+        <v>0.00253289691094377</v>
       </c>
       <c r="Q130" t="n">
         <v>0.0616110059418756</v>
@@ -15855,13 +15855,13 @@
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>87.5698449020592</v>
+        <v>87.5698449020591</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>869.329733027715</v>
+        <v>869.329733027714</v>
       </c>
       <c r="AA130" t="n">
         <v>0.006</v>
@@ -15920,7 +15920,7 @@
         <v>0.0253554805805795</v>
       </c>
       <c r="L131" t="n">
-        <v>0.0486940479331583</v>
+        <v>0.0486940479331584</v>
       </c>
       <c r="M131" t="n">
         <v>0.0343241960256109</v>
@@ -15962,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>948.705087086845</v>
+        <v>948.705087086846</v>
       </c>
       <c r="AA131" t="n">
         <v>0.00423076923076923</v>
@@ -16024,7 +16024,7 @@
         <v>0.0796089708849129</v>
       </c>
       <c r="M132" t="n">
-        <v>0.0532086248534564</v>
+        <v>0.0532086248534563</v>
       </c>
       <c r="N132" t="n">
         <v>0.00641864042969063</v>
@@ -16033,10 +16033,10 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>0.00792180921407972</v>
+        <v>0.00792180921407971</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.059627265283147</v>
+        <v>0.0596272652831469</v>
       </c>
       <c r="R132" t="n">
         <v>0.0325211115104325</v>
@@ -16149,7 +16149,7 @@
         <v>1210.41849797167</v>
       </c>
       <c r="U133" t="n">
-        <v>5013.56774307795</v>
+        <v>5013.56774307794</v>
       </c>
       <c r="V133" t="n">
         <v>2383.59334985191</v>
@@ -16158,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>72.4182007333479</v>
+        <v>72.418200733348</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
@@ -16235,7 +16235,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>0.00591515344059149</v>
+        <v>0.0059151534405915</v>
       </c>
       <c r="Q134" t="n">
         <v>0.0425891047722588</v>
@@ -16259,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>252.174821479296</v>
+        <v>252.174821479297</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
@@ -16342,7 +16342,7 @@
         <v>0.0604357051768069</v>
       </c>
       <c r="R135" t="n">
-        <v>0.0455743627911941</v>
+        <v>0.045574362791194</v>
       </c>
       <c r="S135" t="n">
         <v>24288.1609413227</v>
@@ -16559,7 +16559,7 @@
         <v>1563.63231343531</v>
       </c>
       <c r="W137" t="n">
-        <v>275.772894785769</v>
+        <v>275.772894785768</v>
       </c>
       <c r="X137" t="n">
         <v>385.805489625076</v>
@@ -16627,13 +16627,13 @@
         <v>0.0226758721251612</v>
       </c>
       <c r="L138" t="n">
-        <v>0.0701219851203773</v>
+        <v>0.0701219851203771</v>
       </c>
       <c r="M138" t="n">
         <v>0.0331067733027354</v>
       </c>
       <c r="N138" t="n">
-        <v>0.0175566222059961</v>
+        <v>0.017556622205996</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16648,19 +16648,19 @@
         <v>0.0331067733027354</v>
       </c>
       <c r="S138" t="n">
-        <v>28867.3060303385</v>
+        <v>28867.3060303384</v>
       </c>
       <c r="T138" t="n">
         <v>1168.91853217994</v>
       </c>
       <c r="U138" t="n">
-        <v>3614.71821097033</v>
+        <v>3614.71821097032</v>
       </c>
       <c r="V138" t="n">
         <v>1706.62105698271</v>
       </c>
       <c r="W138" t="n">
-        <v>905.026318096892</v>
+        <v>905.02631809689</v>
       </c>
       <c r="X138" t="n">
         <v>284.436842830451</v>
@@ -16722,7 +16722,7 @@
         <v>0.622178054342336</v>
       </c>
       <c r="J139" t="n">
-        <v>0.508428822391889</v>
+        <v>0.50842882239189</v>
       </c>
       <c r="K139" t="n">
         <v>0.0217137060236311</v>
@@ -16847,7 +16847,7 @@
         <v>0.0314833037372112</v>
       </c>
       <c r="R140" t="n">
-        <v>0.00842926472214493</v>
+        <v>0.00842926472214491</v>
       </c>
       <c r="S140" t="n">
         <v>25774.7603694905</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>393.317921200005</v>
+        <v>393.317921200004</v>
       </c>
       <c r="AA140" t="n">
         <v>0.004</v>
@@ -16915,7 +16915,7 @@
         <v>60242</v>
       </c>
       <c r="G141" t="n">
-        <v>504700.620119969</v>
+        <v>504700.62011997</v>
       </c>
       <c r="H141" t="n">
         <v>30080.6310943824</v>
@@ -16972,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>669.744898737401</v>
+        <v>669.7448987374</v>
       </c>
       <c r="AA141" t="n">
         <v>0.00413223140495868</v>
@@ -17147,7 +17147,7 @@
         <v>0.00250734528158155</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.0476843343729348</v>
+        <v>0.0476843343729347</v>
       </c>
       <c r="R143" t="n">
         <v>0.0150440716894893</v>
@@ -17245,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0.00801586397508361</v>
+        <v>0.00801586397508363</v>
       </c>
       <c r="Q144" t="n">
         <v>0.0539843900362775</v>
@@ -17254,7 +17254,7 @@
         <v>0.00944726825634857</v>
       </c>
       <c r="S144" t="n">
-        <v>19973.412062934</v>
+        <v>19973.4120629341</v>
       </c>
       <c r="T144" t="n">
         <v>1203.18690827718</v>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>311.937346590379</v>
+        <v>311.93734659038</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
@@ -17340,7 +17340,7 @@
         <v>0.0431261563508662</v>
       </c>
       <c r="N145" t="n">
-        <v>0.00401618307480351</v>
+        <v>0.0040161830748035</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17349,7 +17349,7 @@
         <v>0.00823317530334718</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.0471423394256698</v>
+        <v>0.0471423394256697</v>
       </c>
       <c r="R145" t="n">
         <v>0.013721958838912</v>
@@ -17364,7 +17364,7 @@
         <v>1392.72687473396</v>
       </c>
       <c r="V145" t="n">
-        <v>1976.77362865466</v>
+        <v>1976.77362865465</v>
       </c>
       <c r="W145" t="n">
         <v>184.089783599768</v>
@@ -17432,13 +17432,13 @@
         <v>0.291259870500739</v>
       </c>
       <c r="K146" t="n">
-        <v>0.0602701326268273</v>
+        <v>0.0602701326268275</v>
       </c>
       <c r="L146" t="n">
         <v>0.0252482988031304</v>
       </c>
       <c r="M146" t="n">
-        <v>0.0517422442265289</v>
+        <v>0.0517422442265292</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
@@ -17450,10 +17450,10 @@
         <v>0.00733015126542496</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.0517422442265289</v>
+        <v>0.0517422442265292</v>
       </c>
       <c r="R146" t="n">
-        <v>0.00827875907624465</v>
+        <v>0.00827875907624467</v>
       </c>
       <c r="S146" t="n">
         <v>19832.0784341255</v>
@@ -17465,7 +17465,7 @@
         <v>1148.84809214004</v>
       </c>
       <c r="V146" t="n">
-        <v>2354.37559679552</v>
+        <v>2354.37559679553</v>
       </c>
       <c r="W146" t="n">
         <v>0</v>
@@ -17477,7 +17477,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>376.700095487284</v>
+        <v>376.700095487285</v>
       </c>
       <c r="AA146" t="n">
         <v>0.0123333333333333</v>
@@ -17536,7 +17536,7 @@
         <v>0.0237150445812698</v>
       </c>
       <c r="L147" t="n">
-        <v>0.0410354967843757</v>
+        <v>0.0410354967843758</v>
       </c>
       <c r="M147" t="n">
         <v>0.0441390217512613</v>
@@ -17628,13 +17628,13 @@
         <v>13441.8611920191</v>
       </c>
       <c r="I148" t="n">
-        <v>0.578886375636202</v>
+        <v>0.578886375636201</v>
       </c>
       <c r="J148" t="n">
         <v>0.398643530117118</v>
       </c>
       <c r="K148" t="n">
-        <v>0.0688004499794516</v>
+        <v>0.0688004499794515</v>
       </c>
       <c r="L148" t="n">
         <v>0.0230927436273622</v>
@@ -17649,7 +17649,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>0.00808246026957674</v>
+        <v>0.00808246026957677</v>
       </c>
       <c r="Q148" t="n">
         <v>0.0802671916426934</v>
@@ -17664,7 +17664,7 @@
         <v>2319.88237285713</v>
       </c>
       <c r="U148" t="n">
-        <v>778.664222371025</v>
+        <v>778.664222371026</v>
       </c>
       <c r="V148" t="n">
         <v>2435.87649149998</v>
@@ -17673,7 +17673,7 @@
         <v>270.652943499998</v>
       </c>
       <c r="X148" t="n">
-        <v>272.532477829858</v>
+        <v>272.532477829859</v>
       </c>
       <c r="Y148" t="n">
         <v>0</v>
@@ -17756,7 +17756,7 @@
         <v>0.0466321618205805</v>
       </c>
       <c r="R149" t="n">
-        <v>0.0370239278999787</v>
+        <v>0.0370239278999788</v>
       </c>
       <c r="S149" t="n">
         <v>29235.938693811</v>
@@ -17771,7 +17771,7 @@
         <v>1918.13039534708</v>
       </c>
       <c r="W149" t="n">
-        <v>536.539970726458</v>
+        <v>536.539970726456</v>
       </c>
       <c r="X149" t="n">
         <v>590.333691749812</v>
@@ -17851,7 +17851,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>0.011068970389039</v>
+        <v>0.0110689703890389</v>
       </c>
       <c r="Q150" t="n">
         <v>0.0440492564089264</v>
@@ -17875,13 +17875,13 @@
         <v>54.9731809518313</v>
       </c>
       <c r="X150" t="n">
-        <v>565.724007613392</v>
+        <v>565.724007613391</v>
       </c>
       <c r="Y150" t="n">
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>919.083926214985</v>
+        <v>919.083926214987</v>
       </c>
       <c r="AA150" t="n">
         <v>0.00344827586206897</v>
@@ -17925,7 +17925,7 @@
         <v>50685</v>
       </c>
       <c r="G151" t="n">
-        <v>350160.763619861</v>
+        <v>350160.763619862</v>
       </c>
       <c r="H151" t="n">
         <v>20867.5186687993</v>
@@ -17976,13 +17976,13 @@
         <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>86.1934187371966</v>
+        <v>86.1934187371967</v>
       </c>
       <c r="Y151" t="n">
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>808.06330066122</v>
+        <v>808.063300661219</v>
       </c>
       <c r="AA151" t="n">
         <v>0.00323076923076923</v>
@@ -18059,7 +18059,7 @@
         <v>0.0474911828591287</v>
       </c>
       <c r="R152" t="n">
-        <v>0.102897562861445</v>
+        <v>0.102897562861446</v>
       </c>
       <c r="S152" t="n">
         <v>34848.321176913</v>
@@ -18071,7 +18071,7 @@
         <v>6760.31585877648</v>
       </c>
       <c r="V152" t="n">
-        <v>2447.17316154804</v>
+        <v>2447.17316154805</v>
       </c>
       <c r="W152" t="n">
         <v>0</v>
@@ -18083,7 +18083,7 @@
         <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>5302.20851668742</v>
+        <v>5302.20851668743</v>
       </c>
       <c r="AA152" t="n">
         <v>0.004</v>
@@ -18142,10 +18142,10 @@
         <v>0.0405204563760224</v>
       </c>
       <c r="L153" t="n">
-        <v>0.0246300813266019</v>
+        <v>0.0246300813266018</v>
       </c>
       <c r="M153" t="n">
-        <v>0.0523020344483786</v>
+        <v>0.0523020344483785</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -18157,10 +18157,10 @@
         <v>0.00768034794055326</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.0523020344483786</v>
+        <v>0.0523020344483785</v>
       </c>
       <c r="R153" t="n">
-        <v>0.00980663145907098</v>
+        <v>0.00980663145907097</v>
       </c>
       <c r="S153" t="n">
         <v>18542.3556605875</v>
@@ -18172,7 +18172,7 @@
         <v>1115.964354827</v>
       </c>
       <c r="V153" t="n">
-        <v>2369.75287882159</v>
+        <v>2369.75287882158</v>
       </c>
       <c r="W153" t="n">
         <v>0</v>
@@ -18184,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>444.328664779047</v>
+        <v>444.328664779046</v>
       </c>
       <c r="AA153" t="n">
         <v>0.0085</v>
@@ -18240,13 +18240,13 @@
         <v>0.606572675114964</v>
       </c>
       <c r="K154" t="n">
-        <v>0.0422998260841265</v>
+        <v>0.0422998260841264</v>
       </c>
       <c r="L154" t="n">
         <v>0.073401891717497</v>
       </c>
       <c r="M154" t="n">
-        <v>0.0335049432916973</v>
+        <v>0.0335049432916974</v>
       </c>
       <c r="N154" t="n">
         <v>0.0122140747817915</v>
@@ -18258,7 +18258,7 @@
         <v>0.00407135826059717</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.0457190180734888</v>
+        <v>0.0457190180734889</v>
       </c>
       <c r="R154" t="n">
         <v>0.00977125982543321</v>
@@ -18273,7 +18273,7 @@
         <v>3416.56445188262</v>
       </c>
       <c r="V154" t="n">
-        <v>1559.52109045534</v>
+        <v>1559.52109045535</v>
       </c>
       <c r="W154" t="n">
         <v>568.516324793267</v>
@@ -18368,7 +18368,7 @@
         <v>20675.6174697509</v>
       </c>
       <c r="T155" t="n">
-        <v>992.220558971719</v>
+        <v>992.220558971718</v>
       </c>
       <c r="U155" t="n">
         <v>1561.168847673</v>
@@ -18380,13 +18380,13 @@
         <v>0</v>
       </c>
       <c r="X155" t="n">
-        <v>96.5360446870263</v>
+        <v>96.5360446870262</v>
       </c>
       <c r="Y155" t="n">
         <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>837.794959248121</v>
+        <v>837.79495924812</v>
       </c>
       <c r="AA155" t="n">
         <v>0.00365448504983389</v>
@@ -18445,7 +18445,7 @@
         <v>0.0487117640536731</v>
       </c>
       <c r="L156" t="n">
-        <v>0.0405931367113943</v>
+        <v>0.0405931367113942</v>
       </c>
       <c r="M156" t="n">
         <v>0.0412617295513466</v>
@@ -18457,7 +18457,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>0.00865986916509744</v>
+        <v>0.00865986916509743</v>
       </c>
       <c r="Q156" t="n">
         <v>0.0412617295513466</v>
@@ -18481,7 +18481,7 @@
         <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>467.806132298564</v>
+        <v>467.806132298563</v>
       </c>
       <c r="Y156" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
         <v>0.0373824540120395</v>
       </c>
       <c r="R157" t="n">
-        <v>0.0068661650226195</v>
+        <v>0.00686616502261951</v>
       </c>
       <c r="S157" t="n">
         <v>21291.7272731735</v>
@@ -18588,7 +18588,7 @@
         <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>382.012823363481</v>
+        <v>382.012823363482</v>
       </c>
       <c r="AA157" t="n">
         <v>0.00466666666666667</v>
@@ -18760,7 +18760,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>0.00855138103848638</v>
+        <v>0.0085513810384864</v>
       </c>
       <c r="Q159" t="n">
         <v>0.0630871919610129</v>
@@ -18784,7 +18784,7 @@
         <v>58.7159990788658</v>
       </c>
       <c r="X159" t="n">
-        <v>330.929894808384</v>
+        <v>330.929894808385</v>
       </c>
       <c r="Y159" t="n">
         <v>0</v>
@@ -18849,7 +18849,7 @@
         <v>0.0768273975127008</v>
       </c>
       <c r="L160" t="n">
-        <v>0.0209529265943729</v>
+        <v>0.020952926594373</v>
       </c>
       <c r="M160" t="n">
         <v>0.0557254723292123</v>
@@ -18861,13 +18861,13 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>0.0091962969591263</v>
+        <v>0.00919629695912628</v>
       </c>
       <c r="Q160" t="n">
         <v>0.0614875271426649</v>
       </c>
       <c r="R160" t="n">
-        <v>0.00833381939120824</v>
+        <v>0.00833381939120823</v>
       </c>
       <c r="S160" t="n">
         <v>17485.291929853</v>
@@ -18876,7 +18876,7 @@
         <v>2835.46876000125</v>
       </c>
       <c r="U160" t="n">
-        <v>773.309661818522</v>
+        <v>773.309661818523</v>
       </c>
       <c r="V160" t="n">
         <v>2056.66000725424</v>
@@ -18891,7 +18891,7 @@
         <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>307.576272271323</v>
+        <v>307.576272271322</v>
       </c>
       <c r="AA160" t="n">
         <v>0.015</v>
@@ -18947,7 +18947,7 @@
         <v>0.356710732999925</v>
       </c>
       <c r="K161" t="n">
-        <v>0.0448871938756031</v>
+        <v>0.0448871938756032</v>
       </c>
       <c r="L161" t="n">
         <v>0.0807494493000269</v>
@@ -18956,7 +18956,7 @@
         <v>0.0437162236005874</v>
       </c>
       <c r="N161" t="n">
-        <v>0.00870539517587452</v>
+        <v>0.00870539517587455</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -18983,16 +18983,16 @@
         <v>2280.85025013705</v>
       </c>
       <c r="W161" t="n">
-        <v>454.195287906077</v>
+        <v>454.195287906079</v>
       </c>
       <c r="X161" t="n">
-        <v>390.324075544286</v>
+        <v>390.324075544287</v>
       </c>
       <c r="Y161" t="n">
         <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>881.673205935331</v>
+        <v>881.67320593533</v>
       </c>
       <c r="AA161" t="n">
         <v>0.0075</v>
@@ -19054,10 +19054,10 @@
         <v>0.0326842721764946</v>
       </c>
       <c r="M162" t="n">
-        <v>0.0789104552581188</v>
+        <v>0.0789104552581186</v>
       </c>
       <c r="N162" t="n">
-        <v>0.00722970075793429</v>
+        <v>0.0072297007579343</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19066,7 +19066,7 @@
         <v>0.0171328846086464</v>
       </c>
       <c r="Q162" t="n">
-        <v>0.0861401560160531</v>
+        <v>0.0861401560160529</v>
       </c>
       <c r="R162" t="n">
         <v>0.012651976326385</v>
@@ -19081,7 +19081,7 @@
         <v>1032.03857824499</v>
       </c>
       <c r="V162" t="n">
-        <v>2491.67653523036</v>
+        <v>2491.67653523035</v>
       </c>
       <c r="W162" t="n">
         <v>228.285031132533</v>
@@ -19170,7 +19170,7 @@
         <v>0.0423059212329028</v>
       </c>
       <c r="R163" t="n">
-        <v>0.00764062016499532</v>
+        <v>0.00764062016499534</v>
       </c>
       <c r="S163" t="n">
         <v>24465.8914607291</v>
@@ -19194,7 +19194,7 @@
         <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>444.447234377613</v>
+        <v>444.447234377614</v>
       </c>
       <c r="AA163" t="n">
         <v>0.00526315789473684</v>
@@ -19354,7 +19354,7 @@
         <v>0.0288189198939406</v>
       </c>
       <c r="L165" t="n">
-        <v>0.0454452198327524</v>
+        <v>0.0454452198327525</v>
       </c>
       <c r="M165" t="n">
         <v>0.0364028461818197</v>
@@ -19369,13 +19369,13 @@
         <v>0.00576378397878812</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.0491718445348273</v>
+        <v>0.0491718445348272</v>
       </c>
       <c r="R165" t="n">
         <v>0.0107233190303035</v>
       </c>
       <c r="S165" t="n">
-        <v>24301.4856913513</v>
+        <v>24301.4856913514</v>
       </c>
       <c r="T165" t="n">
         <v>1481.55185282759</v>
@@ -19387,7 +19387,7 @@
         <v>1871.43391936117</v>
       </c>
       <c r="W165" t="n">
-        <v>656.441436329765</v>
+        <v>656.441436329764</v>
       </c>
       <c r="X165" t="n">
         <v>296.310370565518</v>
@@ -19455,13 +19455,13 @@
         <v>0.0410830522802948</v>
       </c>
       <c r="L166" t="n">
-        <v>0.121879721764874</v>
+        <v>0.121879721764875</v>
       </c>
       <c r="M166" t="n">
         <v>0.039439730189083</v>
       </c>
       <c r="N166" t="n">
-        <v>0.00917203027653092</v>
+        <v>0.00917203027653093</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -19482,16 +19482,16 @@
         <v>1502.11964052442</v>
       </c>
       <c r="U166" t="n">
-        <v>4456.2882668891</v>
+        <v>4456.28826688911</v>
       </c>
       <c r="V166" t="n">
         <v>1442.03485490344</v>
       </c>
       <c r="W166" t="n">
-        <v>335.3569430008</v>
+        <v>335.356943000801</v>
       </c>
       <c r="X166" t="n">
-        <v>559.880956922737</v>
+        <v>559.880956922738</v>
       </c>
       <c r="Y166" t="n">
         <v>0</v>
@@ -19583,7 +19583,7 @@
         <v>1050.68034939039</v>
       </c>
       <c r="U167" t="n">
-        <v>7343.46480756725</v>
+        <v>7343.46480756724</v>
       </c>
       <c r="V167" t="n">
         <v>2101.36069878078</v>
@@ -19598,7 +19598,7 @@
         <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>4697.15920903941</v>
+        <v>4697.15920903939</v>
       </c>
       <c r="AA167" t="n">
         <v>0.003</v>
@@ -19648,7 +19648,7 @@
         <v>13529.1528203115</v>
       </c>
       <c r="I168" t="n">
-        <v>0.530247066527861</v>
+        <v>0.530247066527862</v>
       </c>
       <c r="J168" t="n">
         <v>0.361046990294392</v>
@@ -19660,7 +19660,7 @@
         <v>0.0711193881478797</v>
       </c>
       <c r="M168" t="n">
-        <v>0.0608034849781466</v>
+        <v>0.0608034849781469</v>
       </c>
       <c r="N168" t="n">
         <v>0</v>
@@ -19672,7 +19672,7 @@
         <v>0.00395645273445499</v>
       </c>
       <c r="Q168" t="n">
-        <v>0.0608034849781466</v>
+        <v>0.0608034849781469</v>
       </c>
       <c r="R168" t="n">
         <v>0.0121166364992684</v>
@@ -19687,7 +19687,7 @@
         <v>2664.98571267735</v>
       </c>
       <c r="V168" t="n">
-        <v>2278.42818910111</v>
+        <v>2278.42818910112</v>
       </c>
       <c r="W168" t="n">
         <v>0</v>
@@ -19770,13 +19770,13 @@
         <v>0</v>
       </c>
       <c r="P169" t="n">
-        <v>0.00979578145463049</v>
+        <v>0.0097957814546305</v>
       </c>
       <c r="Q169" t="n">
         <v>0.0625171795912188</v>
       </c>
       <c r="R169" t="n">
-        <v>0.00886284988752281</v>
+        <v>0.00886284988752284</v>
       </c>
       <c r="S169" t="n">
         <v>18412.5654221282</v>
@@ -19788,7 +19788,7 @@
         <v>1166.99987966685</v>
       </c>
       <c r="V169" t="n">
-        <v>2056.53125647585</v>
+        <v>2056.53125647586</v>
       </c>
       <c r="W169" t="n">
         <v>509.236311127355</v>
@@ -19800,7 +19800,7 @@
         <v>0</v>
       </c>
       <c r="Z169" t="n">
-        <v>363.740222233824</v>
+        <v>363.740222233825</v>
       </c>
       <c r="AA169" t="n">
         <v>0.00769230769230769</v>
@@ -19892,7 +19892,7 @@
         <v>1995.42508876898</v>
       </c>
       <c r="W170" t="n">
-        <v>99.9711968321133</v>
+        <v>99.9711968321134</v>
       </c>
       <c r="X170" t="n">
         <v>148.469128628645</v>
@@ -19978,7 +19978,7 @@
         <v>0.0357148905980751</v>
       </c>
       <c r="R171" t="n">
-        <v>0.013736496383875</v>
+        <v>0.0137364963838751</v>
       </c>
       <c r="S171" t="n">
         <v>27646.3422963052</v>
@@ -20073,7 +20073,7 @@
         <v>0</v>
       </c>
       <c r="P172" t="n">
-        <v>0.00768825747079071</v>
+        <v>0.00768825747079072</v>
       </c>
       <c r="Q172" t="n">
         <v>0.0495022238095723</v>
@@ -20159,13 +20159,13 @@
         <v>0.362569137679196</v>
       </c>
       <c r="K173" t="n">
-        <v>0.0265496351944455</v>
+        <v>0.0265496351944456</v>
       </c>
       <c r="L173" t="n">
         <v>0.0790957881834524</v>
       </c>
       <c r="M173" t="n">
-        <v>0.0449301518675232</v>
+        <v>0.0449301518675233</v>
       </c>
       <c r="N173" t="n">
         <v>0</v>
@@ -20177,7 +20177,7 @@
         <v>0.0110623479976857</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.0449301518675232</v>
+        <v>0.0449301518675233</v>
       </c>
       <c r="R173" t="n">
         <v>0.0153708414283632</v>
@@ -20204,7 +20204,7 @@
         <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>736.324787784311</v>
+        <v>736.324787784312</v>
       </c>
       <c r="AA173" t="n">
         <v>0.00436363636363636</v>
@@ -20364,7 +20364,7 @@
         <v>0.0230824066860768</v>
       </c>
       <c r="L175" t="n">
-        <v>0.027660735284968</v>
+        <v>0.0276607352849681</v>
       </c>
       <c r="M175" t="n">
         <v>0.0433736393579172</v>
@@ -20406,7 +20406,7 @@
         <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>1421.58247577723</v>
+        <v>1421.58247577724</v>
       </c>
       <c r="AA175" t="n">
         <v>0.00366666666666667</v>
@@ -20489,7 +20489,7 @@
         <v>11074.760112271</v>
       </c>
       <c r="T176" t="n">
-        <v>645.32282787315</v>
+        <v>645.322827873151</v>
       </c>
       <c r="U176" t="n">
         <v>1360.55562876589</v>
@@ -20584,7 +20584,7 @@
         <v>0.0531395841665292</v>
       </c>
       <c r="R177" t="n">
-        <v>0.00867585047616804</v>
+        <v>0.00867585047616803</v>
       </c>
       <c r="S177" t="n">
         <v>16382.4350038486</v>
@@ -20768,10 +20768,10 @@
         <v>0.0249530618245038</v>
       </c>
       <c r="L179" t="n">
-        <v>0.0279804553546825</v>
+        <v>0.0279804553546826</v>
       </c>
       <c r="M179" t="n">
-        <v>0.0340269024879597</v>
+        <v>0.0340269024879598</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
@@ -20783,7 +20783,7 @@
         <v>0.00779783182015745</v>
       </c>
       <c r="Q179" t="n">
-        <v>0.0340269024879597</v>
+        <v>0.0340269024879598</v>
       </c>
       <c r="R179" t="n">
         <v>0.0408322829855517</v>
@@ -20795,7 +20795,7 @@
         <v>1626.36571053569</v>
       </c>
       <c r="U179" t="n">
-        <v>1823.68213865214</v>
+        <v>1823.68213865215</v>
       </c>
       <c r="V179" t="n">
         <v>2217.77142345775</v>
@@ -20810,7 +20810,7 @@
         <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>2661.32570814931</v>
+        <v>2661.3257081493</v>
       </c>
       <c r="AA179" t="n">
         <v>0.0016</v>
@@ -20854,7 +20854,7 @@
         <v>41137</v>
       </c>
       <c r="G180" t="n">
-        <v>276183.537825948</v>
+        <v>276183.537825949</v>
       </c>
       <c r="H180" t="n">
         <v>16458.9616921205</v>
@@ -20905,7 +20905,7 @@
         <v>0</v>
       </c>
       <c r="X180" t="n">
-        <v>460.305896376582</v>
+        <v>460.305896376581</v>
       </c>
       <c r="Y180" t="n">
         <v>0</v>
@@ -20961,7 +20961,7 @@
         <v>13119.9965140794</v>
       </c>
       <c r="I181" t="n">
-        <v>0.546937657428829</v>
+        <v>0.54693765742883</v>
       </c>
       <c r="J181" t="n">
         <v>0.330578424563581</v>
@@ -21012,7 +21012,7 @@
         <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>629.070616203551</v>
+        <v>629.07061620355</v>
       </c>
       <c r="AA181" t="n">
         <v>0.00606060606060606</v>
@@ -21062,16 +21062,16 @@
         <v>19505.2618353079</v>
       </c>
       <c r="I182" t="n">
-        <v>0.547194036679861</v>
+        <v>0.547194036679862</v>
       </c>
       <c r="J182" t="n">
         <v>0.371741220417532</v>
       </c>
       <c r="K182" t="n">
-        <v>0.0415860624847443</v>
+        <v>0.0415860624847442</v>
       </c>
       <c r="L182" t="n">
-        <v>0.0650524834582783</v>
+        <v>0.0650524834582785</v>
       </c>
       <c r="M182" t="n">
         <v>0.0382591774859647</v>
@@ -21083,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="n">
-        <v>0.012129268224717</v>
+        <v>0.0121292682247171</v>
       </c>
       <c r="Q182" t="n">
         <v>0.0566850020945898</v>
@@ -21098,16 +21098,16 @@
         <v>2182.02069857453</v>
       </c>
       <c r="U182" t="n">
-        <v>3413.30380705586</v>
+        <v>3413.30380705587</v>
       </c>
       <c r="V182" t="n">
         <v>2007.45904268857</v>
       </c>
       <c r="W182" t="n">
-        <v>966.80301721456</v>
+        <v>966.803017214561</v>
       </c>
       <c r="X182" t="n">
-        <v>636.422703750903</v>
+        <v>636.422703750905</v>
       </c>
       <c r="Y182" t="n">
         <v>0</v>
@@ -21169,7 +21169,7 @@
         <v>0.466049422680589</v>
       </c>
       <c r="K183" t="n">
-        <v>0.0212250219338312</v>
+        <v>0.0212250219338313</v>
       </c>
       <c r="L183" t="n">
         <v>0.0632688452860138</v>
@@ -21190,7 +21190,7 @@
         <v>0.0291937143791644</v>
       </c>
       <c r="R183" t="n">
-        <v>0.00804316620650449</v>
+        <v>0.00804316620650448</v>
       </c>
       <c r="S183" t="n">
         <v>33505.958677269</v>
@@ -21208,13 +21208,13 @@
         <v>0</v>
       </c>
       <c r="X183" t="n">
-        <v>717.193189223504</v>
+        <v>717.193189223505</v>
       </c>
       <c r="Y183" t="n">
         <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>454.905394307481</v>
+        <v>454.90539430748</v>
       </c>
       <c r="AA183" t="n">
         <v>0.00271428571428571</v>
@@ -21273,7 +21273,7 @@
         <v>0.0355585303399112</v>
       </c>
       <c r="L184" t="n">
-        <v>0.0636722995067279</v>
+        <v>0.063672299506728</v>
       </c>
       <c r="M184" t="n">
         <v>0.0495664362313913</v>
@@ -21291,7 +21291,7 @@
         <v>0.0495664362313913</v>
       </c>
       <c r="R184" t="n">
-        <v>0.00608488219720404</v>
+        <v>0.00608488219720405</v>
       </c>
       <c r="S184" t="n">
         <v>22777.9995532097</v>
@@ -21300,7 +21300,7 @@
         <v>1677.22475907293</v>
       </c>
       <c r="U184" t="n">
-        <v>3003.29502313334</v>
+        <v>3003.29502313335</v>
       </c>
       <c r="V184" t="n">
         <v>2337.94966416227</v>
@@ -21309,13 +21309,13 @@
         <v>0</v>
       </c>
       <c r="X184" t="n">
-        <v>613.405084300446</v>
+        <v>613.405084300445</v>
       </c>
       <c r="Y184" t="n">
         <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>287.01172347772</v>
+        <v>287.011723477721</v>
       </c>
       <c r="AA184" t="n">
         <v>0.0066</v>
@@ -21567,7 +21567,7 @@
         <v>21856.3737151789</v>
       </c>
       <c r="I187" t="n">
-        <v>0.586679478965213</v>
+        <v>0.586679478965212</v>
       </c>
       <c r="J187" t="n">
         <v>0.466896815243503</v>
@@ -21612,7 +21612,7 @@
         <v>0</v>
       </c>
       <c r="X187" t="n">
-        <v>458.413365994202</v>
+        <v>458.413365994203</v>
       </c>
       <c r="Y187" t="n">
         <v>0</v>
@@ -21695,7 +21695,7 @@
         <v>0.0673440451242587</v>
       </c>
       <c r="R188" t="n">
-        <v>0.00678565788581875</v>
+        <v>0.00678565788581876</v>
       </c>
       <c r="S188" t="n">
         <v>16674.6094733327</v>
@@ -21778,13 +21778,13 @@
         <v>0.028608137195997</v>
       </c>
       <c r="L189" t="n">
-        <v>0.0839586635099914</v>
+        <v>0.0839586635099912</v>
       </c>
       <c r="M189" t="n">
         <v>0.0429122057939955</v>
       </c>
       <c r="N189" t="n">
-        <v>0.0110345672041702</v>
+        <v>0.0110345672041703</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -21805,13 +21805,13 @@
         <v>1464.30750237711</v>
       </c>
       <c r="U189" t="n">
-        <v>4297.42419175891</v>
+        <v>4297.4241917589</v>
       </c>
       <c r="V189" t="n">
         <v>2196.46125356566</v>
       </c>
       <c r="W189" t="n">
-        <v>564.804322345454</v>
+        <v>564.804322345455</v>
       </c>
       <c r="X189" t="n">
         <v>307.504575499192</v>
@@ -21876,13 +21876,13 @@
         <v>0.330534280669528</v>
       </c>
       <c r="K190" t="n">
-        <v>0.0539815467119206</v>
+        <v>0.0539815467119207</v>
       </c>
       <c r="L190" t="n">
         <v>0.0231085388321578</v>
       </c>
       <c r="M190" t="n">
-        <v>0.0570450787170982</v>
+        <v>0.0570450787170981</v>
       </c>
       <c r="N190" t="n">
         <v>0.00133105183673229</v>
@@ -21891,13 +21891,13 @@
         <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>0.00853238356879674</v>
+        <v>0.00853238356879673</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.0583761305538305</v>
+        <v>0.0583761305538304</v>
       </c>
       <c r="R190" t="n">
-        <v>0.00950751311951633</v>
+        <v>0.00950751311951636</v>
       </c>
       <c r="S190" t="n">
         <v>17230.2888850086</v>
@@ -21906,22 +21906,22 @@
         <v>1960.06996110984</v>
       </c>
       <c r="U190" t="n">
-        <v>839.071044995651</v>
+        <v>839.07104499565</v>
       </c>
       <c r="V190" t="n">
-        <v>2071.30680821784</v>
+        <v>2071.30680821783</v>
       </c>
       <c r="W190" t="n">
         <v>48.3304921917494</v>
       </c>
       <c r="X190" t="n">
-        <v>309.81084738301</v>
+        <v>309.810847383009</v>
       </c>
       <c r="Y190" t="n">
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>345.217801369638</v>
+        <v>345.217801369639</v>
       </c>
       <c r="AA190" t="n">
         <v>0.00973333333333333</v>
@@ -21980,7 +21980,7 @@
         <v>0.0383530727349929</v>
       </c>
       <c r="L191" t="n">
-        <v>0.0510613329467862</v>
+        <v>0.0510613329467861</v>
       </c>
       <c r="M191" t="n">
         <v>0.0561126236566152</v>
@@ -21998,7 +21998,7 @@
         <v>0.0787135415183074</v>
       </c>
       <c r="R191" t="n">
-        <v>0.00774888612400877</v>
+        <v>0.00774888612400876</v>
       </c>
       <c r="S191" t="n">
         <v>23683.06299018</v>
@@ -22010,7 +22010,7 @@
         <v>1945.64103060434</v>
       </c>
       <c r="V191" t="n">
-        <v>2138.11541181167</v>
+        <v>2138.11541181166</v>
       </c>
       <c r="W191" t="n">
         <v>861.18537420192</v>
@@ -22081,7 +22081,7 @@
         <v>0.0607042770670587</v>
       </c>
       <c r="L192" t="n">
-        <v>0.0235653249483923</v>
+        <v>0.0235653249483924</v>
       </c>
       <c r="M192" t="n">
         <v>0.0548977809997748</v>
@@ -22093,7 +22093,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="n">
-        <v>0.00703817705125316</v>
+        <v>0.00703817705125318</v>
       </c>
       <c r="Q192" t="n">
         <v>0.0591206872305267</v>
@@ -22108,7 +22108,7 @@
         <v>2308.40154402904</v>
       </c>
       <c r="U192" t="n">
-        <v>896.118611812515</v>
+        <v>896.118611812516</v>
       </c>
       <c r="V192" t="n">
         <v>2087.59791807844</v>
@@ -22117,7 +22117,7 @@
         <v>160.584455236803</v>
       </c>
       <c r="X192" t="n">
-        <v>267.640758728004</v>
+        <v>267.640758728005</v>
       </c>
       <c r="Y192" t="n">
         <v>0</v>
@@ -22212,7 +22212,7 @@
         <v>1424.23057023831</v>
       </c>
       <c r="V193" t="n">
-        <v>1846.94987210731</v>
+        <v>1846.94987210732</v>
       </c>
       <c r="W193" t="n">
         <v>0</v>
@@ -22313,7 +22313,7 @@
         <v>2114.14242380206</v>
       </c>
       <c r="V194" t="n">
-        <v>2131.90832652308</v>
+        <v>2131.90832652309</v>
       </c>
       <c r="W194" t="n">
         <v>0</v>
@@ -22384,7 +22384,7 @@
         <v>0.0196360716113191</v>
       </c>
       <c r="L195" t="n">
-        <v>0.0783296845697429</v>
+        <v>0.0783296845697428</v>
       </c>
       <c r="M195" t="n">
         <v>0.0403942044575707</v>
@@ -22396,7 +22396,7 @@
         <v>0</v>
       </c>
       <c r="P195" t="n">
-        <v>0.00900221048083396</v>
+        <v>0.00900221048083397</v>
       </c>
       <c r="Q195" t="n">
         <v>0.0456304902205891</v>
@@ -22485,7 +22485,7 @@
         <v>0.0269985879052669</v>
       </c>
       <c r="L196" t="n">
-        <v>0.0851118275049757</v>
+        <v>0.0851118275049758</v>
       </c>
       <c r="M196" t="n">
         <v>0.0479974896093634</v>
@@ -22586,7 +22586,7 @@
         <v>0.034432947330086</v>
       </c>
       <c r="L197" t="n">
-        <v>0.0826515492977609</v>
+        <v>0.0826515492977608</v>
       </c>
       <c r="M197" t="n">
         <v>0.068865894660172</v>
@@ -22604,7 +22604,7 @@
         <v>0.068865894660172</v>
       </c>
       <c r="R197" t="n">
-        <v>0.0105947530246419</v>
+        <v>0.0105947530246418</v>
       </c>
       <c r="S197" t="n">
         <v>20627.5974121058</v>
@@ -22622,13 +22622,13 @@
         <v>0</v>
       </c>
       <c r="X197" t="n">
-        <v>790.624468353697</v>
+        <v>790.624468353696</v>
       </c>
       <c r="Y197" t="n">
         <v>0</v>
       </c>
       <c r="Z197" t="n">
-        <v>398.076655394869</v>
+        <v>398.076655394868</v>
       </c>
       <c r="AA197" t="n">
         <v>0.006</v>
@@ -22684,13 +22684,13 @@
         <v>0.424757257468179</v>
       </c>
       <c r="K198" t="n">
-        <v>0.031673392603946</v>
+        <v>0.0316733926039461</v>
       </c>
       <c r="L198" t="n">
         <v>0.0454315225162851</v>
       </c>
       <c r="M198" t="n">
-        <v>0.0334636278380821</v>
+        <v>0.0334636278380822</v>
       </c>
       <c r="N198" t="n">
         <v>0.0142530266717757</v>
@@ -22788,7 +22788,7 @@
         <v>0.0166186036516509</v>
       </c>
       <c r="L199" t="n">
-        <v>0.035251583503502</v>
+        <v>0.0352515835035019</v>
       </c>
       <c r="M199" t="n">
         <v>0.0348990676684669</v>
@@ -22800,7 +22800,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>0.00904790643256552</v>
+        <v>0.0090479064325655</v>
       </c>
       <c r="Q199" t="n">
         <v>0.0465320902246225</v>
@@ -22812,7 +22812,7 @@
         <v>32024.604347925</v>
       </c>
       <c r="T199" t="n">
-        <v>934.198185673903</v>
+        <v>934.198185673904</v>
       </c>
       <c r="U199" t="n">
         <v>1981.63251506586</v>
@@ -22824,7 +22824,7 @@
         <v>653.938729971733</v>
       </c>
       <c r="X199" t="n">
-        <v>508.619012200238</v>
+        <v>508.619012200237</v>
       </c>
       <c r="Y199" t="n">
         <v>0</v>
@@ -22889,7 +22889,7 @@
         <v>0.052152324631263</v>
       </c>
       <c r="L200" t="n">
-        <v>0.0991988272706544</v>
+        <v>0.0991988272706542</v>
       </c>
       <c r="M200" t="n">
         <v>0.0430321329850025</v>
@@ -22907,7 +22907,7 @@
         <v>0.0632609134480379</v>
       </c>
       <c r="R200" t="n">
-        <v>0.0245079455609851</v>
+        <v>0.0245079455609852</v>
       </c>
       <c r="S200" t="n">
         <v>30735.567962715</v>
@@ -22916,16 +22916,16 @@
         <v>2336.16338185743</v>
       </c>
       <c r="U200" t="n">
-        <v>4443.61146758896</v>
+        <v>4443.61146758895</v>
       </c>
       <c r="V200" t="n">
         <v>1927.62439706319</v>
       </c>
       <c r="W200" t="n">
-        <v>906.14822084167</v>
+        <v>906.148220841669</v>
       </c>
       <c r="X200" t="n">
-        <v>871.296366193911</v>
+        <v>871.296366193912</v>
       </c>
       <c r="Y200" t="n">
         <v>0</v>
@@ -22987,16 +22987,16 @@
         <v>0.202670163188334</v>
       </c>
       <c r="K201" t="n">
-        <v>0.0400141042053314</v>
+        <v>0.0400141042053316</v>
       </c>
       <c r="L201" t="n">
         <v>0.0223203675020365</v>
       </c>
       <c r="M201" t="n">
-        <v>0.0417213726514258</v>
+        <v>0.0417213726514257</v>
       </c>
       <c r="N201" t="n">
-        <v>0.00906986361987517</v>
+        <v>0.00906986361987515</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -23005,7 +23005,7 @@
         <v>0.00850299714363296</v>
       </c>
       <c r="Q201" t="n">
-        <v>0.050791236271301</v>
+        <v>0.0507912362713009</v>
       </c>
       <c r="R201" t="n">
         <v>0.0125582727044425</v>
@@ -23014,13 +23014,13 @@
         <v>14494.8622180122</v>
       </c>
       <c r="T201" t="n">
-        <v>1788.47040156149</v>
+        <v>1788.4704015615</v>
       </c>
       <c r="U201" t="n">
         <v>997.631145871024</v>
       </c>
       <c r="V201" t="n">
-        <v>1864.77847202813</v>
+        <v>1864.77847202812</v>
       </c>
       <c r="W201" t="n">
         <v>405.38662435394</v>
@@ -23091,7 +23091,7 @@
         <v>0.0255470999478817</v>
       </c>
       <c r="L202" t="n">
-        <v>0.0850021689174971</v>
+        <v>0.0850021689174972</v>
       </c>
       <c r="M202" t="n">
         <v>0.0487717362641377</v>
@@ -23284,7 +23284,7 @@
         <v>19984.0295328361</v>
       </c>
       <c r="I204" t="n">
-        <v>0.739967503958039</v>
+        <v>0.73996750395804</v>
       </c>
       <c r="J204" t="n">
         <v>0.538449898497496</v>
@@ -23293,7 +23293,7 @@
         <v>0.02839454201373</v>
       </c>
       <c r="L204" t="n">
-        <v>0.0934978841149775</v>
+        <v>0.0934978841149777</v>
       </c>
       <c r="M204" t="n">
         <v>0.0520394515451633</v>
@@ -23320,7 +23320,7 @@
         <v>1053.83503229757</v>
       </c>
       <c r="U204" t="n">
-        <v>3470.08047104327</v>
+        <v>3470.08047104328</v>
       </c>
       <c r="V204" t="n">
         <v>1931.39220464719</v>
@@ -23329,7 +23329,7 @@
         <v>0</v>
       </c>
       <c r="X204" t="n">
-        <v>17.8832611541406</v>
+        <v>17.8832611541407</v>
       </c>
       <c r="Y204" t="n">
         <v>1005.93343992041</v>
@@ -23400,19 +23400,19 @@
         <v>0.0417993672026376</v>
       </c>
       <c r="N205" t="n">
-        <v>0.00680732551585813</v>
+        <v>0.00680732551585812</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
       </c>
       <c r="P205" t="n">
-        <v>0.0100276259703298</v>
+        <v>0.0100276259703297</v>
       </c>
       <c r="Q205" t="n">
         <v>0.0486066927184957</v>
       </c>
       <c r="R205" t="n">
-        <v>0.00907643402114415</v>
+        <v>0.00907643402114416</v>
       </c>
       <c r="S205" t="n">
         <v>26304.6162054238</v>
@@ -23427,16 +23427,16 @@
         <v>2052.1817321807</v>
       </c>
       <c r="W205" t="n">
-        <v>334.212453526571</v>
+        <v>334.21245352657</v>
       </c>
       <c r="X205" t="n">
-        <v>492.31632463931</v>
+        <v>492.316324639308</v>
       </c>
       <c r="Y205" t="n">
         <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>445.616604702093</v>
+        <v>445.616604702094</v>
       </c>
       <c r="AA205" t="n">
         <v>0.005</v>
@@ -23486,7 +23486,7 @@
         <v>11349.0241561157</v>
       </c>
       <c r="I206" t="n">
-        <v>0.492410179099396</v>
+        <v>0.492410179099397</v>
       </c>
       <c r="J206" t="n">
         <v>0.315926402475174</v>
@@ -23495,13 +23495,13 @@
         <v>0.0311862754912579</v>
       </c>
       <c r="L206" t="n">
-        <v>0.0579105146429973</v>
+        <v>0.0579105146429974</v>
       </c>
       <c r="M206" t="n">
         <v>0.0508960016017329</v>
       </c>
       <c r="N206" t="n">
-        <v>0.0248273178545038</v>
+        <v>0.0248273178545039</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -23537,7 +23537,7 @@
         <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>507.871407094182</v>
+        <v>507.871407094181</v>
       </c>
       <c r="AA206" t="n">
         <v>0.00588235294117647</v>
@@ -23593,10 +23593,10 @@
         <v>0.38662558664895</v>
       </c>
       <c r="K207" t="n">
-        <v>0.0460427007882519</v>
+        <v>0.0460427007882518</v>
       </c>
       <c r="L207" t="n">
-        <v>0.0982443602533735</v>
+        <v>0.0982443602533737</v>
       </c>
       <c r="M207" t="n">
         <v>0.0311416085331449</v>
@@ -23623,16 +23623,16 @@
         <v>2149.73369980348</v>
       </c>
       <c r="U207" t="n">
-        <v>4587.02918023001</v>
+        <v>4587.02918023002</v>
       </c>
       <c r="V207" t="n">
         <v>1454.00170241253</v>
       </c>
       <c r="W207" t="n">
-        <v>894.770278407712</v>
+        <v>894.770278407713</v>
       </c>
       <c r="X207" t="n">
-        <v>571.214954519211</v>
+        <v>571.21495451921</v>
       </c>
       <c r="Y207" t="n">
         <v>0</v>
@@ -23703,19 +23703,19 @@
         <v>0.0423683895254581</v>
       </c>
       <c r="N208" t="n">
-        <v>0.00805920452929911</v>
+        <v>0.0080592045292991</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
       </c>
       <c r="P208" t="n">
-        <v>0.00869598118346595</v>
+        <v>0.00869598118346594</v>
       </c>
       <c r="Q208" t="n">
         <v>0.0504275940547572</v>
       </c>
       <c r="R208" t="n">
-        <v>0.00764693499067161</v>
+        <v>0.00764693499067159</v>
       </c>
       <c r="S208" t="n">
         <v>19302.5024055813</v>
@@ -23739,7 +23739,7 @@
         <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>340.563896744551</v>
+        <v>340.56389674455</v>
       </c>
       <c r="AA208" t="n">
         <v>0.00702702702702703</v>
@@ -23789,7 +23789,7 @@
         <v>28058.3066214532</v>
       </c>
       <c r="I209" t="n">
-        <v>0.601227556586616</v>
+        <v>0.601227556586617</v>
       </c>
       <c r="J209" t="n">
         <v>0.505864973523478</v>
@@ -23813,7 +23813,7 @@
         <v>0.00509343179612785</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.0360698129235992</v>
+        <v>0.0360698129235993</v>
       </c>
       <c r="R209" t="n">
         <v>0.0109144967059883</v>
@@ -23825,22 +23825,22 @@
         <v>941.707626680092</v>
       </c>
       <c r="U209" t="n">
-        <v>2064.51287387558</v>
+        <v>2064.51287387559</v>
       </c>
       <c r="V209" t="n">
-        <v>1153.11137960827</v>
+        <v>1153.11137960828</v>
       </c>
       <c r="W209" t="n">
         <v>847.536864012083</v>
       </c>
       <c r="X209" t="n">
-        <v>282.512288004027</v>
+        <v>282.512288004028</v>
       </c>
       <c r="Y209" t="n">
         <v>0</v>
       </c>
       <c r="Z209" t="n">
-        <v>605.383474294347</v>
+        <v>605.383474294345</v>
       </c>
       <c r="AA209" t="n">
         <v>0.002</v>
@@ -23899,10 +23899,10 @@
         <v>0.0451989512603587</v>
       </c>
       <c r="L210" t="n">
-        <v>0.05738494302173</v>
+        <v>0.0573849430217299</v>
       </c>
       <c r="M210" t="n">
-        <v>0.0561341814039939</v>
+        <v>0.0561341814039938</v>
       </c>
       <c r="N210" t="n">
         <v>0.00460207503741834</v>
@@ -23914,7 +23914,7 @@
         <v>0.0118647247058442</v>
       </c>
       <c r="Q210" t="n">
-        <v>0.0607362564414123</v>
+        <v>0.0607362564414122</v>
       </c>
       <c r="R210" t="n">
         <v>0.0126557063529004</v>
@@ -23926,10 +23926,10 @@
         <v>1888.54778051157</v>
       </c>
       <c r="U210" t="n">
-        <v>2397.71507427695</v>
+        <v>2397.71507427694</v>
       </c>
       <c r="V210" t="n">
-        <v>2345.45450160308</v>
+        <v>2345.45450160307</v>
       </c>
       <c r="W210" t="n">
         <v>192.28850128845</v>
@@ -24027,7 +24027,7 @@
         <v>1112.47778926664</v>
       </c>
       <c r="U211" t="n">
-        <v>3275.2654913409</v>
+        <v>3275.26549134091</v>
       </c>
       <c r="V211" t="n">
         <v>1484.89014011205</v>
@@ -24125,7 +24125,7 @@
         <v>72333.0019364016</v>
       </c>
       <c r="T212" t="n">
-        <v>1610.96314623764</v>
+        <v>1610.96314623763</v>
       </c>
       <c r="U212" t="n">
         <v>9665.77887742579</v>
@@ -24137,7 +24137,7 @@
         <v>644.385258495053</v>
       </c>
       <c r="X212" t="n">
-        <v>577.061425517957</v>
+        <v>577.061425517958</v>
       </c>
       <c r="Y212" t="n">
         <v>0</v>
@@ -24202,7 +24202,7 @@
         <v>0.0362852341565601</v>
       </c>
       <c r="L213" t="n">
-        <v>0.049580026428498</v>
+        <v>0.0495800264284981</v>
       </c>
       <c r="M213" t="n">
         <v>0.0482314497096429</v>
@@ -24238,7 +24238,7 @@
         <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>674.99467281148</v>
+        <v>674.994672811479</v>
       </c>
       <c r="Y213" t="n">
         <v>0</v>
@@ -24300,10 +24300,10 @@
         <v>0.294857751695498</v>
       </c>
       <c r="K214" t="n">
-        <v>0.0488319439895618</v>
+        <v>0.0488319439895619</v>
       </c>
       <c r="L214" t="n">
-        <v>0.0633514549351104</v>
+        <v>0.0633514549351103</v>
       </c>
       <c r="M214" t="n">
         <v>0.0445270226115347</v>
@@ -24330,13 +24330,13 @@
         <v>2088.88406804149</v>
       </c>
       <c r="U214" t="n">
-        <v>2709.98518775922</v>
+        <v>2709.98518775921</v>
       </c>
       <c r="V214" t="n">
         <v>1904.73244625362</v>
       </c>
       <c r="W214" t="n">
-        <v>461.753320303907</v>
+        <v>461.753320303908</v>
       </c>
       <c r="X214" t="n">
         <v>317.455407708937</v>
@@ -24401,7 +24401,7 @@
         <v>0.433522082023685</v>
       </c>
       <c r="K215" t="n">
-        <v>0.0249030228905141</v>
+        <v>0.0249030228905142</v>
       </c>
       <c r="L215" t="n">
         <v>0.0342931476872005</v>
@@ -24428,10 +24428,10 @@
         <v>22118.1170740681</v>
       </c>
       <c r="T215" t="n">
-        <v>992.260947072536</v>
+        <v>992.260947072537</v>
       </c>
       <c r="U215" t="n">
-        <v>1366.4104695965</v>
+        <v>1366.41046959651</v>
       </c>
       <c r="V215" t="n">
         <v>2426.60633078449</v>
@@ -24440,13 +24440,13 @@
         <v>0</v>
       </c>
       <c r="X215" t="n">
-        <v>59.151968380801</v>
+        <v>59.1519683808011</v>
       </c>
       <c r="Y215" t="n">
         <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>891.829677125925</v>
+        <v>891.829677125924</v>
       </c>
       <c r="AA215" t="n">
         <v>0.00342342342342342</v>
@@ -24511,13 +24511,13 @@
         <v>0.056342272032876</v>
       </c>
       <c r="N216" t="n">
-        <v>0.0000695248855895012</v>
+        <v>0.0000695248855895014</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
       </c>
       <c r="P216" t="n">
-        <v>0.0068316246953443</v>
+        <v>0.00683162469534432</v>
       </c>
       <c r="Q216" t="n">
         <v>0.0564117969184655</v>
@@ -24538,7 +24538,7 @@
         <v>2009.10907842033</v>
       </c>
       <c r="W216" t="n">
-        <v>2.47918789523602</v>
+        <v>2.47918789523603</v>
       </c>
       <c r="X216" t="n">
         <v>243.608905011283</v>
@@ -24603,16 +24603,16 @@
         <v>0.445081033885656</v>
       </c>
       <c r="K217" t="n">
-        <v>0.0231170593330347</v>
+        <v>0.0231170593330346</v>
       </c>
       <c r="L217" t="n">
-        <v>0.107598307456236</v>
+        <v>0.107598307456237</v>
       </c>
       <c r="M217" t="n">
         <v>0.0358492243195368</v>
       </c>
       <c r="N217" t="n">
-        <v>0.0081475509817129</v>
+        <v>0.00814755098171291</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -24627,19 +24627,19 @@
         <v>0.0291274947596236</v>
       </c>
       <c r="S217" t="n">
-        <v>37733.1874477281</v>
+        <v>37733.1874477282</v>
       </c>
       <c r="T217" t="n">
         <v>1393.93556072266</v>
       </c>
       <c r="U217" t="n">
-        <v>6488.0703413036</v>
+        <v>6488.07034130362</v>
       </c>
       <c r="V217" t="n">
         <v>2161.67237724375</v>
       </c>
       <c r="W217" t="n">
-        <v>491.289176646306</v>
+        <v>491.289176646307</v>
       </c>
       <c r="X217" t="n">
         <v>360.278729540625</v>
@@ -24725,7 +24725,7 @@
         <v>0.0422353919093644</v>
       </c>
       <c r="R218" t="n">
-        <v>0.0901719799717837</v>
+        <v>0.0901719799717835</v>
       </c>
       <c r="S218" t="n">
         <v>43742.4662714724</v>
@@ -24734,7 +24734,7 @@
         <v>1188.42833657695</v>
       </c>
       <c r="U218" t="n">
-        <v>8116.4005124772</v>
+        <v>8116.40051247719</v>
       </c>
       <c r="V218" t="n">
         <v>2112.76148724791</v>
@@ -24749,7 +24749,7 @@
         <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>5954.14600951685</v>
+        <v>5954.14600951684</v>
       </c>
       <c r="AA218" t="n">
         <v>0.00225</v>
@@ -24805,10 +24805,10 @@
         <v>0.366005578295344</v>
       </c>
       <c r="K219" t="n">
-        <v>0.0450408572732792</v>
+        <v>0.0450408572732793</v>
       </c>
       <c r="L219" t="n">
-        <v>0.0837536602189075</v>
+        <v>0.0837536602189077</v>
       </c>
       <c r="M219" t="n">
         <v>0.0417651585624953</v>
@@ -24823,10 +24823,10 @@
         <v>0.00737032209926388</v>
       </c>
       <c r="Q219" t="n">
-        <v>0.0586116090750984</v>
+        <v>0.0586116090750985</v>
       </c>
       <c r="R219" t="n">
-        <v>0.00765085339023933</v>
+        <v>0.00765085339023932</v>
       </c>
       <c r="S219" t="n">
         <v>24633.4720983551</v>
@@ -24835,13 +24835,13 @@
         <v>1978.50973744334</v>
       </c>
       <c r="U219" t="n">
-        <v>3679.04703243595</v>
+        <v>3679.04703243596</v>
       </c>
       <c r="V219" t="n">
         <v>1834.61812017473</v>
       </c>
       <c r="W219" t="n">
-        <v>740.014031667118</v>
+        <v>740.014031667119</v>
       </c>
       <c r="X219" t="n">
         <v>323.756138854364</v>
@@ -25001,7 +25001,7 @@
         <v>11691.2791358436</v>
       </c>
       <c r="I221" t="n">
-        <v>0.381313931664145</v>
+        <v>0.381313931664144</v>
       </c>
       <c r="J221" t="n">
         <v>0.246209942841816</v>
@@ -25010,7 +25010,7 @@
         <v>0.0247893701221523</v>
       </c>
       <c r="L221" t="n">
-        <v>0.0490022432647197</v>
+        <v>0.0490022432647196</v>
       </c>
       <c r="M221" t="n">
         <v>0.0356966929758993</v>
@@ -25037,7 +25037,7 @@
         <v>1177.1232402504</v>
       </c>
       <c r="U221" t="n">
-        <v>2326.87152142522</v>
+        <v>2326.87152142521</v>
       </c>
       <c r="V221" t="n">
         <v>1695.05746596058</v>
@@ -25052,7 +25052,7 @@
         <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>2017.92555471498</v>
+        <v>2017.92555471497</v>
       </c>
       <c r="AA221" t="n">
         <v>0.006</v>
@@ -25129,7 +25129,7 @@
         <v>0.0588658622351626</v>
       </c>
       <c r="R222" t="n">
-        <v>0.0120134412724821</v>
+        <v>0.0120134412724822</v>
       </c>
       <c r="S222" t="n">
         <v>18715.7420873552</v>
@@ -25153,7 +25153,7 @@
         <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>477.486236816075</v>
+        <v>477.486236816076</v>
       </c>
       <c r="AA222" t="n">
         <v>0.00681818181818182</v>
@@ -25215,7 +25215,7 @@
         <v>0.0774213292455303</v>
       </c>
       <c r="M223" t="n">
-        <v>0.0384768642324638</v>
+        <v>0.0384768642324637</v>
       </c>
       <c r="N223" t="n">
         <v>0.00731060420416811</v>
@@ -25227,7 +25227,7 @@
         <v>0.00338453898341116</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.0457874684366319</v>
+        <v>0.0457874684366318</v>
       </c>
       <c r="R223" t="n">
         <v>0.0146212084083362</v>
@@ -25331,7 +25331,7 @@
         <v>0.0514451735459789</v>
       </c>
       <c r="R224" t="n">
-        <v>0.00988877477771677</v>
+        <v>0.00988877477771676</v>
       </c>
       <c r="S224" t="n">
         <v>20317.1900449429</v>
@@ -25450,7 +25450,7 @@
         <v>378.308499783698</v>
       </c>
       <c r="X225" t="n">
-        <v>683.424445996193</v>
+        <v>683.424445996191</v>
       </c>
       <c r="Y225" t="n">
         <v>0</v>
@@ -25509,7 +25509,7 @@
         <v>0.626829476267886</v>
       </c>
       <c r="J226" t="n">
-        <v>0.470275874852751</v>
+        <v>0.470275874852752</v>
       </c>
       <c r="K226" t="n">
         <v>0.0555627489406356</v>
@@ -25533,7 +25533,7 @@
         <v>0.0378715696779372</v>
       </c>
       <c r="R226" t="n">
-        <v>0.0896958229214305</v>
+        <v>0.0896958229214303</v>
       </c>
       <c r="S226" t="n">
         <v>37973.3296723086</v>
@@ -25557,7 +25557,7 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>5433.77295258026</v>
+        <v>5433.77295258025</v>
       </c>
       <c r="AA226" t="n">
         <v>0.00704225352112676</v>
@@ -25622,7 +25622,7 @@
         <v>0.0647962084645994</v>
       </c>
       <c r="N227" t="n">
-        <v>0.00852581690323674</v>
+        <v>0.00852581690323676</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -25717,7 +25717,7 @@
         <v>0.0299454550372347</v>
       </c>
       <c r="L228" t="n">
-        <v>0.073972403812217</v>
+        <v>0.0739724038122167</v>
       </c>
       <c r="M228" t="n">
         <v>0.0561477281948151</v>
@@ -25735,16 +25735,16 @@
         <v>0.072118637548007</v>
       </c>
       <c r="R228" t="n">
-        <v>0.0855584429635277</v>
+        <v>0.0855584429635278</v>
       </c>
       <c r="S228" t="n">
         <v>21854.0615308652</v>
       </c>
       <c r="T228" t="n">
-        <v>1169.48980102416</v>
+        <v>1169.48980102417</v>
       </c>
       <c r="U228" t="n">
-        <v>2888.91825848232</v>
+        <v>2888.91825848231</v>
       </c>
       <c r="V228" t="n">
         <v>2192.79337692031</v>
@@ -25818,10 +25818,10 @@
         <v>0.0413616066189249</v>
       </c>
       <c r="L229" t="n">
-        <v>0.056977723403621</v>
+        <v>0.0569777234036211</v>
       </c>
       <c r="M229" t="n">
-        <v>0.042543366808037</v>
+        <v>0.0425433668080371</v>
       </c>
       <c r="N229" t="n">
         <v>0.00850867336160741</v>
@@ -25830,7 +25830,7 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>0.00559781142211015</v>
+        <v>0.00559781142211014</v>
       </c>
       <c r="Q229" t="n">
         <v>0.0510520401696445</v>
@@ -25845,7 +25845,7 @@
         <v>2553.91376229214</v>
       </c>
       <c r="U229" t="n">
-        <v>3518.14650927998</v>
+        <v>3518.14650927999</v>
       </c>
       <c r="V229" t="n">
         <v>2626.88272692906</v>
@@ -25910,7 +25910,7 @@
         <v>22970.5497917818</v>
       </c>
       <c r="I230" t="n">
-        <v>0.670484039141627</v>
+        <v>0.670484039141628</v>
       </c>
       <c r="J230" t="n">
         <v>0.471422850055038</v>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="X230" t="n">
-        <v>702.608194187595</v>
+        <v>702.608194187596</v>
       </c>
       <c r="Y230" t="n">
         <v>0</v>
@@ -26020,7 +26020,7 @@
         <v>0.0350284101635188</v>
       </c>
       <c r="L231" t="n">
-        <v>0.0725640785257844</v>
+        <v>0.0725640785257847</v>
       </c>
       <c r="M231" t="n">
         <v>0.0292215614198338</v>
@@ -26032,13 +26032,13 @@
         <v>0</v>
       </c>
       <c r="P231" t="n">
-        <v>0.00752676582026022</v>
+        <v>0.00752676582026023</v>
       </c>
       <c r="Q231" t="n">
         <v>0.0429824075178165</v>
       </c>
       <c r="R231" t="n">
-        <v>0.070915994880396</v>
+        <v>0.0709159948803961</v>
       </c>
       <c r="S231" t="n">
         <v>32488.633542144</v>
@@ -26047,13 +26047,13 @@
         <v>1999.07136803202</v>
       </c>
       <c r="U231" t="n">
-        <v>4141.23196146651</v>
+        <v>4141.23196146653</v>
       </c>
       <c r="V231" t="n">
         <v>1667.67451022992</v>
       </c>
       <c r="W231" t="n">
-        <v>785.33148681187</v>
+        <v>785.331486811872</v>
       </c>
       <c r="X231" t="n">
         <v>429.552525362251</v>
@@ -26062,7 +26062,7 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>4047.1758278242</v>
+        <v>4047.17582782421</v>
       </c>
       <c r="AA231" t="n">
         <v>0.00507692307692308</v>
@@ -26121,7 +26121,7 @@
         <v>0.0379069640520415</v>
       </c>
       <c r="L232" t="n">
-        <v>0.0560187977989365</v>
+        <v>0.0560187977989367</v>
       </c>
       <c r="M232" t="n">
         <v>0.0334473212223895</v>
@@ -26139,22 +26139,22 @@
         <v>0.0456099834850766</v>
       </c>
       <c r="R232" t="n">
-        <v>0.10291483453043</v>
+        <v>0.102914834530429</v>
       </c>
       <c r="S232" t="n">
-        <v>23479.0309887203</v>
+        <v>23479.0309887204</v>
       </c>
       <c r="T232" t="n">
         <v>1831.7782238868</v>
       </c>
       <c r="U232" t="n">
-        <v>2706.99636603801</v>
+        <v>2706.99636603802</v>
       </c>
       <c r="V232" t="n">
         <v>1616.27490342953</v>
       </c>
       <c r="W232" t="n">
-        <v>587.736328519828</v>
+        <v>587.736328519829</v>
       </c>
       <c r="X232" t="n">
         <v>682.427181448023</v>
@@ -26163,7 +26163,7 @@
         <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>4973.15354901395</v>
+        <v>4973.15354901394</v>
       </c>
       <c r="AA232" t="n">
         <v>0.0068</v>
@@ -26326,7 +26326,7 @@
         <v>0.0206115598129148</v>
       </c>
       <c r="M234" t="n">
-        <v>0.0667306804500235</v>
+        <v>0.0667306804500233</v>
       </c>
       <c r="N234" t="n">
         <v>0.00551640291720192</v>
@@ -26338,28 +26338,28 @@
         <v>0.0108876373365827</v>
       </c>
       <c r="Q234" t="n">
-        <v>0.0722470833672255</v>
+        <v>0.0722470833672252</v>
       </c>
       <c r="R234" t="n">
         <v>0.0068955036465024</v>
       </c>
       <c r="S234" t="n">
-        <v>16936.3978126106</v>
+        <v>16936.3978126105</v>
       </c>
       <c r="T234" t="n">
         <v>1641.27352419354</v>
       </c>
       <c r="U234" t="n">
-        <v>706.461212587654</v>
+        <v>706.461212587655</v>
       </c>
       <c r="V234" t="n">
-        <v>2287.19407242456</v>
+        <v>2287.19407242455</v>
       </c>
       <c r="W234" t="n">
         <v>189.074709987096</v>
       </c>
       <c r="X234" t="n">
-        <v>373.173769711373</v>
+        <v>373.173769711374</v>
       </c>
       <c r="Y234" t="n">
         <v>0</v>
@@ -26457,7 +26457,7 @@
         <v>2095.66888861094</v>
       </c>
       <c r="W235" t="n">
-        <v>669.234180066703</v>
+        <v>669.234180066704</v>
       </c>
       <c r="X235" t="n">
         <v>855.555059744366</v>
@@ -26531,7 +26531,7 @@
         <v>0.0452800814243982</v>
       </c>
       <c r="N236" t="n">
-        <v>0.00807055860284773</v>
+        <v>0.00807055860284772</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -26540,7 +26540,7 @@
         <v>0.010491726183702</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.0533506400272459</v>
+        <v>0.053350640027246</v>
       </c>
       <c r="R236" t="n">
         <v>0.0262293154592551</v>
@@ -26552,13 +26552,13 @@
         <v>1322.27225093197</v>
       </c>
       <c r="U236" t="n">
-        <v>555.955378232758</v>
+        <v>555.955378232759</v>
       </c>
       <c r="V236" t="n">
         <v>1711.99459857507</v>
       </c>
       <c r="W236" t="n">
-        <v>305.13975021507</v>
+        <v>305.139750215069</v>
       </c>
       <c r="X236" t="n">
         <v>396.68167527959</v>
@@ -26733,7 +26733,7 @@
         <v>0.0619149380065502</v>
       </c>
       <c r="N238" t="n">
-        <v>0.00728411035371177</v>
+        <v>0.00728411035371179</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -26745,7 +26745,7 @@
         <v>0.069199048360262</v>
       </c>
       <c r="R238" t="n">
-        <v>0.00855966884883184</v>
+        <v>0.00855966884883183</v>
       </c>
       <c r="S238" t="n">
         <v>17986.612748369</v>
@@ -26760,7 +26760,7 @@
         <v>2545.32310144928</v>
       </c>
       <c r="W238" t="n">
-        <v>299.449776641091</v>
+        <v>299.449776641092</v>
       </c>
       <c r="X238" t="n">
         <v>424.220516908213</v>
@@ -26769,7 +26769,7 @@
         <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>351.887986375477</v>
+        <v>351.887986375476</v>
       </c>
       <c r="AA238" t="n">
         <v>0.00666666666666667</v>
@@ -26828,10 +26828,10 @@
         <v>0.0254397166083637</v>
       </c>
       <c r="L239" t="n">
-        <v>0.0300329987737626</v>
+        <v>0.0300329987737627</v>
       </c>
       <c r="M239" t="n">
-        <v>0.0496074473863091</v>
+        <v>0.0496074473863092</v>
       </c>
       <c r="N239" t="n">
         <v>0.0200839867960766</v>
@@ -26843,7 +26843,7 @@
         <v>0.0127198583041818</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.0696914341823858</v>
+        <v>0.0696914341823857</v>
       </c>
       <c r="R239" t="n">
         <v>0.0127198583041818</v>
@@ -26861,7 +26861,7 @@
         <v>1773.36702916578</v>
       </c>
       <c r="W239" t="n">
-        <v>717.962359986147</v>
+        <v>717.962359986146</v>
       </c>
       <c r="X239" t="n">
         <v>454.709494657892</v>
@@ -26929,7 +26929,7 @@
         <v>0.0327403572439567</v>
       </c>
       <c r="L240" t="n">
-        <v>0.0283747290037691</v>
+        <v>0.028374729003769</v>
       </c>
       <c r="M240" t="n">
         <v>0.0546178341419112</v>
@@ -27042,7 +27042,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="n">
-        <v>0.00989284727938552</v>
+        <v>0.00989284727938549</v>
       </c>
       <c r="Q241" t="n">
         <v>0.0338605181880785</v>
@@ -27066,7 +27066,7 @@
         <v>643.201452864301</v>
       </c>
       <c r="X241" t="n">
-        <v>628.908087245097</v>
+        <v>628.908087245095</v>
       </c>
       <c r="Y241" t="n">
         <v>0</v>
@@ -27173,7 +27173,7 @@
         <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>1194.52000101165</v>
+        <v>1194.52000101166</v>
       </c>
       <c r="AA242" t="n">
         <v>0.0065</v>
@@ -27223,16 +27223,16 @@
         <v>15148.4800063993</v>
       </c>
       <c r="I243" t="n">
-        <v>0.693352149819933</v>
+        <v>0.693352149819932</v>
       </c>
       <c r="J243" t="n">
         <v>0.485325986172406</v>
       </c>
       <c r="K243" t="n">
-        <v>0.0361952301084772</v>
+        <v>0.0361952301084773</v>
       </c>
       <c r="L243" t="n">
-        <v>0.0841999208879411</v>
+        <v>0.0841999208879408</v>
       </c>
       <c r="M243" t="n">
         <v>0.049571728192045</v>
@@ -27253,13 +27253,13 @@
         <v>0.0195454242585777</v>
       </c>
       <c r="S243" t="n">
-        <v>21641.6006523296</v>
+        <v>21641.6006523295</v>
       </c>
       <c r="T243" t="n">
         <v>1129.7617173759</v>
       </c>
       <c r="U243" t="n">
-        <v>2628.13213067531</v>
+        <v>2628.1321306753</v>
       </c>
       <c r="V243" t="n">
         <v>1547.2823520583</v>
@@ -27553,7 +27553,7 @@
         <v>0.0291288333292624</v>
       </c>
       <c r="R246" t="n">
-        <v>0.0916577511933994</v>
+        <v>0.0916577511933995</v>
       </c>
       <c r="S246" t="n">
         <v>41665.7059746236</v>
@@ -27571,7 +27571,7 @@
         <v>0</v>
       </c>
       <c r="X246" t="n">
-        <v>104.071559738203</v>
+        <v>104.071559738202</v>
       </c>
       <c r="Y246" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
         <v>0.0261090979490126</v>
       </c>
       <c r="L247" t="n">
-        <v>0.0322816292576107</v>
+        <v>0.0322816292576106</v>
       </c>
       <c r="M247" t="n">
         <v>0.033229761026016</v>
@@ -27672,7 +27672,7 @@
         <v>165.614055200769</v>
       </c>
       <c r="X247" t="n">
-        <v>386.43279546846</v>
+        <v>386.432795468461</v>
       </c>
       <c r="Y247" t="n">
         <v>0</v>
@@ -27734,7 +27734,7 @@
         <v>0.364325040845167</v>
       </c>
       <c r="K248" t="n">
-        <v>0.0407555648283802</v>
+        <v>0.0407555648283801</v>
       </c>
       <c r="L248" t="n">
         <v>0.0327500074513769</v>
@@ -27844,7 +27844,7 @@
         <v>0.0470190657978311</v>
       </c>
       <c r="N249" t="n">
-        <v>0.0080604112796282</v>
+        <v>0.00806041127962819</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -27871,7 +27871,7 @@
         <v>2433.70684569574</v>
       </c>
       <c r="W249" t="n">
-        <v>417.206887833556</v>
+        <v>417.206887833555</v>
       </c>
       <c r="X249" t="n">
         <v>481.671146543948</v>
@@ -27880,7 +27880,7 @@
         <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>6084.26711423935</v>
+        <v>6084.26711423934</v>
       </c>
       <c r="AA249" t="n">
         <v>0.0046</v>
@@ -27936,7 +27936,7 @@
         <v>0.381332678502876</v>
       </c>
       <c r="K250" t="n">
-        <v>0.0914064204072269</v>
+        <v>0.0914064204072268</v>
       </c>
       <c r="L250" t="n">
         <v>0.0319922471425294</v>
@@ -27963,7 +27963,7 @@
         <v>23758.282247795</v>
       </c>
       <c r="T250" t="n">
-        <v>3738.61400107599</v>
+        <v>3738.61400107598</v>
       </c>
       <c r="U250" t="n">
         <v>1308.51490037659</v>
@@ -27981,7 +27981,7 @@
         <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>697.874613534185</v>
+        <v>697.874613534184</v>
       </c>
       <c r="AA250" t="n">
         <v>0.0142857142857143</v>
@@ -28052,7 +28052,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="n">
-        <v>0.00717354886158272</v>
+        <v>0.00717354886158271</v>
       </c>
       <c r="Q251" t="n">
         <v>0.0484691606824968</v>
@@ -28061,7 +28061,7 @@
         <v>0.139453789869168</v>
       </c>
       <c r="S251" t="n">
-        <v>60030.0266383631</v>
+        <v>60030.026638363</v>
       </c>
       <c r="T251" t="n">
         <v>1922.02329358158</v>
@@ -28073,7 +28073,7 @@
         <v>2505.25794818565</v>
       </c>
       <c r="W251" t="n">
-        <v>741.351841810039</v>
+        <v>741.351841810038</v>
       </c>
       <c r="X251" t="n">
         <v>480.505823395395</v>
@@ -28132,7 +28132,7 @@
         <v>16524.74480976</v>
       </c>
       <c r="I252" t="n">
-        <v>0.729010279641311</v>
+        <v>0.729010279641312</v>
       </c>
       <c r="J252" t="n">
         <v>0.51179214599108</v>
@@ -28141,7 +28141,7 @@
         <v>0.0381694959374555</v>
       </c>
       <c r="L252" t="n">
-        <v>0.0895358920660524</v>
+        <v>0.0895358920660525</v>
       </c>
       <c r="M252" t="n">
         <v>0.0607497661657187</v>
@@ -28156,7 +28156,7 @@
         <v>0.00815145167477863</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.0813612939719447</v>
+        <v>0.0813612939719446</v>
       </c>
       <c r="R252" t="n">
         <v>0.0437994965882302</v>
@@ -28171,13 +28171,13 @@
         <v>2890.9348830287</v>
       </c>
       <c r="V252" t="n">
-        <v>1961.48844995873</v>
+        <v>1961.48844995872</v>
       </c>
       <c r="W252" t="n">
         <v>665.505009807424</v>
       </c>
       <c r="X252" t="n">
-        <v>263.194071675252</v>
+        <v>263.194071675253</v>
       </c>
       <c r="Y252" t="n">
         <v>0</v>
@@ -28328,7 +28328,7 @@
         <v>57103</v>
       </c>
       <c r="G254" t="n">
-        <v>423150.005991713</v>
+        <v>423150.005991714</v>
       </c>
       <c r="H254" t="n">
         <v>25217.5412241064</v>
@@ -28355,7 +28355,7 @@
         <v>0.00463143361548117</v>
       </c>
       <c r="P254" t="n">
-        <v>0.00271710772108229</v>
+        <v>0.00271710772108228</v>
       </c>
       <c r="Q254" t="n">
         <v>0.0535393725949623</v>
@@ -28370,7 +28370,7 @@
         <v>2031.12002876022</v>
       </c>
       <c r="U254" t="n">
-        <v>6825.00009664053</v>
+        <v>6825.00009664054</v>
       </c>
       <c r="V254" t="n">
         <v>2792.79003954531</v>
@@ -28441,7 +28441,7 @@
         <v>0.328100500010532</v>
       </c>
       <c r="K255" t="n">
-        <v>0.0300257338576873</v>
+        <v>0.0300257338576874</v>
       </c>
       <c r="L255" t="n">
         <v>0.0385330251173654</v>
@@ -28468,7 +28468,7 @@
         <v>21783.2517007283</v>
       </c>
       <c r="T255" t="n">
-        <v>1507.41194259133</v>
+        <v>1507.41194259134</v>
       </c>
       <c r="U255" t="n">
         <v>1934.51199299221</v>
@@ -28542,7 +28542,7 @@
         <v>0.262151315062795</v>
       </c>
       <c r="K256" t="n">
-        <v>0.0347842859637993</v>
+        <v>0.0347842859637992</v>
       </c>
       <c r="L256" t="n">
         <v>0.0549898638398297</v>
@@ -28551,7 +28551,7 @@
         <v>0.0431920385069208</v>
       </c>
       <c r="N256" t="n">
-        <v>0.00918091639760634</v>
+        <v>0.00918091639760635</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -28569,7 +28569,7 @@
         <v>23585.4202387103</v>
       </c>
       <c r="T256" t="n">
-        <v>1977.55622561392</v>
+        <v>1977.55622561391</v>
       </c>
       <c r="U256" t="n">
         <v>3126.283739022</v>
@@ -28643,7 +28643,7 @@
         <v>0.483707944217235</v>
       </c>
       <c r="K257" t="n">
-        <v>0.0177103890012007</v>
+        <v>0.0177103890012008</v>
       </c>
       <c r="L257" t="n">
         <v>0.0413668140532854</v>
@@ -28658,7 +28658,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="n">
-        <v>0.00878421097754943</v>
+        <v>0.00878421097754947</v>
       </c>
       <c r="Q257" t="n">
         <v>0.0353423329467228</v>
@@ -28679,16 +28679,16 @@
         <v>1341.35927379573</v>
       </c>
       <c r="W257" t="n">
-        <v>917.439909495213</v>
+        <v>917.439909495212</v>
       </c>
       <c r="X257" t="n">
-        <v>561.416491997139</v>
+        <v>561.416491997142</v>
       </c>
       <c r="Y257" t="n">
         <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>1521.78524670237</v>
+        <v>1521.78524670238</v>
       </c>
       <c r="AA257" t="n">
         <v>0.00218181818181818</v>
@@ -28759,13 +28759,13 @@
         <v>0</v>
       </c>
       <c r="P258" t="n">
-        <v>0.00793411199219449</v>
+        <v>0.00793411199219451</v>
       </c>
       <c r="Q258" t="n">
         <v>0.0555082681300069</v>
       </c>
       <c r="R258" t="n">
-        <v>0.0073237956851026</v>
+        <v>0.00732379568510262</v>
       </c>
       <c r="S258" t="n">
         <v>22368.2272057603</v>
@@ -28789,7 +28789,7 @@
         <v>0</v>
       </c>
       <c r="Z258" t="n">
-        <v>348.832388481437</v>
+        <v>348.832388481438</v>
       </c>
       <c r="AA258" t="n">
         <v>0.01</v>
@@ -28860,13 +28860,13 @@
         <v>0</v>
       </c>
       <c r="P259" t="n">
-        <v>0.00778244108389873</v>
+        <v>0.00778244108389872</v>
       </c>
       <c r="Q259" t="n">
         <v>0.0301531442780076</v>
       </c>
       <c r="R259" t="n">
-        <v>0.00938834162502066</v>
+        <v>0.00938834162502068</v>
       </c>
       <c r="S259" t="n">
         <v>39839.4276807979</v>
@@ -28890,7 +28890,7 @@
         <v>0</v>
       </c>
       <c r="Z259" t="n">
-        <v>612.279475758972</v>
+        <v>612.279475758974</v>
       </c>
       <c r="AA259" t="n">
         <v>0.00225</v>
@@ -28949,7 +28949,7 @@
         <v>0.047706106808479</v>
       </c>
       <c r="L260" t="n">
-        <v>0.0963296387478906</v>
+        <v>0.0963296387478903</v>
       </c>
       <c r="M260" t="n">
         <v>0.034075790577485</v>
@@ -28970,13 +28970,13 @@
         <v>0.00670867126994236</v>
       </c>
       <c r="S260" t="n">
-        <v>29096.1782519502</v>
+        <v>29096.1782519501</v>
       </c>
       <c r="T260" t="n">
         <v>2477.09188992346</v>
       </c>
       <c r="U260" t="n">
-        <v>5001.82016234547</v>
+        <v>5001.82016234546</v>
       </c>
       <c r="V260" t="n">
         <v>1769.35134994533</v>
@@ -28985,7 +28985,7 @@
         <v>1161.13682340162</v>
       </c>
       <c r="X260" t="n">
-        <v>233.947567381661</v>
+        <v>233.94756738166</v>
       </c>
       <c r="Y260" t="n">
         <v>0</v>
@@ -29041,7 +29041,7 @@
         <v>23289.5192430357</v>
       </c>
       <c r="I261" t="n">
-        <v>0.504671743397514</v>
+        <v>0.504671743397515</v>
       </c>
       <c r="J261" t="n">
         <v>0.379604890517598</v>
@@ -29151,7 +29151,7 @@
         <v>0.0272553139667054</v>
       </c>
       <c r="L262" t="n">
-        <v>0.0921870913579742</v>
+        <v>0.092187091357974</v>
       </c>
       <c r="M262" t="n">
         <v>0.0507075608682891</v>
@@ -29175,10 +29175,10 @@
         <v>26240.7847545485</v>
       </c>
       <c r="T262" t="n">
-        <v>1207.76472780662</v>
+        <v>1207.76472780661</v>
       </c>
       <c r="U262" t="n">
-        <v>4085.08657934591</v>
+        <v>4085.0865793459</v>
       </c>
       <c r="V262" t="n">
         <v>2247.00414475649</v>
@@ -29187,7 +29187,7 @@
         <v>103.522690954853</v>
       </c>
       <c r="X262" t="n">
-        <v>603.882363903308</v>
+        <v>603.882363903307</v>
       </c>
       <c r="Y262" t="n">
         <v>0</v>
@@ -29264,10 +29264,10 @@
         <v>0</v>
       </c>
       <c r="P263" t="n">
-        <v>0.00969661841256878</v>
+        <v>0.00969661841256879</v>
       </c>
       <c r="Q263" t="n">
-        <v>0.0700192971066368</v>
+        <v>0.0700192971066367</v>
       </c>
       <c r="R263" t="n">
         <v>0.00459619712755761</v>
@@ -29285,7 +29285,7 @@
         <v>1799.17157925961</v>
       </c>
       <c r="W263" t="n">
-        <v>534.011438927737</v>
+        <v>534.011438927736</v>
       </c>
       <c r="X263" t="n">
         <v>323.110718743617</v>
@@ -29457,7 +29457,7 @@
         <v>0.0342139665157161</v>
       </c>
       <c r="M265" t="n">
-        <v>0.0522184544595984</v>
+        <v>0.0522184544595985</v>
       </c>
       <c r="N265" t="n">
         <v>0.0110964215726647</v>
@@ -29469,7 +29469,7 @@
         <v>0.00554821078633234</v>
       </c>
       <c r="Q265" t="n">
-        <v>0.063314876032263</v>
+        <v>0.0633148760322632</v>
       </c>
       <c r="R265" t="n">
         <v>0.00924701797722056</v>
@@ -29484,7 +29484,7 @@
         <v>1281.72361361176</v>
       </c>
       <c r="V265" t="n">
-        <v>1956.20774096547</v>
+        <v>1956.20774096548</v>
       </c>
       <c r="W265" t="n">
         <v>415.694144955164</v>
@@ -29552,7 +29552,7 @@
         <v>0.396873531841055</v>
       </c>
       <c r="K266" t="n">
-        <v>0.0463207056997295</v>
+        <v>0.0463207056997294</v>
       </c>
       <c r="L266" t="n">
         <v>0.0435370094437361</v>
@@ -29579,10 +29579,10 @@
         <v>27398.1562816974</v>
       </c>
       <c r="T266" t="n">
-        <v>2404.69311569576</v>
+        <v>2404.69311569575</v>
       </c>
       <c r="U266" t="n">
-        <v>2260.18030826212</v>
+        <v>2260.18030826211</v>
       </c>
       <c r="V266" t="n">
         <v>1803.51983677182</v>
@@ -29680,7 +29680,7 @@
         <v>27294.1645695363</v>
       </c>
       <c r="T267" t="n">
-        <v>2300.31812443518</v>
+        <v>2300.31812443517</v>
       </c>
       <c r="U267" t="n">
         <v>2091.85179440824</v>
@@ -29790,10 +29790,10 @@
         <v>1477.64502742983</v>
       </c>
       <c r="W268" t="n">
-        <v>973.507312189061</v>
+        <v>973.507312189062</v>
       </c>
       <c r="X268" t="n">
-        <v>407.808842695686</v>
+        <v>407.808842695687</v>
       </c>
       <c r="Y268" t="n">
         <v>0</v>
@@ -29870,13 +29870,13 @@
         <v>0</v>
       </c>
       <c r="P269" t="n">
-        <v>0.00805699162541054</v>
+        <v>0.00805699162541055</v>
       </c>
       <c r="Q269" t="n">
         <v>0.0448285030065283</v>
       </c>
       <c r="R269" t="n">
-        <v>0.00821575008108369</v>
+        <v>0.00821575008108366</v>
       </c>
       <c r="S269" t="n">
         <v>25329.3324512611</v>
@@ -29900,7 +29900,7 @@
         <v>0</v>
       </c>
       <c r="Z269" t="n">
-        <v>398.357074181505</v>
+        <v>398.357074181504</v>
       </c>
       <c r="AA269" t="n">
         <v>0.008</v>
@@ -29950,7 +29950,7 @@
         <v>10192.0907370285</v>
       </c>
       <c r="I270" t="n">
-        <v>0.422143114684027</v>
+        <v>0.422143114684026</v>
       </c>
       <c r="J270" t="n">
         <v>0.242121172040112</v>
@@ -29959,13 +29959,13 @@
         <v>0.0304740637442457</v>
       </c>
       <c r="L270" t="n">
-        <v>0.0840989666120271</v>
+        <v>0.0840989666120268</v>
       </c>
       <c r="M270" t="n">
         <v>0.0511964270903328</v>
       </c>
       <c r="N270" t="n">
-        <v>0.00450078479915014</v>
+        <v>0.00450078479915013</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -29977,7 +29977,7 @@
         <v>0.0556972118894829</v>
       </c>
       <c r="R270" t="n">
-        <v>0.0113391865094867</v>
+        <v>0.0113391865094868</v>
       </c>
       <c r="S270" t="n">
         <v>17770.1144126241</v>
@@ -29986,7 +29986,7 @@
         <v>1282.80571331402</v>
       </c>
       <c r="U270" t="n">
-        <v>3540.14599953328</v>
+        <v>3540.14599953327</v>
       </c>
       <c r="V270" t="n">
         <v>2155.11359836756</v>
@@ -30158,7 +30158,7 @@
         <v>0.404589872885174</v>
       </c>
       <c r="K272" t="n">
-        <v>0.0171971754250837</v>
+        <v>0.0171971754250838</v>
       </c>
       <c r="L272" t="n">
         <v>0.0263523242252632</v>
@@ -30167,13 +30167,13 @@
         <v>0.0325841218580535</v>
       </c>
       <c r="N272" t="n">
-        <v>0.000756082278124497</v>
+        <v>0.0007560822781245</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
       </c>
       <c r="P272" t="n">
-        <v>0.0085953319050021</v>
+        <v>0.00859533190500211</v>
       </c>
       <c r="Q272" t="n">
         <v>0.0333402041361779</v>
@@ -30185,7 +30185,7 @@
         <v>32502.748086624</v>
       </c>
       <c r="T272" t="n">
-        <v>1140.5510685424</v>
+        <v>1140.55106854241</v>
       </c>
       <c r="U272" t="n">
         <v>1747.73884726791</v>
@@ -30194,10 +30194,10 @@
         <v>2161.04412986982</v>
       </c>
       <c r="W272" t="n">
-        <v>50.1448888497729</v>
+        <v>50.1448888497731</v>
       </c>
       <c r="X272" t="n">
-        <v>570.059602603549</v>
+        <v>570.05960260355</v>
       </c>
       <c r="Y272" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>0.0473801567590039</v>
       </c>
       <c r="N273" t="n">
-        <v>0.00842313897937848</v>
+        <v>0.00842313897937847</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -30277,13 +30277,13 @@
         <v>0.00947603135180078</v>
       </c>
       <c r="Q273" t="n">
-        <v>0.0558032957383824</v>
+        <v>0.0558032957383823</v>
       </c>
       <c r="R273" t="n">
-        <v>0.00334448165357673</v>
+        <v>0.00334448165357674</v>
       </c>
       <c r="S273" t="n">
-        <v>9603.49658607213</v>
+        <v>9603.49658607212</v>
       </c>
       <c r="T273" t="n">
         <v>890.482407860702</v>
@@ -30381,7 +30381,7 @@
         <v>0.0666310290555671</v>
       </c>
       <c r="R274" t="n">
-        <v>0.0298290071934807</v>
+        <v>0.0298290071934806</v>
       </c>
       <c r="S274" t="n">
         <v>31829.4996758557</v>
@@ -30405,7 +30405,7 @@
         <v>0</v>
       </c>
       <c r="Z274" t="n">
-        <v>1282.19987421177</v>
+        <v>1282.19987421176</v>
       </c>
       <c r="AA274" t="n">
         <v>0.00366666666666667</v>
@@ -30464,7 +30464,7 @@
         <v>0.0208801809389819</v>
       </c>
       <c r="L275" t="n">
-        <v>0.0650497944637516</v>
+        <v>0.0650497944637514</v>
       </c>
       <c r="M275" t="n">
         <v>0.0375843256901675</v>
@@ -30491,22 +30491,22 @@
         <v>942.322565776255</v>
       </c>
       <c r="U275" t="n">
-        <v>2935.69722414911</v>
+        <v>2935.6972241491</v>
       </c>
       <c r="V275" t="n">
         <v>1696.18061839726</v>
       </c>
       <c r="W275" t="n">
-        <v>770.991190180571</v>
+        <v>770.991190180572</v>
       </c>
       <c r="X275" t="n">
-        <v>575.863790196599</v>
+        <v>575.8637901966</v>
       </c>
       <c r="Y275" t="n">
         <v>0</v>
       </c>
       <c r="Z275" t="n">
-        <v>879.50106139117</v>
+        <v>879.501061391171</v>
       </c>
       <c r="AA275" t="n">
         <v>0.004</v>
@@ -30562,7 +30562,7 @@
         <v>0.646709090014284</v>
       </c>
       <c r="K276" t="n">
-        <v>0.0362625644626995</v>
+        <v>0.0362625644626994</v>
       </c>
       <c r="L276" t="n">
         <v>0.135635938230674</v>
@@ -30598,7 +30598,7 @@
         <v>1908.91224543487</v>
       </c>
       <c r="W276" t="n">
-        <v>674.936829635898</v>
+        <v>674.9368296359</v>
       </c>
       <c r="X276" t="n">
         <v>365.590782719446</v>
@@ -30699,7 +30699,7 @@
         <v>1275.30255631765</v>
       </c>
       <c r="W277" t="n">
-        <v>472.334280117647</v>
+        <v>472.334280117648</v>
       </c>
       <c r="X277" t="n">
         <v>304.655610675883</v>
@@ -30708,7 +30708,7 @@
         <v>0</v>
       </c>
       <c r="Z277" t="n">
-        <v>455.465198684876</v>
+        <v>455.465198684875</v>
       </c>
       <c r="AA277" t="n">
         <v>0.00314285714285714</v>
@@ -30803,10 +30803,10 @@
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>9.10524357721888</v>
+        <v>9.10524357721886</v>
       </c>
       <c r="Y278" t="n">
-        <v>449.19201647613</v>
+        <v>449.192016476131</v>
       </c>
       <c r="Z278" t="n">
         <v>3059.36184194554</v>
@@ -30904,7 +30904,7 @@
         <v>514.302027426163</v>
       </c>
       <c r="X279" t="n">
-        <v>854.312812224569</v>
+        <v>854.312812224572</v>
       </c>
       <c r="Y279" t="n">
         <v>0</v>
@@ -31097,7 +31097,7 @@
         <v>1938.17914234192</v>
       </c>
       <c r="U281" t="n">
-        <v>5624.1805469743</v>
+        <v>5624.18054697431</v>
       </c>
       <c r="V281" t="n">
         <v>2309.66347795745</v>
@@ -31106,7 +31106,7 @@
         <v>629.908221261123</v>
       </c>
       <c r="X281" t="n">
-        <v>437.436264764668</v>
+        <v>437.436264764669</v>
       </c>
       <c r="Y281" t="n">
         <v>0</v>
@@ -31156,7 +31156,7 @@
         <v>65331</v>
       </c>
       <c r="G282" t="n">
-        <v>548014.295037365</v>
+        <v>548014.295037364</v>
       </c>
       <c r="H282" t="n">
         <v>32656.8089160868</v>
@@ -31204,7 +31204,7 @@
         <v>1409.17961581037</v>
       </c>
       <c r="W282" t="n">
-        <v>848.538263283659</v>
+        <v>848.538263283661</v>
       </c>
       <c r="X282" t="n">
         <v>521.918376226061</v>
@@ -31492,7 +31492,7 @@
         <v>0.0717092624428343</v>
       </c>
       <c r="R285" t="n">
-        <v>0.0882169942382155</v>
+        <v>0.0882169942382153</v>
       </c>
       <c r="S285" t="n">
         <v>27784.0892412322</v>
@@ -31501,7 +31501,7 @@
         <v>1236.34483776817</v>
       </c>
       <c r="U285" t="n">
-        <v>4425.55254428379</v>
+        <v>4425.5525442838</v>
       </c>
       <c r="V285" t="n">
         <v>2813.75032043791</v>
@@ -31516,7 +31516,7 @@
         <v>0</v>
       </c>
       <c r="Z285" t="n">
-        <v>3793.33075224327</v>
+        <v>3793.33075224326</v>
       </c>
       <c r="AA285" t="n">
         <v>0.004</v>
@@ -31578,7 +31578,7 @@
         <v>0.0442338398352324</v>
       </c>
       <c r="M286" t="n">
-        <v>0.0300861744628302</v>
+        <v>0.0300861744628301</v>
       </c>
       <c r="N286" t="n">
         <v>0.00489974841251805</v>
@@ -31611,7 +31611,7 @@
         <v>318.228859896222</v>
       </c>
       <c r="X286" t="n">
-        <v>428.59105709929</v>
+        <v>428.591057099289</v>
       </c>
       <c r="Y286" t="n">
         <v>0</v>
@@ -31676,7 +31676,7 @@
         <v>0.0421004138422466</v>
       </c>
       <c r="L287" t="n">
-        <v>0.0774789128693444</v>
+        <v>0.0774789128693446</v>
       </c>
       <c r="M287" t="n">
         <v>0.0378903724580219</v>
@@ -31703,7 +31703,7 @@
         <v>2116.97720964353</v>
       </c>
       <c r="U287" t="n">
-        <v>3895.94965472211</v>
+        <v>3895.94965472212</v>
       </c>
       <c r="V287" t="n">
         <v>1905.27948867918</v>
@@ -31777,7 +31777,7 @@
         <v>0.0276346145148904</v>
       </c>
       <c r="L288" t="n">
-        <v>0.105995781700949</v>
+        <v>0.10599578170095</v>
       </c>
       <c r="M288" t="n">
         <v>0.0530584598685896</v>
@@ -31804,7 +31804,7 @@
         <v>1170.46409777818</v>
       </c>
       <c r="U288" t="n">
-        <v>4489.45133394371</v>
+        <v>4489.45133394372</v>
       </c>
       <c r="V288" t="n">
         <v>2247.29106773411</v>
@@ -31985,7 +31985,7 @@
         <v>0.032617067374009</v>
       </c>
       <c r="N290" t="n">
-        <v>0.000716819096772679</v>
+        <v>0.00071681909677268</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -32015,7 +32015,7 @@
         <v>45.3775161020977</v>
       </c>
       <c r="X290" t="n">
-        <v>754.817403589295</v>
+        <v>754.817403589296</v>
       </c>
       <c r="Y290" t="n">
         <v>0</v>
@@ -32080,7 +32080,7 @@
         <v>0.0241006641066426</v>
       </c>
       <c r="L291" t="n">
-        <v>0.0509919314256333</v>
+        <v>0.0509919314256332</v>
       </c>
       <c r="M291" t="n">
         <v>0.0404891156991595</v>
@@ -32092,7 +32092,7 @@
         <v>0</v>
       </c>
       <c r="P291" t="n">
-        <v>0.00761073603367662</v>
+        <v>0.0076107360336766</v>
       </c>
       <c r="Q291" t="n">
         <v>0.0404891156991595</v>
@@ -32122,7 +32122,7 @@
         <v>0</v>
       </c>
       <c r="Z291" t="n">
-        <v>883.08779069885</v>
+        <v>883.087790698852</v>
       </c>
       <c r="AA291" t="n">
         <v>0.00333333333333333</v>
@@ -32172,7 +32172,7 @@
         <v>34923.278183686</v>
       </c>
       <c r="I292" t="n">
-        <v>0.714453532305358</v>
+        <v>0.714453532305357</v>
       </c>
       <c r="J292" t="n">
         <v>0.547773165770308</v>
@@ -32211,7 +32211,7 @@
         <v>5859.59814458883</v>
       </c>
       <c r="V292" t="n">
-        <v>2083.41267363159</v>
+        <v>2083.41267363158</v>
       </c>
       <c r="W292" t="n">
         <v>562.521421880528</v>
@@ -32279,7 +32279,7 @@
         <v>0.356998477785356</v>
       </c>
       <c r="K293" t="n">
-        <v>0.0234681521106</v>
+        <v>0.0234681521105999</v>
       </c>
       <c r="L293" t="n">
         <v>0.044112265821288</v>
@@ -32288,7 +32288,7 @@
         <v>0.0451858976878378</v>
       </c>
       <c r="N293" t="n">
-        <v>0.00668713073604364</v>
+        <v>0.00668713073604365</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -32306,10 +32306,10 @@
         <v>24062.0852021192</v>
       </c>
       <c r="T293" t="n">
-        <v>1179.18077094921</v>
+        <v>1179.1807709492</v>
       </c>
       <c r="U293" t="n">
-        <v>2216.46490845643</v>
+        <v>2216.46490845644</v>
       </c>
       <c r="V293" t="n">
         <v>2270.4106152231</v>
@@ -32380,10 +32380,10 @@
         <v>0.349018219954725</v>
       </c>
       <c r="K294" t="n">
-        <v>0.0312357604708457</v>
+        <v>0.0312357604708458</v>
       </c>
       <c r="L294" t="n">
-        <v>0.0628264727652237</v>
+        <v>0.0628264727652239</v>
       </c>
       <c r="M294" t="n">
         <v>0.0304548664590746</v>
@@ -32404,19 +32404,19 @@
         <v>0.0430751212944728</v>
       </c>
       <c r="S294" t="n">
-        <v>28498.2001526031</v>
+        <v>28498.2001526032</v>
       </c>
       <c r="T294" t="n">
         <v>1813.32960261401</v>
       </c>
       <c r="U294" t="n">
-        <v>3647.26522343953</v>
+        <v>3647.26522343954</v>
       </c>
       <c r="V294" t="n">
         <v>1767.99636254866</v>
       </c>
       <c r="W294" t="n">
-        <v>829.82880119624</v>
+        <v>829.828801196242</v>
       </c>
       <c r="X294" t="n">
         <v>178.22543977305</v>
@@ -32502,7 +32502,7 @@
         <v>0.0538541912759356</v>
       </c>
       <c r="R295" t="n">
-        <v>0.0694679371495483</v>
+        <v>0.0694679371495484</v>
       </c>
       <c r="S295" t="n">
         <v>26161.7862026355</v>
@@ -32585,7 +32585,7 @@
         <v>0.0343002821256094</v>
       </c>
       <c r="L296" t="n">
-        <v>0.109173351672946</v>
+        <v>0.109173351672947</v>
       </c>
       <c r="M296" t="n">
         <v>0.0382771264300279</v>
@@ -32597,7 +32597,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="n">
-        <v>0.00898340722337387</v>
+        <v>0.00898340722337389</v>
       </c>
       <c r="Q296" t="n">
         <v>0.0616339852108</v>
@@ -32618,7 +32618,7 @@
         <v>1579.69700776725</v>
       </c>
       <c r="W296" t="n">
-        <v>963.937561882466</v>
+        <v>963.937561882465</v>
       </c>
       <c r="X296" t="n">
         <v>370.74521610864</v>
@@ -32677,7 +32677,7 @@
         <v>12027.8898888188</v>
       </c>
       <c r="I297" t="n">
-        <v>0.414463758227883</v>
+        <v>0.414463758227882</v>
       </c>
       <c r="J297" t="n">
         <v>0.289459001487709</v>
@@ -32689,7 +32689,7 @@
         <v>0.0361355696976965</v>
       </c>
       <c r="M297" t="n">
-        <v>0.0567043266244331</v>
+        <v>0.0567043266244329</v>
       </c>
       <c r="N297" t="n">
         <v>0</v>
@@ -32701,7 +32701,7 @@
         <v>0.00373586197490032</v>
       </c>
       <c r="Q297" t="n">
-        <v>0.0567043266244331</v>
+        <v>0.0567043266244329</v>
       </c>
       <c r="R297" t="n">
         <v>0.011207585924701</v>
@@ -32716,7 +32716,7 @@
         <v>1501.54132764838</v>
       </c>
       <c r="V297" t="n">
-        <v>2356.23488422507</v>
+        <v>2356.23488422506</v>
       </c>
       <c r="W297" t="n">
         <v>0</v>
@@ -32802,7 +32802,7 @@
         <v>0.00798130825341734</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.0675424997772188</v>
+        <v>0.0675424997772189</v>
       </c>
       <c r="R298" t="n">
         <v>0.013682242720144</v>
@@ -32820,7 +32820,7 @@
         <v>2352.99196416015</v>
       </c>
       <c r="W298" t="n">
-        <v>450.764744091982</v>
+        <v>450.764744091983</v>
       </c>
       <c r="X298" t="n">
         <v>331.312086907607</v>
@@ -32873,7 +32873,7 @@
         <v>65382</v>
       </c>
       <c r="G299" t="n">
-        <v>586587.277266274</v>
+        <v>586587.277266273</v>
       </c>
       <c r="H299" t="n">
         <v>34960.683164546</v>
@@ -32918,13 +32918,13 @@
         <v>5865.87277266273</v>
       </c>
       <c r="V299" t="n">
-        <v>1877.07928725208</v>
+        <v>1877.07928725207</v>
       </c>
       <c r="W299" t="n">
         <v>610.050768356924</v>
       </c>
       <c r="X299" t="n">
-        <v>828.123214964149</v>
+        <v>828.123214964151</v>
       </c>
       <c r="Y299" t="n">
         <v>0</v>
@@ -32989,7 +32989,7 @@
         <v>0.0299271382720127</v>
       </c>
       <c r="L300" t="n">
-        <v>0.0669422829768704</v>
+        <v>0.0669422829768706</v>
       </c>
       <c r="M300" t="n">
         <v>0.0598542765440255</v>
@@ -33016,7 +33016,7 @@
         <v>1042.24251746112</v>
       </c>
       <c r="U300" t="n">
-        <v>2331.33194695249</v>
+        <v>2331.3319469525</v>
       </c>
       <c r="V300" t="n">
         <v>2084.48503492223</v>
@@ -33025,7 +33025,7 @@
         <v>347.414172487039</v>
       </c>
       <c r="X300" t="n">
-        <v>393.736062151978</v>
+        <v>393.736062151977</v>
       </c>
       <c r="Y300" t="n">
         <v>0</v>
@@ -33093,7 +33093,7 @@
         <v>0.074559234514604</v>
       </c>
       <c r="M301" t="n">
-        <v>0.0482988537873968</v>
+        <v>0.0482988537873967</v>
       </c>
       <c r="N301" t="n">
         <v>0.0101367964738981</v>
@@ -33114,7 +33114,7 @@
         <v>26693.8594328664</v>
       </c>
       <c r="T301" t="n">
-        <v>1943.20276572027</v>
+        <v>1943.20276572028</v>
       </c>
       <c r="U301" t="n">
         <v>3118.43998357331</v>
@@ -33123,7 +33123,7 @@
         <v>2020.09955965787</v>
       </c>
       <c r="W301" t="n">
-        <v>423.971512520786</v>
+        <v>423.971512520787</v>
       </c>
       <c r="X301" t="n">
         <v>238.483975792943</v>
@@ -33215,7 +33215,7 @@
         <v>37602.3965828343</v>
       </c>
       <c r="T302" t="n">
-        <v>952.688545828611</v>
+        <v>952.68854582861</v>
       </c>
       <c r="U302" t="n">
         <v>2203.09226222866</v>
@@ -33233,7 +33233,7 @@
         <v>0</v>
       </c>
       <c r="Z302" t="n">
-        <v>1353.82056512486</v>
+        <v>1353.82056512487</v>
       </c>
       <c r="AA302" t="n">
         <v>0.00177777777777778</v>
@@ -33310,7 +33310,7 @@
         <v>0.0635280470033559</v>
       </c>
       <c r="R303" t="n">
-        <v>0.00538853970117752</v>
+        <v>0.00538853970117751</v>
       </c>
       <c r="S303" t="n">
         <v>19132.4828149661</v>
@@ -33325,16 +33325,16 @@
         <v>2040.0867614266</v>
       </c>
       <c r="W303" t="n">
-        <v>536.864937217526</v>
+        <v>536.864937217527</v>
       </c>
       <c r="X303" t="n">
-        <v>607.168678996013</v>
+        <v>607.168678996012</v>
       </c>
       <c r="Y303" t="n">
         <v>0</v>
       </c>
       <c r="Z303" t="n">
-        <v>218.580724438565</v>
+        <v>218.580724438564</v>
       </c>
       <c r="AA303" t="n">
         <v>0.0076</v>
@@ -33393,7 +33393,7 @@
         <v>0.0369218017816522</v>
       </c>
       <c r="L304" t="n">
-        <v>0.0648134193011252</v>
+        <v>0.0648134193011253</v>
       </c>
       <c r="M304" t="n">
         <v>0.0389504722092156</v>
@@ -33420,7 +33420,7 @@
         <v>1797.64868514508</v>
       </c>
       <c r="U304" t="n">
-        <v>3155.63575893318</v>
+        <v>3155.63575893319</v>
       </c>
       <c r="V304" t="n">
         <v>1896.42059092229</v>
@@ -33512,7 +33512,7 @@
         <v>0.0383495417657826</v>
       </c>
       <c r="R305" t="n">
-        <v>0.0107421685618438</v>
+        <v>0.0107421685618439</v>
       </c>
       <c r="S305" t="n">
         <v>34860.3299276728</v>
@@ -33521,7 +33521,7 @@
         <v>1029.63623391832</v>
       </c>
       <c r="U305" t="n">
-        <v>3655.31284460376</v>
+        <v>3655.31284460377</v>
       </c>
       <c r="V305" t="n">
         <v>1748.79754191666</v>
@@ -33530,13 +33530,13 @@
         <v>546.499231848957</v>
       </c>
       <c r="X305" t="n">
-        <v>738.512475471562</v>
+        <v>738.512475471563</v>
       </c>
       <c r="Y305" t="n">
         <v>0</v>
       </c>
       <c r="Z305" t="n">
-        <v>642.940272763477</v>
+        <v>642.940272763478</v>
       </c>
       <c r="AA305" t="n">
         <v>0.00226086956521739</v>
@@ -33598,7 +33598,7 @@
         <v>0.121636838475671</v>
       </c>
       <c r="M306" t="n">
-        <v>0.0324364902601791</v>
+        <v>0.032436490260179</v>
       </c>
       <c r="N306" t="n">
         <v>0</v>
@@ -33610,7 +33610,7 @@
         <v>0.0131773241681977</v>
       </c>
       <c r="Q306" t="n">
-        <v>0.0324364902601791</v>
+        <v>0.032436490260179</v>
       </c>
       <c r="R306" t="n">
         <v>0.0369775988966041</v>
@@ -33631,7 +33631,7 @@
         <v>0</v>
       </c>
       <c r="X306" t="n">
-        <v>923.664537569817</v>
+        <v>923.66453756982</v>
       </c>
       <c r="Y306" t="n">
         <v>0</v>
@@ -33696,10 +33696,10 @@
         <v>0.0381984721129199</v>
       </c>
       <c r="L307" t="n">
-        <v>0.0801093277048449</v>
+        <v>0.0801093277048448</v>
       </c>
       <c r="M307" t="n">
-        <v>0.0663720058432635</v>
+        <v>0.0663720058432636</v>
       </c>
       <c r="N307" t="n">
         <v>0</v>
@@ -33711,10 +33711,10 @@
         <v>0.00224696894781882</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.0663720058432635</v>
+        <v>0.0663720058432636</v>
       </c>
       <c r="R307" t="n">
-        <v>0.0338971315556667</v>
+        <v>0.0338971315556668</v>
       </c>
       <c r="S307" t="n">
         <v>34640.3124641319</v>
@@ -33812,7 +33812,7 @@
         <v>0.00806330629322763</v>
       </c>
       <c r="Q308" t="n">
-        <v>0.0336458745528461</v>
+        <v>0.0336458745528462</v>
       </c>
       <c r="R308" t="n">
         <v>0.0393654748264241</v>
@@ -33830,10 +33830,10 @@
         <v>1268.09388042906</v>
       </c>
       <c r="W308" t="n">
-        <v>932.71641994716</v>
+        <v>932.716419947163</v>
       </c>
       <c r="X308" t="n">
-        <v>527.428927946313</v>
+        <v>527.428927946312</v>
       </c>
       <c r="Y308" t="n">
         <v>0</v>
@@ -33895,7 +33895,7 @@
         <v>0.288167748549334</v>
       </c>
       <c r="K309" t="n">
-        <v>0.0433134866074142</v>
+        <v>0.0433134866074141</v>
       </c>
       <c r="L309" t="n">
         <v>0.0570727375197027</v>
@@ -33904,7 +33904,7 @@
         <v>0.0493340612458447</v>
       </c>
       <c r="N309" t="n">
-        <v>0.0062746023842092</v>
+        <v>0.00627460238420918</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
@@ -34011,13 +34011,13 @@
         <v>0</v>
       </c>
       <c r="P310" t="n">
-        <v>0.00871385082505743</v>
+        <v>0.00871385082505744</v>
       </c>
       <c r="Q310" t="n">
         <v>0.0415888334832287</v>
       </c>
       <c r="R310" t="n">
-        <v>0.00950601908188082</v>
+        <v>0.00950601908188084</v>
       </c>
       <c r="S310" t="n">
         <v>24727.5603436451</v>
@@ -34041,7 +34041,7 @@
         <v>0</v>
       </c>
       <c r="Z310" t="n">
-        <v>485.082647729296</v>
+        <v>485.082647729297</v>
       </c>
       <c r="AA310" t="n">
         <v>0.00571428571428571</v>
@@ -34106,7 +34106,7 @@
         <v>0.0235251052683761</v>
       </c>
       <c r="N311" t="n">
-        <v>0.00212896880256798</v>
+        <v>0.00212896880256797</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -34142,7 +34142,7 @@
         <v>0</v>
       </c>
       <c r="Z311" t="n">
-        <v>3706.65314717778</v>
+        <v>3706.65314717779</v>
       </c>
       <c r="AA311" t="n">
         <v>0.0018</v>
@@ -34314,13 +34314,13 @@
         <v>0</v>
       </c>
       <c r="P313" t="n">
-        <v>0.0085265305737383</v>
+        <v>0.00852653057373829</v>
       </c>
       <c r="Q313" t="n">
         <v>0.0269345349432962</v>
       </c>
       <c r="R313" t="n">
-        <v>0.053520376524388</v>
+        <v>0.0535203765243881</v>
       </c>
       <c r="S313" t="n">
         <v>84034.2161855255</v>
@@ -34391,7 +34391,7 @@
         <v>1605115.17098401</v>
       </c>
       <c r="H314" t="n">
-        <v>95646.2845140265</v>
+        <v>95646.2845140264</v>
       </c>
       <c r="I314" t="n">
         <v>0.959288788231032</v>
@@ -34501,7 +34501,7 @@
         <v>0.832043525062576</v>
       </c>
       <c r="K315" t="n">
-        <v>0.0247229201412861</v>
+        <v>0.0247229201412862</v>
       </c>
       <c r="L315" t="n">
         <v>0.139611784327263</v>
@@ -34528,7 +34528,7 @@
         <v>67932.2794614431</v>
       </c>
       <c r="T315" t="n">
-        <v>1606.52007370091</v>
+        <v>1606.52007370092</v>
       </c>
       <c r="U315" t="n">
         <v>9072.11335736989</v>
@@ -34721,7 +34721,7 @@
         <v>0.00801947754346986</v>
       </c>
       <c r="Q317" t="n">
-        <v>0.0354243838856282</v>
+        <v>0.0354243838856281</v>
       </c>
       <c r="R317" t="n">
         <v>0.0200486938586746</v>
@@ -34736,7 +34736,7 @@
         <v>2762.056619546</v>
       </c>
       <c r="V317" t="n">
-        <v>1177.15378394002</v>
+        <v>1177.15378394001</v>
       </c>
       <c r="W317" t="n">
         <v>798.782924816438</v>
@@ -34950,7 +34950,7 @@
         <v>0</v>
       </c>
       <c r="Z319" t="n">
-        <v>2968.36859368294</v>
+        <v>2968.36859368295</v>
       </c>
       <c r="AA319" t="n">
         <v>0.00215384615384615</v>
@@ -35021,7 +35021,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="n">
-        <v>0.00990012964513164</v>
+        <v>0.00990012964513161</v>
       </c>
       <c r="Q320" t="n">
         <v>0.0439141464973338</v>
@@ -35045,13 +35045,13 @@
         <v>0</v>
       </c>
       <c r="X320" t="n">
-        <v>547.368267949683</v>
+        <v>547.368267949681</v>
       </c>
       <c r="Y320" t="n">
         <v>0</v>
       </c>
       <c r="Z320" t="n">
-        <v>959.671638613079</v>
+        <v>959.671638613078</v>
       </c>
       <c r="AA320" t="n">
         <v>0.0048</v>
@@ -35110,7 +35110,7 @@
         <v>0.0285289834068074</v>
       </c>
       <c r="L321" t="n">
-        <v>0.0709149016112069</v>
+        <v>0.070914901611207</v>
       </c>
       <c r="M321" t="n">
         <v>0.0479286921234365</v>
@@ -35137,13 +35137,13 @@
         <v>1173.0262107377</v>
       </c>
       <c r="U321" t="n">
-        <v>2915.80800954799</v>
+        <v>2915.808009548</v>
       </c>
       <c r="V321" t="n">
         <v>1970.68403403934</v>
       </c>
       <c r="W321" t="n">
-        <v>743.654352467675</v>
+        <v>743.654352467674</v>
       </c>
       <c r="X321" t="n">
         <v>609.973629583604</v>
@@ -35152,7 +35152,7 @@
         <v>0</v>
       </c>
       <c r="Z321" t="n">
-        <v>923.037018285405</v>
+        <v>923.037018285404</v>
       </c>
       <c r="AA321" t="n">
         <v>0.005</v>
@@ -35217,7 +35217,7 @@
         <v>0.0233518020716135</v>
       </c>
       <c r="N322" t="n">
-        <v>0.00126618660121637</v>
+        <v>0.00126618660121638</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
@@ -35238,16 +35238,16 @@
         <v>1362.37056709788</v>
       </c>
       <c r="U322" t="n">
-        <v>6113.20126261869</v>
+        <v>6113.20126261868</v>
       </c>
       <c r="V322" t="n">
         <v>1861.16197690967</v>
       </c>
       <c r="W322" t="n">
-        <v>100.916338303546</v>
+        <v>100.916338303547</v>
       </c>
       <c r="X322" t="n">
-        <v>840.969485862887</v>
+        <v>840.969485862888</v>
       </c>
       <c r="Y322" t="n">
         <v>0</v>
@@ -35303,7 +35303,7 @@
         <v>21949.5130904673</v>
       </c>
       <c r="I323" t="n">
-        <v>0.565316211789593</v>
+        <v>0.565316211789592</v>
       </c>
       <c r="J323" t="n">
         <v>0.42918761664517</v>
@@ -35312,7 +35312,7 @@
         <v>0.0484078087097193</v>
       </c>
       <c r="L323" t="n">
-        <v>0.0472770707537474</v>
+        <v>0.0472770707537473</v>
       </c>
       <c r="M323" t="n">
         <v>0.0364833518308918</v>
@@ -35336,7 +35336,7 @@
         <v>28911.4017033433</v>
       </c>
       <c r="T323" t="n">
-        <v>2475.67215303246</v>
+        <v>2475.67215303247</v>
       </c>
       <c r="U323" t="n">
         <v>2417.84395248815</v>
@@ -35416,7 +35416,7 @@
         <v>0.0458371847638385</v>
       </c>
       <c r="M324" t="n">
-        <v>0.0485381857818527</v>
+        <v>0.0485381857818528</v>
       </c>
       <c r="N324" t="n">
         <v>0</v>
@@ -35428,7 +35428,7 @@
         <v>0.00446618723339965</v>
       </c>
       <c r="Q324" t="n">
-        <v>0.0485381857818527</v>
+        <v>0.0485381857818528</v>
       </c>
       <c r="R324" t="n">
         <v>0.0146166127638534</v>
@@ -35455,7 +35455,7 @@
         <v>0</v>
       </c>
       <c r="Z324" t="n">
-        <v>517.369625389354</v>
+        <v>517.369625389355</v>
       </c>
       <c r="AA324" t="n">
         <v>0.00666666666666667</v>
@@ -35514,7 +35514,7 @@
         <v>0.0232314164247242</v>
       </c>
       <c r="L325" t="n">
-        <v>0.0824715283077706</v>
+        <v>0.0824715283077709</v>
       </c>
       <c r="M325" t="n">
         <v>0.0390287795935366</v>
@@ -35535,19 +35535,19 @@
         <v>0.0339759465211591</v>
       </c>
       <c r="S325" t="n">
-        <v>26923.2894061551</v>
+        <v>26923.2894061552</v>
       </c>
       <c r="T325" t="n">
         <v>1071.61877683968</v>
       </c>
       <c r="U325" t="n">
-        <v>3804.24665778084</v>
+        <v>3804.24665778086</v>
       </c>
       <c r="V325" t="n">
         <v>1800.31954509066</v>
       </c>
       <c r="W325" t="n">
-        <v>857.295021471743</v>
+        <v>857.295021471742</v>
       </c>
       <c r="X325" t="n">
         <v>232.458842360607</v>
@@ -35615,19 +35615,19 @@
         <v>0.048291000739463</v>
       </c>
       <c r="L326" t="n">
-        <v>0.0637958036524681</v>
+        <v>0.0637958036524679</v>
       </c>
       <c r="M326" t="n">
         <v>0.0489908703153973</v>
       </c>
       <c r="N326" t="n">
-        <v>0.00581430109237683</v>
+        <v>0.00581430109237682</v>
       </c>
       <c r="O326" t="n">
         <v>0</v>
       </c>
       <c r="P326" t="n">
-        <v>0.00954367603546701</v>
+        <v>0.009543676035467</v>
       </c>
       <c r="Q326" t="n">
         <v>0.0548051714077741</v>
@@ -35642,7 +35642,7 @@
         <v>2722.59833069019</v>
       </c>
       <c r="U326" t="n">
-        <v>3596.7436141225</v>
+        <v>3596.74361412249</v>
       </c>
       <c r="V326" t="n">
         <v>2762.05627751178</v>
@@ -35713,7 +35713,7 @@
         <v>0.32692352317586</v>
       </c>
       <c r="K327" t="n">
-        <v>0.0442023648687139</v>
+        <v>0.044202364868714</v>
       </c>
       <c r="L327" t="n">
         <v>0.0260191193204475</v>
@@ -35743,7 +35743,7 @@
         <v>1465.35259776274</v>
       </c>
       <c r="U327" t="n">
-        <v>862.559824592155</v>
+        <v>862.559824592156</v>
       </c>
       <c r="V327" t="n">
         <v>1963.83890874711</v>
@@ -35820,7 +35820,7 @@
         <v>0.0272632114796006</v>
       </c>
       <c r="M328" t="n">
-        <v>0.0304478772758695</v>
+        <v>0.0304478772758694</v>
       </c>
       <c r="N328" t="n">
         <v>0.00902506311048848</v>
@@ -35829,7 +35829,7 @@
         <v>0</v>
       </c>
       <c r="P328" t="n">
-        <v>0.00712504982406984</v>
+        <v>0.00712504982406985</v>
       </c>
       <c r="Q328" t="n">
         <v>0.0394729403863579</v>
@@ -35853,7 +35853,7 @@
         <v>423.880139110312</v>
       </c>
       <c r="X328" t="n">
-        <v>334.642215087088</v>
+        <v>334.642215087089</v>
       </c>
       <c r="Y328" t="n">
         <v>0</v>
@@ -35918,7 +35918,7 @@
         <v>0.0309335400294238</v>
       </c>
       <c r="L329" t="n">
-        <v>0.062452942559405</v>
+        <v>0.0624529425594048</v>
       </c>
       <c r="M329" t="n">
         <v>0.0356438745339042</v>
@@ -35930,7 +35930,7 @@
         <v>0</v>
       </c>
       <c r="P329" t="n">
-        <v>0.00800536205141028</v>
+        <v>0.00800536205141027</v>
       </c>
       <c r="Q329" t="n">
         <v>0.0356438745339042</v>
@@ -35960,7 +35960,7 @@
         <v>0</v>
       </c>
       <c r="Z329" t="n">
-        <v>939.900071020244</v>
+        <v>939.900071020243</v>
       </c>
       <c r="AA329" t="n">
         <v>0.00676923076923077</v>
@@ -36016,10 +36016,10 @@
         <v>0.401459215936612</v>
       </c>
       <c r="K330" t="n">
-        <v>0.0367428544370534</v>
+        <v>0.0367428544370535</v>
       </c>
       <c r="L330" t="n">
-        <v>0.0730948274439253</v>
+        <v>0.0730948274439255</v>
       </c>
       <c r="M330" t="n">
         <v>0.0303128549105691</v>
@@ -36031,7 +36031,7 @@
         <v>0</v>
       </c>
       <c r="P330" t="n">
-        <v>0.00829069536015565</v>
+        <v>0.00829069536015566</v>
       </c>
       <c r="Q330" t="n">
         <v>0.0410907588787715</v>
@@ -36040,13 +36040,13 @@
         <v>0.0373081291207005</v>
       </c>
       <c r="S330" t="n">
-        <v>28489.7491030478</v>
+        <v>28489.7491030479</v>
       </c>
       <c r="T330" t="n">
         <v>1867.01466251</v>
       </c>
       <c r="U330" t="n">
-        <v>3714.16746690818</v>
+        <v>3714.16746690819</v>
       </c>
       <c r="V330" t="n">
         <v>1540.28709657075</v>
@@ -36117,7 +36117,7 @@
         <v>0.347724311081752</v>
       </c>
       <c r="K331" t="n">
-        <v>0.0348342324628732</v>
+        <v>0.0348342324628733</v>
       </c>
       <c r="L331" t="n">
         <v>0.0497668482907079</v>
@@ -36156,7 +36156,7 @@
         <v>848.141592946695</v>
       </c>
       <c r="X331" t="n">
-        <v>78.5316289765458</v>
+        <v>78.5316289765459</v>
       </c>
       <c r="Y331" t="n">
         <v>0</v>
@@ -36212,7 +36212,7 @@
         <v>16622.6560425987</v>
       </c>
       <c r="I332" t="n">
-        <v>0.455232677801865</v>
+        <v>0.455232677801866</v>
       </c>
       <c r="J332" t="n">
         <v>0.354601532576716</v>
@@ -36242,7 +36242,7 @@
         <v>0.00952023569755863</v>
       </c>
       <c r="S332" t="n">
-        <v>21339.942237318</v>
+        <v>21339.9422373181</v>
       </c>
       <c r="T332" t="n">
         <v>1115.70022198614</v>
@@ -36364,7 +36364,7 @@
         <v>0</v>
       </c>
       <c r="Z333" t="n">
-        <v>668.252433154318</v>
+        <v>668.252433154317</v>
       </c>
       <c r="AA333" t="n">
         <v>0.00276923076923077</v>
@@ -36414,7 +36414,7 @@
         <v>11598.5813285029</v>
       </c>
       <c r="I334" t="n">
-        <v>0.457901872225975</v>
+        <v>0.457901872225974</v>
       </c>
       <c r="J334" t="n">
         <v>0.273094142556166</v>
@@ -36423,7 +36423,7 @@
         <v>0.0336104235700099</v>
       </c>
       <c r="L334" t="n">
-        <v>0.0889285291201077</v>
+        <v>0.0889285291201076</v>
       </c>
       <c r="M334" t="n">
         <v>0.044669137001213</v>
@@ -36521,7 +36521,7 @@
         <v>0.612674677867021</v>
       </c>
       <c r="K335" t="n">
-        <v>0.0365522974659314</v>
+        <v>0.0365522974659313</v>
       </c>
       <c r="L335" t="n">
         <v>0.134929379317598</v>
@@ -36652,7 +36652,7 @@
         <v>1714.82318479098</v>
       </c>
       <c r="U336" t="n">
-        <v>1855.34341798912</v>
+        <v>1855.34341798913</v>
       </c>
       <c r="V336" t="n">
         <v>2218.32446032535</v>
@@ -36667,7 +36667,7 @@
         <v>0</v>
       </c>
       <c r="Z336" t="n">
-        <v>339.982335767255</v>
+        <v>339.982335767254</v>
       </c>
       <c r="AA336" t="n">
         <v>0.00631578947368421</v>
@@ -36744,13 +36744,13 @@
         <v>0.0634663141756284</v>
       </c>
       <c r="R337" t="n">
-        <v>0.0647330947756387</v>
+        <v>0.0647330947756386</v>
       </c>
       <c r="S337" t="n">
         <v>18365.6321327539</v>
       </c>
       <c r="T337" t="n">
-        <v>1140.54348875867</v>
+        <v>1140.54348875866</v>
       </c>
       <c r="U337" t="n">
         <v>2476.80424018832</v>
@@ -36759,16 +36759,16 @@
         <v>1624.13392799234</v>
       </c>
       <c r="W337" t="n">
-        <v>958.056530557279</v>
+        <v>958.056530557278</v>
       </c>
       <c r="X337" t="n">
-        <v>67.6722469996807</v>
+        <v>67.6722469996808</v>
       </c>
       <c r="Y337" t="n">
         <v>0</v>
       </c>
       <c r="Z337" t="n">
-        <v>2633.73069404164</v>
+        <v>2633.73069404163</v>
       </c>
       <c r="AA337" t="n">
         <v>0.00561797752808989</v>
@@ -36854,7 +36854,7 @@
         <v>1039.3437263443</v>
       </c>
       <c r="U338" t="n">
-        <v>3928.09502063434</v>
+        <v>3928.09502063435</v>
       </c>
       <c r="V338" t="n">
         <v>2113.91944341214</v>
@@ -36925,10 +36925,10 @@
         <v>0.384350269004075</v>
       </c>
       <c r="K339" t="n">
-        <v>0.0207012830479437</v>
+        <v>0.0207012830479436</v>
       </c>
       <c r="L339" t="n">
-        <v>0.0377741543968247</v>
+        <v>0.0377741543968246</v>
       </c>
       <c r="M339" t="n">
         <v>0.0386954752357716</v>
@@ -36964,7 +36964,7 @@
         <v>226.848354022187</v>
       </c>
       <c r="X339" t="n">
-        <v>229.029588195477</v>
+        <v>229.029588195478</v>
       </c>
       <c r="Y339" t="n">
         <v>0</v>
@@ -37053,7 +37053,7 @@
         <v>42162.7531540566</v>
       </c>
       <c r="T340" t="n">
-        <v>1220.21361779833</v>
+        <v>1220.21361779832</v>
       </c>
       <c r="U340" t="n">
         <v>5389.27681194259</v>
@@ -37121,7 +37121,7 @@
         <v>12435.9665808298</v>
       </c>
       <c r="I341" t="n">
-        <v>0.397988364903313</v>
+        <v>0.397988364903314</v>
       </c>
       <c r="J341" t="n">
         <v>0.286807347343861</v>
@@ -37133,7 +37133,7 @@
         <v>0.0232595722898265</v>
       </c>
       <c r="M341" t="n">
-        <v>0.0522770495893304</v>
+        <v>0.0522770495893306</v>
       </c>
       <c r="N341" t="n">
         <v>0</v>
@@ -37145,10 +37145,10 @@
         <v>0.0057747903616121</v>
       </c>
       <c r="Q341" t="n">
-        <v>0.0522770495893304</v>
+        <v>0.0522770495893306</v>
       </c>
       <c r="R341" t="n">
-        <v>0.00329988020663549</v>
+        <v>0.00329988020663548</v>
       </c>
       <c r="S341" t="n">
         <v>17256.7755022077</v>
@@ -37160,7 +37160,7 @@
         <v>1008.53505448688</v>
       </c>
       <c r="V341" t="n">
-        <v>2266.73287019336</v>
+        <v>2266.73287019337</v>
       </c>
       <c r="W341" t="n">
         <v>0</v>
@@ -37228,10 +37228,10 @@
         <v>0.367718335833759</v>
       </c>
       <c r="K342" t="n">
-        <v>0.0251109883480471</v>
+        <v>0.025110988348047</v>
       </c>
       <c r="L342" t="n">
-        <v>0.12683042051347</v>
+        <v>0.126830420513469</v>
       </c>
       <c r="M342" t="n">
         <v>0.0555311570896811</v>
@@ -37258,7 +37258,7 @@
         <v>1070.53165525394</v>
       </c>
       <c r="U342" t="n">
-        <v>5407.03448733023</v>
+        <v>5407.03448733022</v>
       </c>
       <c r="V342" t="n">
         <v>2367.40428904729</v>
@@ -37433,7 +37433,7 @@
         <v>0.0389748228871019</v>
       </c>
       <c r="L344" t="n">
-        <v>0.0466003317128392</v>
+        <v>0.0466003317128393</v>
       </c>
       <c r="M344" t="n">
         <v>0.0363765013612951</v>
@@ -37445,13 +37445,13 @@
         <v>0</v>
       </c>
       <c r="P344" t="n">
-        <v>0.00544949984439344</v>
+        <v>0.00544949984439345</v>
       </c>
       <c r="Q344" t="n">
         <v>0.0363765013612951</v>
       </c>
       <c r="R344" t="n">
-        <v>0.0259832152580679</v>
+        <v>0.025983215258068</v>
       </c>
       <c r="S344" t="n">
         <v>28800.7806747796</v>
@@ -37546,7 +37546,7 @@
         <v>0</v>
       </c>
       <c r="P345" t="n">
-        <v>0.00541903503107914</v>
+        <v>0.00541903503107915</v>
       </c>
       <c r="Q345" t="n">
         <v>0.0653535624748146</v>
@@ -37576,7 +37576,7 @@
         <v>0</v>
       </c>
       <c r="Z345" t="n">
-        <v>474.125237516868</v>
+        <v>474.125237516869</v>
       </c>
       <c r="AA345" t="n">
         <v>0.00775193798449612</v>
@@ -37736,7 +37736,7 @@
         <v>0.027795453731941</v>
       </c>
       <c r="L347" t="n">
-        <v>0.0705777978773424</v>
+        <v>0.0705777978773425</v>
       </c>
       <c r="M347" t="n">
         <v>0.036386775794541</v>
@@ -37778,7 +37778,7 @@
         <v>0</v>
       </c>
       <c r="Z347" t="n">
-        <v>542.203389089545</v>
+        <v>542.203389089544</v>
       </c>
       <c r="AA347" t="n">
         <v>0.0055</v>
@@ -37837,7 +37837,7 @@
         <v>0.0433187765726917</v>
       </c>
       <c r="L348" t="n">
-        <v>0.0694170801909775</v>
+        <v>0.0694170801909777</v>
       </c>
       <c r="M348" t="n">
         <v>0.0438602612798504</v>
@@ -37855,7 +37855,7 @@
         <v>0.06185421462543</v>
       </c>
       <c r="R348" t="n">
-        <v>0.0201656373700462</v>
+        <v>0.0201656373700461</v>
       </c>
       <c r="S348" t="n">
         <v>21629.5424803526</v>
@@ -37864,7 +37864,7 @@
         <v>1961.95070975378</v>
       </c>
       <c r="U348" t="n">
-        <v>3143.96897892956</v>
+        <v>3143.96897892957</v>
       </c>
       <c r="V348" t="n">
         <v>1986.4750936257</v>
@@ -37873,7 +37873,7 @@
         <v>814.964140974647</v>
       </c>
       <c r="X348" t="n">
-        <v>567.564312464486</v>
+        <v>567.564312464487</v>
       </c>
       <c r="Y348" t="n">
         <v>0</v>
@@ -37941,7 +37941,7 @@
         <v>0.0622949532445938</v>
       </c>
       <c r="M349" t="n">
-        <v>0.0359745274771396</v>
+        <v>0.0359745274771397</v>
       </c>
       <c r="N349" t="n">
         <v>0.0217466018599309</v>
@@ -38066,7 +38066,7 @@
         <v>1358.14356213384</v>
       </c>
       <c r="U350" t="n">
-        <v>9327.28409505655</v>
+        <v>9327.28409505654</v>
       </c>
       <c r="V350" t="n">
         <v>2287.39968359384</v>
@@ -38146,7 +38146,7 @@
         <v>0.0357029922490573</v>
       </c>
       <c r="N351" t="n">
-        <v>0.0077070679436713</v>
+        <v>0.00770706794367131</v>
       </c>
       <c r="O351" t="n">
         <v>0</v>
@@ -38155,7 +38155,7 @@
         <v>0.0100306914132558</v>
       </c>
       <c r="Q351" t="n">
-        <v>0.0434100601927286</v>
+        <v>0.0434100601927287</v>
       </c>
       <c r="R351" t="n">
         <v>0.0140011734310029</v>
@@ -38232,7 +38232,7 @@
         <v>15053.1005269098</v>
       </c>
       <c r="I352" t="n">
-        <v>0.49535528270842</v>
+        <v>0.495355282708421</v>
       </c>
       <c r="J352" t="n">
         <v>0.327426382888367</v>
@@ -38241,7 +38241,7 @@
         <v>0.047093138640217</v>
       </c>
       <c r="L352" t="n">
-        <v>0.0457849959002109</v>
+        <v>0.045784995900211</v>
       </c>
       <c r="M352" t="n">
         <v>0.0439535960642025</v>
@@ -38354,10 +38354,10 @@
         <v>0</v>
       </c>
       <c r="P353" t="n">
-        <v>0.0085018116685815</v>
+        <v>0.00850181166858148</v>
       </c>
       <c r="Q353" t="n">
-        <v>0.0612424875174007</v>
+        <v>0.0612424875174008</v>
       </c>
       <c r="R353" t="n">
         <v>0.00947344728784793</v>
@@ -38375,10 +38375,10 @@
         <v>2407.69098191456</v>
       </c>
       <c r="W353" t="n">
-        <v>160.512732127637</v>
+        <v>160.512732127638</v>
       </c>
       <c r="X353" t="n">
-        <v>356.523472321965</v>
+        <v>356.523472321964</v>
       </c>
       <c r="Y353" t="n">
         <v>0</v>
@@ -38443,7 +38443,7 @@
         <v>0.0310764504935725</v>
       </c>
       <c r="L354" t="n">
-        <v>0.0462950322495676</v>
+        <v>0.0462950322495677</v>
       </c>
       <c r="M354" t="n">
         <v>0.0374951500864267</v>
@@ -38470,7 +38470,7 @@
         <v>1214.37445593733</v>
       </c>
       <c r="U354" t="n">
-        <v>1809.07097521635</v>
+        <v>1809.07097521636</v>
       </c>
       <c r="V354" t="n">
         <v>1465.1979799273</v>
@@ -38485,7 +38485,7 @@
         <v>0</v>
       </c>
       <c r="Z354" t="n">
-        <v>484.727151254142</v>
+        <v>484.727151254143</v>
       </c>
       <c r="AA354" t="n">
         <v>0.00316455696202532</v>
@@ -38541,7 +38541,7 @@
         <v>0.319769651201757</v>
       </c>
       <c r="K355" t="n">
-        <v>0.0362138334576665</v>
+        <v>0.0362138334576666</v>
       </c>
       <c r="L355" t="n">
         <v>0.0595028644018225</v>
@@ -38550,7 +38550,7 @@
         <v>0.0489289127605806</v>
       </c>
       <c r="N355" t="n">
-        <v>0.00666001534853639</v>
+        <v>0.00666001534853638</v>
       </c>
       <c r="O355" t="n">
         <v>0</v>
@@ -38562,7 +38562,7 @@
         <v>0.055588928109117</v>
       </c>
       <c r="R355" t="n">
-        <v>0.00990463821064386</v>
+        <v>0.00990463821064384</v>
       </c>
       <c r="S355" t="n">
         <v>24534.8760566416</v>
@@ -38586,7 +38586,7 @@
         <v>0</v>
       </c>
       <c r="Z355" t="n">
-        <v>505.215785848522</v>
+        <v>505.215785848521</v>
       </c>
       <c r="AA355" t="n">
         <v>0.00675</v>
@@ -38657,7 +38657,7 @@
         <v>0</v>
       </c>
       <c r="P356" t="n">
-        <v>0.00322767808297684</v>
+        <v>0.00322767808297683</v>
       </c>
       <c r="Q356" t="n">
         <v>0.0294835978733461</v>
@@ -38666,7 +38666,7 @@
         <v>0.113217015833649</v>
       </c>
       <c r="S356" t="n">
-        <v>56919.564937563</v>
+        <v>56919.5649375629</v>
       </c>
       <c r="T356" t="n">
         <v>1366.13312155673</v>
@@ -38737,7 +38737,7 @@
         <v>13553.7286498695</v>
       </c>
       <c r="I357" t="n">
-        <v>0.594978438560465</v>
+        <v>0.594978438560466</v>
       </c>
       <c r="J357" t="n">
         <v>0.387326855367345</v>
@@ -38746,7 +38746,7 @@
         <v>0.0299978210070319</v>
       </c>
       <c r="L357" t="n">
-        <v>0.111936313572535</v>
+        <v>0.111936313572536</v>
       </c>
       <c r="M357" t="n">
         <v>0.0584957509637121</v>
@@ -38758,7 +38758,7 @@
         <v>0</v>
       </c>
       <c r="P357" t="n">
-        <v>0.00722169764984099</v>
+        <v>0.007221697649841</v>
       </c>
       <c r="Q357" t="n">
         <v>0.0584957509637121</v>
@@ -38844,7 +38844,7 @@
         <v>0.372627960592864</v>
       </c>
       <c r="K358" t="n">
-        <v>0.0333466798264313</v>
+        <v>0.0333466798264314</v>
       </c>
       <c r="L358" t="n">
         <v>0.0512705202331382</v>
@@ -38871,7 +38871,7 @@
         <v>18806.0995257647</v>
       </c>
       <c r="T358" t="n">
-        <v>1192.47727059318</v>
+        <v>1192.47727059319</v>
       </c>
       <c r="U358" t="n">
         <v>1833.43380353702</v>
@@ -38948,7 +38948,7 @@
         <v>0.0201094731732607</v>
       </c>
       <c r="L359" t="n">
-        <v>0.0868363614299895</v>
+        <v>0.0868363614299894</v>
       </c>
       <c r="M359" t="n">
         <v>0.0347345445719958</v>
@@ -38963,7 +38963,7 @@
         <v>0.0124051944899985</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.0382079990291954</v>
+        <v>0.0382079990291953</v>
       </c>
       <c r="R359" t="n">
         <v>0.0226529638513016</v>
@@ -38984,7 +38984,7 @@
         <v>234.065675507308</v>
       </c>
       <c r="X359" t="n">
-        <v>835.948841097529</v>
+        <v>835.948841097528</v>
       </c>
       <c r="Y359" t="n">
         <v>0</v>
@@ -39049,7 +39049,7 @@
         <v>0.0466489270502561</v>
       </c>
       <c r="L360" t="n">
-        <v>0.0607663654996759</v>
+        <v>0.0607663654996757</v>
       </c>
       <c r="M360" t="n">
         <v>0.0471436790274562</v>
@@ -39076,7 +39076,7 @@
         <v>2189.37409324967</v>
       </c>
       <c r="U360" t="n">
-        <v>2851.94783199629</v>
+        <v>2851.94783199628</v>
       </c>
       <c r="V360" t="n">
         <v>2212.5942877956</v>
@@ -39284,7 +39284,7 @@
         <v>2044.28189675431</v>
       </c>
       <c r="W362" t="n">
-        <v>282.433683104213</v>
+        <v>282.433683104214</v>
       </c>
       <c r="X362" t="n">
         <v>596.24888655334</v>
@@ -39364,7 +39364,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="n">
-        <v>0.00966222408791351</v>
+        <v>0.00966222408791353</v>
       </c>
       <c r="Q363" t="n">
         <v>0.0539152104105575</v>
@@ -39388,13 +39388,13 @@
         <v>522.928843373005</v>
       </c>
       <c r="X363" t="n">
-        <v>484.193373493522</v>
+        <v>484.193373493523</v>
       </c>
       <c r="Y363" t="n">
         <v>0</v>
       </c>
       <c r="Z363" t="n">
-        <v>804.505912881547</v>
+        <v>804.505912881546</v>
       </c>
       <c r="AA363" t="n">
         <v>0.00275</v>
@@ -39453,7 +39453,7 @@
         <v>0.0416821149789937</v>
       </c>
       <c r="L364" t="n">
-        <v>0.070297217722509</v>
+        <v>0.0702972177225093</v>
       </c>
       <c r="M364" t="n">
         <v>0.0534386089474279</v>
@@ -39480,7 +39480,7 @@
         <v>1862.4402614914</v>
       </c>
       <c r="U364" t="n">
-        <v>3141.02028227715</v>
+        <v>3141.02028227716</v>
       </c>
       <c r="V364" t="n">
         <v>2387.74392498897</v>
@@ -39495,7 +39495,7 @@
         <v>0</v>
       </c>
       <c r="Z364" t="n">
-        <v>551.834151553006</v>
+        <v>551.834151553007</v>
       </c>
       <c r="AA364" t="n">
         <v>0.0072</v>
@@ -39667,7 +39667,7 @@
         <v>0</v>
       </c>
       <c r="P366" t="n">
-        <v>0.00944964330846404</v>
+        <v>0.00944964330846402</v>
       </c>
       <c r="Q366" t="n">
         <v>0.0519730381965521</v>
@@ -39691,7 +39691,7 @@
         <v>0</v>
       </c>
       <c r="X366" t="n">
-        <v>440.920356772932</v>
+        <v>440.920356772931</v>
       </c>
       <c r="Y366" t="n">
         <v>0</v>
@@ -39783,7 +39783,7 @@
         <v>1434.655357271</v>
       </c>
       <c r="U367" t="n">
-        <v>5053.47641604541</v>
+        <v>5053.47641604542</v>
       </c>
       <c r="V367" t="n">
         <v>1846.54028242299</v>
@@ -39857,7 +39857,7 @@
         <v>0.0311867461865939</v>
       </c>
       <c r="L368" t="n">
-        <v>0.0658323860411553</v>
+        <v>0.0658323860411555</v>
       </c>
       <c r="M368" t="n">
         <v>0.0440286997843248</v>
@@ -39869,13 +39869,13 @@
         <v>0</v>
       </c>
       <c r="P368" t="n">
-        <v>0.0114255763329206</v>
+        <v>0.0114255763329205</v>
       </c>
       <c r="Q368" t="n">
-        <v>0.0487006755678907</v>
+        <v>0.0487006755678906</v>
       </c>
       <c r="R368" t="n">
-        <v>0.00534761535842003</v>
+        <v>0.00534761535842001</v>
       </c>
       <c r="S368" t="n">
         <v>18581.8264439852</v>
@@ -39884,7 +39884,7 @@
         <v>1302.70157496021</v>
       </c>
       <c r="U368" t="n">
-        <v>2749.8845973251</v>
+        <v>2749.88459732511</v>
       </c>
       <c r="V368" t="n">
         <v>1839.12281869103</v>
@@ -39893,13 +39893,13 @@
         <v>195.15310045533</v>
       </c>
       <c r="X368" t="n">
-        <v>477.257749002425</v>
+        <v>477.257749002424</v>
       </c>
       <c r="Y368" t="n">
         <v>0</v>
       </c>
       <c r="Z368" t="n">
-        <v>223.375241136563</v>
+        <v>223.375241136562</v>
       </c>
       <c r="AA368" t="n">
         <v>0.00645994832041344</v>
@@ -40059,25 +40059,25 @@
         <v>0.0229924340058049</v>
       </c>
       <c r="L370" t="n">
-        <v>0.0653575019115447</v>
+        <v>0.0653575019115446</v>
       </c>
       <c r="M370" t="n">
         <v>0.0360508547129346</v>
       </c>
       <c r="N370" t="n">
-        <v>0.00695569432108383</v>
+        <v>0.00695569432108384</v>
       </c>
       <c r="O370" t="n">
         <v>0</v>
       </c>
       <c r="P370" t="n">
-        <v>0.00601764903096314</v>
+        <v>0.00601764903096312</v>
       </c>
       <c r="Q370" t="n">
         <v>0.0430065490340184</v>
       </c>
       <c r="R370" t="n">
-        <v>0.0570488964053809</v>
+        <v>0.0570488964053806</v>
       </c>
       <c r="S370" t="n">
         <v>22915.5969729843</v>
@@ -40086,22 +40086,22 @@
         <v>1222.57669339067</v>
       </c>
       <c r="U370" t="n">
-        <v>3475.25444914257</v>
+        <v>3475.25444914256</v>
       </c>
       <c r="V370" t="n">
         <v>1916.93209765087</v>
       </c>
       <c r="W370" t="n">
-        <v>369.85513413499</v>
+        <v>369.855134134991</v>
       </c>
       <c r="X370" t="n">
-        <v>319.976451923403</v>
+        <v>319.976451923402</v>
       </c>
       <c r="Y370" t="n">
         <v>0</v>
       </c>
       <c r="Z370" t="n">
-        <v>3033.46096856332</v>
+        <v>3033.4609685633</v>
       </c>
       <c r="AA370" t="n">
         <v>0.00466666666666667</v>
@@ -40163,7 +40163,7 @@
         <v>0.0290733911084375</v>
       </c>
       <c r="M371" t="n">
-        <v>0.042220434778311</v>
+        <v>0.0422204347783109</v>
       </c>
       <c r="N371" t="n">
         <v>0.0151181633763875</v>
@@ -40175,7 +40175,7 @@
         <v>0.00831898937113385</v>
       </c>
       <c r="Q371" t="n">
-        <v>0.0573385981546985</v>
+        <v>0.0573385981546984</v>
       </c>
       <c r="R371" t="n">
         <v>0.0287965016693095</v>
@@ -40261,7 +40261,7 @@
         <v>0.0226056357193426</v>
       </c>
       <c r="L372" t="n">
-        <v>0.0654098255768013</v>
+        <v>0.0654098255768014</v>
       </c>
       <c r="M372" t="n">
         <v>0.0169542267895069</v>
@@ -40282,13 +40282,13 @@
         <v>0.00880739054000359</v>
       </c>
       <c r="S372" t="n">
-        <v>37731.5831927304</v>
+        <v>37731.5831927305</v>
       </c>
       <c r="T372" t="n">
         <v>1260.76151533917</v>
       </c>
       <c r="U372" t="n">
-        <v>3648.03679206936</v>
+        <v>3648.03679206937</v>
       </c>
       <c r="V372" t="n">
         <v>945.57113650438</v>
@@ -40297,7 +40297,7 @@
         <v>0</v>
       </c>
       <c r="X372" t="n">
-        <v>570.34449503439</v>
+        <v>570.344495034388</v>
       </c>
       <c r="Y372" t="n">
         <v>0</v>
@@ -40368,7 +40368,7 @@
         <v>0.0501152465617155</v>
       </c>
       <c r="N373" t="n">
-        <v>0.0216761447066244</v>
+        <v>0.0216761447066243</v>
       </c>
       <c r="O373" t="n">
         <v>0</v>
@@ -40377,7 +40377,7 @@
         <v>0.0111864389646686</v>
       </c>
       <c r="Q373" t="n">
-        <v>0.0717913912683399</v>
+        <v>0.0717913912683398</v>
       </c>
       <c r="R373" t="n">
         <v>0.0348022545567469</v>
@@ -40386,7 +40386,7 @@
         <v>13119.7428718607</v>
       </c>
       <c r="T373" t="n">
-        <v>834.022109550617</v>
+        <v>834.022109550616</v>
       </c>
       <c r="U373" t="n">
         <v>1101.76216176431</v>
@@ -40395,7 +40395,7 @@
         <v>1637.7161423903</v>
       </c>
       <c r="W373" t="n">
-        <v>708.354732867778</v>
+        <v>708.354732867777</v>
       </c>
       <c r="X373" t="n">
         <v>365.561638926406</v>
@@ -40481,7 +40481,7 @@
         <v>0.0557569856979455</v>
       </c>
       <c r="R374" t="n">
-        <v>0.00716800699559894</v>
+        <v>0.00716800699559895</v>
       </c>
       <c r="S374" t="n">
         <v>21253.7477371076</v>
@@ -40490,7 +40490,7 @@
         <v>2149.24948315479</v>
       </c>
       <c r="U374" t="n">
-        <v>2787.77970156972</v>
+        <v>2787.77970156971</v>
       </c>
       <c r="V374" t="n">
         <v>1683.57876180459</v>
@@ -40505,7 +40505,7 @@
         <v>0</v>
       </c>
       <c r="Z374" t="n">
-        <v>316.066100463939</v>
+        <v>316.06610046394</v>
       </c>
       <c r="AA374" t="n">
         <v>0.0096</v>
@@ -40561,13 +40561,13 @@
         <v>0.250981895818095</v>
       </c>
       <c r="K375" t="n">
-        <v>0.0430472045037451</v>
+        <v>0.0430472045037452</v>
       </c>
       <c r="L375" t="n">
-        <v>0.0510951601283583</v>
+        <v>0.0510951601283585</v>
       </c>
       <c r="M375" t="n">
-        <v>0.0475611057432683</v>
+        <v>0.0475611057432684</v>
       </c>
       <c r="N375" t="n">
         <v>0.00842227914203711</v>
@@ -40576,13 +40576,13 @@
         <v>0</v>
       </c>
       <c r="P375" t="n">
-        <v>0.0069249850723416</v>
+        <v>0.00692498507234162</v>
       </c>
       <c r="Q375" t="n">
-        <v>0.0559833848853054</v>
+        <v>0.0559833848853055</v>
       </c>
       <c r="R375" t="n">
-        <v>0.0085109347119533</v>
+        <v>0.00851093471195329</v>
       </c>
       <c r="S375" t="n">
         <v>17204.2878285164</v>
@@ -40591,16 +40591,16 @@
         <v>1815.04233069591</v>
       </c>
       <c r="U375" t="n">
-        <v>2154.3763316521</v>
+        <v>2154.37633165211</v>
       </c>
       <c r="V375" t="n">
-        <v>2005.36646255916</v>
+        <v>2005.36646255917</v>
       </c>
       <c r="W375" t="n">
         <v>355.116977744853</v>
       </c>
       <c r="X375" t="n">
-        <v>291.985070590211</v>
+        <v>291.985070590212</v>
       </c>
       <c r="Y375" t="n">
         <v>0</v>
@@ -40662,7 +40662,7 @@
         <v>0.642310564145612</v>
       </c>
       <c r="K376" t="n">
-        <v>0.0481793489441488</v>
+        <v>0.0481793489441487</v>
       </c>
       <c r="L376" t="n">
         <v>0.076516413388931</v>
@@ -40686,7 +40686,7 @@
         <v>0.0599304096622338</v>
       </c>
       <c r="S376" t="n">
-        <v>29616.6119808645</v>
+        <v>29616.6119808646</v>
       </c>
       <c r="T376" t="n">
         <v>1746.74229597011</v>
@@ -40766,7 +40766,7 @@
         <v>0.0338241533474385</v>
       </c>
       <c r="L377" t="n">
-        <v>0.107861466785721</v>
+        <v>0.10786146678572</v>
       </c>
       <c r="M377" t="n">
         <v>0.0710307220296208</v>
@@ -40793,7 +40793,7 @@
         <v>1019.42615773845</v>
       </c>
       <c r="U377" t="n">
-        <v>3250.83674745484</v>
+        <v>3250.83674745483</v>
       </c>
       <c r="V377" t="n">
         <v>2140.79493125074</v>
@@ -40802,7 +40802,7 @@
         <v>131.741226538507</v>
       </c>
       <c r="X377" t="n">
-        <v>176.197113683189</v>
+        <v>176.197113683188</v>
       </c>
       <c r="Y377" t="n">
         <v>0</v>
@@ -40852,7 +40852,7 @@
         <v>51273</v>
       </c>
       <c r="G378" t="n">
-        <v>448642.596005038</v>
+        <v>448642.596005037</v>
       </c>
       <c r="H378" t="n">
         <v>26739.8476084917</v>
@@ -40870,7 +40870,7 @@
         <v>0.0478337433898453</v>
       </c>
       <c r="M378" t="n">
-        <v>0.0480004114852804</v>
+        <v>0.0480004114852803</v>
       </c>
       <c r="N378" t="n">
         <v>0</v>
@@ -40879,13 +40879,13 @@
         <v>0</v>
       </c>
       <c r="P378" t="n">
-        <v>0.01166676668045</v>
+        <v>0.0116667666804501</v>
       </c>
       <c r="Q378" t="n">
-        <v>0.0480004114852804</v>
+        <v>0.0480004114852803</v>
       </c>
       <c r="R378" t="n">
-        <v>0.0214287551273572</v>
+        <v>0.0214287551273573</v>
       </c>
       <c r="S378" t="n">
         <v>34874.575997594</v>
@@ -40903,7 +40903,7 @@
         <v>0</v>
       </c>
       <c r="X378" t="n">
-        <v>598.190128006715</v>
+        <v>598.190128006717</v>
       </c>
       <c r="Y378" t="n">
         <v>0</v>
@@ -40974,13 +40974,13 @@
         <v>0.0424518657310505</v>
       </c>
       <c r="N379" t="n">
-        <v>0.00141329557157056</v>
+        <v>0.00141329557157055</v>
       </c>
       <c r="O379" t="n">
         <v>0</v>
       </c>
       <c r="P379" t="n">
-        <v>0.00471687397011673</v>
+        <v>0.00471687397011672</v>
       </c>
       <c r="Q379" t="n">
         <v>0.0438651613026211</v>
@@ -41001,7 +41001,7 @@
         <v>2339.81948349831</v>
       </c>
       <c r="W379" t="n">
-        <v>77.8966120182544</v>
+        <v>77.8966120182542</v>
       </c>
       <c r="X379" t="n">
         <v>259.979942610924</v>
@@ -41066,7 +41066,7 @@
         <v>0.408721129462649</v>
       </c>
       <c r="K380" t="n">
-        <v>0.0285766150700982</v>
+        <v>0.0285766150700981</v>
       </c>
       <c r="L380" t="n">
         <v>0.0450694043391262</v>
@@ -41081,7 +41081,7 @@
         <v>0</v>
       </c>
       <c r="P380" t="n">
-        <v>0.00705434154873281</v>
+        <v>0.0070543415487328</v>
       </c>
       <c r="Q380" t="n">
         <v>0.0493803908411296</v>
@@ -41099,7 +41099,7 @@
         <v>1858.66223494557</v>
       </c>
       <c r="V380" t="n">
-        <v>2036.44731828819</v>
+        <v>2036.44731828818</v>
       </c>
       <c r="W380" t="n">
         <v>0</v>
@@ -41158,7 +41158,7 @@
         <v>483545.077900569</v>
       </c>
       <c r="H381" t="n">
-        <v>28817.4007579564</v>
+        <v>28817.4007579563</v>
       </c>
       <c r="I381" t="n">
         <v>0.701585522304653</v>
@@ -41188,7 +41188,7 @@
         <v>0.0415254139038699</v>
       </c>
       <c r="R381" t="n">
-        <v>0.0961097249404044</v>
+        <v>0.0961097249404047</v>
       </c>
       <c r="S381" t="n">
         <v>38620.1782463042</v>
@@ -41197,10 +41197,10 @@
         <v>1450.63523370171</v>
       </c>
       <c r="U381" t="n">
-        <v>5714.6236479158</v>
+        <v>5714.62364791581</v>
       </c>
       <c r="V381" t="n">
-        <v>2285.84945916633</v>
+        <v>2285.84945916632</v>
       </c>
       <c r="W381" t="n">
         <v>0</v>
@@ -41212,7 +41212,7 @@
         <v>0</v>
       </c>
       <c r="Z381" t="n">
-        <v>5290.55202879444</v>
+        <v>5290.55202879446</v>
       </c>
       <c r="AA381" t="n">
         <v>0.003</v>
@@ -41372,13 +41372,13 @@
         <v>0.0224840900063327</v>
       </c>
       <c r="L383" t="n">
-        <v>0.0906020074268341</v>
+        <v>0.0906020074268342</v>
       </c>
       <c r="M383" t="n">
         <v>0.0472165890132987</v>
       </c>
       <c r="N383" t="n">
-        <v>0.0133380194952822</v>
+        <v>0.0133380194952821</v>
       </c>
       <c r="O383" t="n">
         <v>0</v>
@@ -41405,7 +41405,7 @@
         <v>2225.83722267592</v>
       </c>
       <c r="W383" t="n">
-        <v>628.767577027096</v>
+        <v>628.767577027095</v>
       </c>
       <c r="X383" t="n">
         <v>525.54489979848</v>
@@ -41414,7 +41414,7 @@
         <v>0</v>
       </c>
       <c r="Z383" t="n">
-        <v>862.727605688338</v>
+        <v>862.727605688339</v>
       </c>
       <c r="AA383" t="n">
         <v>0.00342857142857143</v>
@@ -41464,7 +41464,7 @@
         <v>10503.6822235693</v>
       </c>
       <c r="I384" t="n">
-        <v>0.485348396467387</v>
+        <v>0.485348396467386</v>
       </c>
       <c r="J384" t="n">
         <v>0.311839272736078</v>
@@ -41473,7 +41473,7 @@
         <v>0.0313975120226499</v>
       </c>
       <c r="L384" t="n">
-        <v>0.0674771091714846</v>
+        <v>0.0674771091714844</v>
       </c>
       <c r="M384" t="n">
         <v>0.0376770144271799</v>
@@ -41500,7 +41500,7 @@
         <v>1057.56239745892</v>
       </c>
       <c r="U384" t="n">
-        <v>2272.83146822312</v>
+        <v>2272.83146822311</v>
       </c>
       <c r="V384" t="n">
         <v>1269.0748769507</v>
@@ -41574,7 +41574,7 @@
         <v>0.0264348406461029</v>
       </c>
       <c r="L385" t="n">
-        <v>0.0841108566012366</v>
+        <v>0.0841108566012365</v>
       </c>
       <c r="M385" t="n">
         <v>0.0484478534023123</v>
@@ -41586,7 +41586,7 @@
         <v>0</v>
       </c>
       <c r="P385" t="n">
-        <v>0.00893212636473311</v>
+        <v>0.00893212636473308</v>
       </c>
       <c r="Q385" t="n">
         <v>0.0545038350776013</v>
@@ -41598,7 +41598,7 @@
         <v>34930.3350562269</v>
       </c>
       <c r="T385" t="n">
-        <v>1367.39500210096</v>
+        <v>1367.39500210097</v>
       </c>
       <c r="U385" t="n">
         <v>4350.80227941216</v>
@@ -41610,7 +41610,7 @@
         <v>313.257764117676</v>
       </c>
       <c r="X385" t="n">
-        <v>462.032100468549</v>
+        <v>462.032100468548</v>
       </c>
       <c r="Y385" t="n">
         <v>0</v>
@@ -41687,7 +41687,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="n">
-        <v>0.00995150352574748</v>
+        <v>0.00995150352574746</v>
       </c>
       <c r="Q386" t="n">
         <v>0.0395314898677968</v>
@@ -41711,13 +41711,13 @@
         <v>0</v>
       </c>
       <c r="X386" t="n">
-        <v>467.730617213657</v>
+        <v>467.730617213656</v>
       </c>
       <c r="Y386" t="n">
         <v>0</v>
       </c>
       <c r="Z386" t="n">
-        <v>633.018880439534</v>
+        <v>633.018880439535</v>
       </c>
       <c r="AA386" t="n">
         <v>0.0035</v>
